--- a/数据/用户摸牌表.xlsx
+++ b/数据/用户摸牌表.xlsx
@@ -18,7 +18,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="3">
+  <fonts count="1">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -26,35 +26,16 @@
       <sz val="11"/>
       <scheme val="minor"/>
     </font>
-    <font>
-      <b val="1"/>
-      <color rgb="00FFFFFF"/>
-      <sz val="11"/>
-    </font>
-    <font>
-      <b val="1"/>
-      <color rgb="00FFFFFF"/>
-    </font>
   </fonts>
-  <fills count="4">
+  <fills count="2">
     <fill>
       <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00C00000"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00FDE9D9"/>
-      </patternFill>
-    </fill>
   </fills>
-  <borders count="2">
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -62,32 +43,12 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin"/>
-      <right style="thin"/>
-      <top style="thin"/>
-      <bottom style="thin"/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -453,3557 +414,3538 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M108"/>
+  <dimension ref="A1:M110"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="6" customWidth="1" min="1" max="1"/>
-    <col width="13" customWidth="1" min="2" max="2"/>
-    <col width="15" customWidth="1" min="3" max="3"/>
-    <col width="13" customWidth="1" min="4" max="4"/>
-    <col width="8" customWidth="1" min="5" max="5"/>
-    <col width="10" customWidth="1" min="6" max="6"/>
-    <col width="17" customWidth="1" min="7" max="7"/>
-    <col width="18" customWidth="1" min="8" max="8"/>
-    <col width="12" customWidth="1" min="9" max="9"/>
-    <col width="13" customWidth="1" min="10" max="10"/>
-    <col width="9" customWidth="1" min="11" max="11"/>
-    <col width="55" customWidth="1" min="12" max="12"/>
-    <col width="24" customWidth="1" min="13" max="13"/>
-  </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>序号</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>客户姓名</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>客户分类</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>地址/基地</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>塘口数</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>面积（亩）</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>现用品牌</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>现有经销商（拿料对象）</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>负责人</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="J1" t="inlineStr">
         <is>
           <t>年用量</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="K1" t="inlineStr">
         <is>
           <t>近期包产</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="L1" t="inlineStr">
         <is>
           <t>详细情况</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="M1" t="inlineStr">
         <is>
           <t>跟进建议</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="2" t="n">
+      <c r="A2" t="n">
         <v>1</v>
       </c>
-      <c r="B2" s="2" t="inlineStr">
+      <c r="B2" t="inlineStr">
         <is>
           <t>陈吉</t>
         </is>
       </c>
-      <c r="C2" s="2" t="inlineStr">
+      <c r="C2" t="inlineStr">
         <is>
           <t>一、通威现有用户</t>
         </is>
       </c>
-      <c r="D2" s="2" t="inlineStr"/>
-      <c r="E2" s="2" t="inlineStr"/>
-      <c r="F2" s="2" t="inlineStr"/>
-      <c r="G2" s="3" t="inlineStr">
+      <c r="D2" t="inlineStr"/>
+      <c r="E2" t="inlineStr"/>
+      <c r="F2" t="inlineStr"/>
+      <c r="G2" t="inlineStr">
         <is>
           <t>通威9912</t>
         </is>
       </c>
-      <c r="H2" s="3" t="inlineStr"/>
-      <c r="I2" s="2" t="inlineStr"/>
-      <c r="J2" s="2" t="inlineStr"/>
-      <c r="K2" s="2" t="inlineStr"/>
-      <c r="L2" s="4" t="inlineStr">
+      <c r="H2" t="inlineStr"/>
+      <c r="I2" t="inlineStr"/>
+      <c r="J2" t="inlineStr"/>
+      <c r="K2" t="inlineStr"/>
+      <c r="L2" t="inlineStr">
         <is>
           <t>通威9912饲料用户，合作稳定。日常测水、走访维护，持续沟通后续用料。</t>
         </is>
       </c>
-      <c r="M2" s="4" t="inlineStr">
+      <c r="M2" t="inlineStr">
         <is>
           <t>日常走访维护，持续沟通后续用料</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="2" t="n">
+      <c r="A3" t="n">
         <v>2</v>
       </c>
-      <c r="B3" s="2" t="inlineStr">
+      <c r="B3" t="inlineStr">
         <is>
           <t>陈丽福</t>
         </is>
       </c>
-      <c r="C3" s="2" t="inlineStr">
+      <c r="C3" t="inlineStr">
         <is>
           <t>一、通威现有用户</t>
         </is>
       </c>
-      <c r="D3" s="2" t="inlineStr"/>
-      <c r="E3" s="2" t="inlineStr"/>
-      <c r="F3" s="2" t="inlineStr"/>
-      <c r="G3" s="3" t="inlineStr">
+      <c r="D3" t="inlineStr"/>
+      <c r="E3" t="inlineStr"/>
+      <c r="F3" t="inlineStr"/>
+      <c r="G3" t="inlineStr">
         <is>
           <t>通威</t>
         </is>
       </c>
-      <c r="H3" s="3" t="inlineStr"/>
-      <c r="I3" s="2" t="inlineStr"/>
-      <c r="J3" s="2" t="inlineStr"/>
-      <c r="K3" s="2" t="inlineStr"/>
-      <c r="L3" s="4" t="inlineStr">
+      <c r="H3" t="inlineStr"/>
+      <c r="I3" t="inlineStr"/>
+      <c r="J3" t="inlineStr"/>
+      <c r="K3" t="inlineStr"/>
+      <c r="L3" t="inlineStr">
         <is>
           <t>通威老客户，全程使用通威产品。节日走访并赠送礼品。</t>
         </is>
       </c>
-      <c r="M3" s="4" t="inlineStr">
+      <c r="M3" t="inlineStr">
         <is>
           <t>日常走访维护，持续沟通后续用料</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="2" t="n">
+      <c r="A4" t="n">
         <v>3</v>
       </c>
-      <c r="B4" s="2" t="inlineStr">
+      <c r="B4" t="inlineStr">
         <is>
           <t>吴喜</t>
         </is>
       </c>
-      <c r="C4" s="2" t="inlineStr">
+      <c r="C4" t="inlineStr">
         <is>
           <t>一、通威现有用户</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr"/>
-      <c r="E4" s="2" t="inlineStr"/>
-      <c r="F4" s="2" t="inlineStr"/>
-      <c r="G4" s="3" t="inlineStr">
+      <c r="D4" t="inlineStr"/>
+      <c r="E4" t="inlineStr"/>
+      <c r="F4" t="inlineStr"/>
+      <c r="G4" t="inlineStr">
         <is>
           <t>通威</t>
         </is>
       </c>
-      <c r="H4" s="3" t="inlineStr"/>
-      <c r="I4" s="2" t="inlineStr"/>
-      <c r="J4" s="2" t="inlineStr"/>
-      <c r="K4" s="2" t="inlineStr"/>
-      <c r="L4" s="4" t="inlineStr">
+      <c r="H4" t="inlineStr"/>
+      <c r="I4" t="inlineStr"/>
+      <c r="J4" t="inlineStr"/>
+      <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr">
         <is>
           <t>通威用户，客情维护中。</t>
         </is>
       </c>
-      <c r="M4" s="4" t="inlineStr">
+      <c r="M4" t="inlineStr">
         <is>
           <t>日常走访维护，持续沟通后续用料</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="2" t="n">
+      <c r="A5" t="n">
         <v>4</v>
       </c>
-      <c r="B5" s="2" t="inlineStr">
+      <c r="B5" t="inlineStr">
         <is>
           <t>丁杰秋</t>
         </is>
       </c>
-      <c r="C5" s="2" t="inlineStr">
+      <c r="C5" t="inlineStr">
         <is>
           <t>一、通威现有用户</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr"/>
-      <c r="E5" s="2" t="inlineStr"/>
-      <c r="F5" s="2" t="inlineStr"/>
-      <c r="G5" s="3" t="inlineStr">
+      <c r="D5" t="inlineStr"/>
+      <c r="E5" t="inlineStr"/>
+      <c r="F5" t="inlineStr"/>
+      <c r="G5" t="inlineStr">
         <is>
           <t>通威</t>
         </is>
       </c>
-      <c r="H5" s="3" t="inlineStr"/>
-      <c r="I5" s="2" t="inlineStr"/>
-      <c r="J5" s="2" t="inlineStr"/>
-      <c r="K5" s="2" t="inlineStr"/>
-      <c r="L5" s="4" t="inlineStr">
+      <c r="H5" t="inlineStr"/>
+      <c r="I5" t="inlineStr"/>
+      <c r="J5" t="inlineStr"/>
+      <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr">
         <is>
           <t>已转用通威。有效塘口1、2、3、6、7号已完成两轮打样：9月7/8日至9月29日，1号塘0.50增至0.72、2号塘0.31增至0.50、3号塘0.25增至0.54、6号塘0.55增至0.72、7号塘0.45增至0.66，总增重1.08，平均增重约0.22。期间曾出现死鱼、亚硝酸盐严重超标，协助处理后当日见效，次日回访恢复正常。目前养殖情况稳定，持续跟进中。 【10.05走访秋溪尾基地、10.07走访大致坡基地，均测水做服务；两处均反馈喂料后水面有大片油膜，用户为1053专用料户；】 【10.07大致坡基地测水7口塘：2号、3号塘亚盐0.8超量程⚠️（鱼易浮头，重点处理）；1号、7号塘氨氮0.90偏高；4号、5号塘正常；6号塘氨氮0.50、亚盐0.20；油膜问题待核实塘口还是饲料原因】</t>
         </is>
       </c>
-      <c r="M5" s="4" t="inlineStr">
+      <c r="M5" t="inlineStr">
         <is>
           <t>尽快核实油膜原因（塘口/饲料）并闭环，给用户明确答复</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="2" t="n">
+      <c r="A6" t="n">
         <v>5</v>
       </c>
-      <c r="B6" s="2" t="inlineStr">
+      <c r="B6" t="inlineStr">
         <is>
           <t>陈守建</t>
         </is>
       </c>
-      <c r="C6" s="2" t="inlineStr">
+      <c r="C6" t="inlineStr">
         <is>
           <t>二、高意向客户</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr"/>
-      <c r="E6" s="2" t="n">
+      <c r="D6" t="inlineStr"/>
+      <c r="E6" t="n">
         <v>2</v>
       </c>
-      <c r="F6" s="2" t="inlineStr">
+      <c r="F6" t="inlineStr">
         <is>
           <t>30</t>
         </is>
       </c>
-      <c r="G6" s="3" t="inlineStr">
+      <c r="G6" t="inlineStr">
         <is>
           <t>通威、百洋</t>
         </is>
       </c>
-      <c r="H6" s="3" t="inlineStr">
+      <c r="H6" t="inlineStr">
         <is>
           <t>吴建龙</t>
         </is>
       </c>
-      <c r="I6" s="2" t="inlineStr"/>
-      <c r="J6" s="2" t="inlineStr"/>
-      <c r="K6" s="2" t="inlineStr"/>
-      <c r="L6" s="4" t="inlineStr">
+      <c r="I6" t="inlineStr"/>
+      <c r="J6" t="inlineStr"/>
+      <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr">
         <is>
           <t>养殖两口塘约30亩。用百洋，多次为其测水、检藻、推广动保产品。现跟吴建龙拿料，已确认10月起拉通威料，上一茬鱼已抓完，放苗后即转料。</t>
         </is>
       </c>
-      <c r="M6" s="4" t="inlineStr">
+      <c r="M6" t="inlineStr">
         <is>
           <t>重点跟进，尽快促成拉料</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="2" t="n">
+      <c r="A7" t="n">
         <v>6</v>
       </c>
-      <c r="B7" s="2" t="inlineStr">
+      <c r="B7" t="inlineStr">
         <is>
           <t>陈江乾</t>
         </is>
       </c>
-      <c r="C7" s="2" t="inlineStr">
+      <c r="C7" t="inlineStr">
         <is>
           <t>二、高意向客户</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr"/>
-      <c r="E7" s="2" t="inlineStr"/>
-      <c r="F7" s="2" t="inlineStr"/>
-      <c r="G7" s="3" t="inlineStr">
+      <c r="D7" t="inlineStr"/>
+      <c r="E7" t="inlineStr"/>
+      <c r="F7" t="inlineStr"/>
+      <c r="G7" t="inlineStr">
         <is>
           <t>混料</t>
         </is>
       </c>
-      <c r="H7" s="3" t="inlineStr"/>
-      <c r="I7" s="2" t="inlineStr"/>
-      <c r="J7" s="2" t="inlineStr"/>
-      <c r="K7" s="2" t="inlineStr"/>
-      <c r="L7" s="4" t="inlineStr">
+      <c r="H7" t="inlineStr"/>
+      <c r="I7" t="inlineStr"/>
+      <c r="J7" t="inlineStr"/>
+      <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr">
         <is>
           <t>混料，不拿通威，老板平时不在塘口。</t>
         </is>
       </c>
-      <c r="M7" s="4" t="inlineStr">
+      <c r="M7" t="inlineStr">
         <is>
           <t>重点跟进，尽快促成拉料</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="2" t="n">
+      <c r="A8" t="n">
         <v>7</v>
       </c>
-      <c r="B8" s="2" t="inlineStr">
+      <c r="B8" t="inlineStr">
         <is>
           <t>潘正雄</t>
         </is>
       </c>
-      <c r="C8" s="2" t="inlineStr">
+      <c r="C8" t="inlineStr">
         <is>
           <t>二、高意向客户</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr"/>
-      <c r="E8" s="2" t="inlineStr"/>
-      <c r="F8" s="2" t="inlineStr"/>
-      <c r="G8" s="3" t="inlineStr">
+      <c r="D8" t="inlineStr"/>
+      <c r="E8" t="inlineStr"/>
+      <c r="F8" t="inlineStr"/>
+      <c r="G8" t="inlineStr">
         <is>
           <t>祥泰</t>
         </is>
       </c>
-      <c r="H8" s="3" t="inlineStr"/>
-      <c r="I8" s="2" t="inlineStr"/>
-      <c r="J8" s="2" t="inlineStr"/>
-      <c r="K8" s="2" t="inlineStr"/>
-      <c r="L8" s="4" t="inlineStr">
+      <c r="H8" t="inlineStr"/>
+      <c r="I8" t="inlineStr"/>
+      <c r="J8" t="inlineStr"/>
+      <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr">
         <is>
           <t>祥泰现金料用户，曾到通威饲料厂参观，合作意向较好。</t>
         </is>
       </c>
-      <c r="M8" s="4" t="inlineStr">
+      <c r="M8" t="inlineStr">
         <is>
           <t>重点跟进，尽快促成拉料</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="2" t="n">
+      <c r="A9" t="n">
         <v>8</v>
       </c>
-      <c r="B9" s="2" t="inlineStr">
+      <c r="B9" t="inlineStr">
         <is>
           <t>王旭华</t>
         </is>
       </c>
-      <c r="C9" s="2" t="inlineStr">
+      <c r="C9" t="inlineStr">
         <is>
           <t>二、高意向客户</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr"/>
-      <c r="E9" s="2" t="inlineStr"/>
-      <c r="F9" s="2" t="inlineStr">
+      <c r="D9" t="inlineStr"/>
+      <c r="E9" t="inlineStr"/>
+      <c r="F9" t="inlineStr">
         <is>
           <t>30</t>
         </is>
       </c>
-      <c r="G9" s="3" t="inlineStr"/>
-      <c r="H9" s="3" t="inlineStr"/>
-      <c r="I9" s="2" t="inlineStr"/>
-      <c r="J9" s="2" t="inlineStr"/>
-      <c r="K9" s="2" t="inlineStr"/>
-      <c r="L9" s="4" t="inlineStr">
+      <c r="G9" t="inlineStr"/>
+      <c r="H9" t="inlineStr"/>
+      <c r="I9" t="inlineStr"/>
+      <c r="J9" t="inlineStr"/>
+      <c r="K9" t="inlineStr"/>
+      <c r="L9" t="inlineStr">
         <is>
           <t>30亩、密度2500尾每亩，上一茬已干塘，下一造有换料意向，已推荐通威小料。</t>
         </is>
       </c>
-      <c r="M9" s="4" t="inlineStr">
+      <c r="M9" t="inlineStr">
         <is>
           <t>重点跟进，尽快促成拉料</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="2" t="n">
+      <c r="A10" t="n">
         <v>9</v>
       </c>
-      <c r="B10" s="2" t="inlineStr">
+      <c r="B10" t="inlineStr">
         <is>
           <t>吴国平</t>
         </is>
       </c>
-      <c r="C10" s="2" t="inlineStr">
+      <c r="C10" t="inlineStr">
         <is>
           <t>二、高意向客户</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="D10" t="inlineStr">
         <is>
           <t>昌洒基地</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr"/>
-      <c r="F10" s="2" t="inlineStr">
+      <c r="E10" t="inlineStr"/>
+      <c r="F10" t="inlineStr">
         <is>
           <t>100多</t>
         </is>
       </c>
-      <c r="G10" s="3" t="inlineStr">
+      <c r="G10" t="inlineStr">
         <is>
           <t>海一、海大、鸿业</t>
         </is>
       </c>
-      <c r="H10" s="3" t="inlineStr"/>
-      <c r="I10" s="2" t="inlineStr">
+      <c r="H10" t="inlineStr"/>
+      <c r="I10" t="inlineStr">
         <is>
           <t>其儿子</t>
         </is>
       </c>
-      <c r="J10" s="2" t="inlineStr"/>
-      <c r="K10" s="2" t="inlineStr"/>
-      <c r="L10" s="4" t="inlineStr">
+      <c r="J10" t="inlineStr"/>
+      <c r="K10" t="inlineStr"/>
+      <c r="L10" t="inlineStr">
         <is>
           <t>100多亩大户，现用鸿业料加海大混料。昌洒基地由其儿子负责、约120亩，用海一料，有合作意向，重点跟进。</t>
         </is>
       </c>
-      <c r="M10" s="4" t="inlineStr">
+      <c r="M10" t="inlineStr">
         <is>
           <t>重点跟进，尽快促成拉料</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="2" t="n">
+      <c r="A11" t="n">
         <v>10</v>
       </c>
-      <c r="B11" s="2" t="inlineStr">
+      <c r="B11" t="inlineStr">
         <is>
           <t>绕成洁</t>
         </is>
       </c>
-      <c r="C11" s="2" t="inlineStr">
+      <c r="C11" t="inlineStr">
         <is>
           <t>二、高意向客户</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr"/>
-      <c r="E11" s="2" t="inlineStr"/>
-      <c r="F11" s="2" t="inlineStr"/>
-      <c r="G11" s="3" t="inlineStr">
+      <c r="D11" t="inlineStr"/>
+      <c r="E11" t="inlineStr"/>
+      <c r="F11" t="inlineStr"/>
+      <c r="G11" t="inlineStr">
         <is>
           <t>祥泰</t>
         </is>
       </c>
-      <c r="H11" s="3" t="inlineStr"/>
-      <c r="I11" s="2" t="inlineStr"/>
-      <c r="J11" s="2" t="inlineStr"/>
-      <c r="K11" s="2" t="inlineStr">
+      <c r="H11" t="inlineStr"/>
+      <c r="I11" t="inlineStr"/>
+      <c r="J11" t="inlineStr"/>
+      <c r="K11" t="inlineStr">
         <is>
           <t>40</t>
         </is>
       </c>
-      <c r="L11" s="4" t="inlineStr">
+      <c r="L11" t="inlineStr">
         <is>
           <t>祥泰用户，上一造产量约40、效果不佳，用料不固定，有推料机会。</t>
         </is>
       </c>
-      <c r="M11" s="4" t="inlineStr">
+      <c r="M11" t="inlineStr">
         <is>
           <t>重点跟进，尽快促成拉料</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="2" t="n">
+      <c r="A12" t="n">
         <v>11</v>
       </c>
-      <c r="B12" s="2" t="inlineStr">
+      <c r="B12" t="inlineStr">
         <is>
           <t>丁伟亮</t>
         </is>
       </c>
-      <c r="C12" s="2" t="inlineStr">
+      <c r="C12" t="inlineStr">
         <is>
           <t>二、高意向客户</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="D12" t="inlineStr">
         <is>
           <t>竹堆基地</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr"/>
-      <c r="F12" s="2" t="inlineStr"/>
-      <c r="G12" s="3" t="inlineStr">
+      <c r="E12" t="inlineStr"/>
+      <c r="F12" t="inlineStr"/>
+      <c r="G12" t="inlineStr">
         <is>
           <t>唐人神、桂美达</t>
         </is>
       </c>
-      <c r="H12" s="3" t="inlineStr"/>
-      <c r="I12" s="2" t="inlineStr"/>
-      <c r="J12" s="2" t="inlineStr">
+      <c r="H12" t="inlineStr"/>
+      <c r="I12" t="inlineStr"/>
+      <c r="J12" t="inlineStr">
         <is>
           <t>600包（已采购）</t>
         </is>
       </c>
-      <c r="K12" s="2" t="inlineStr"/>
-      <c r="L12" s="4" t="inlineStr">
+      <c r="K12" t="inlineStr"/>
+      <c r="L12" t="inlineStr">
         <is>
           <t>竹堆基地，部分塘口投喂唐人神、桂美达苗料，已采购600包9912，存鱼出塘收尾中。</t>
         </is>
       </c>
-      <c r="M12" s="4" t="inlineStr">
+      <c r="M12" t="inlineStr">
         <is>
           <t>重点跟进，尽快促成拉料</t>
         </is>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="2" t="n">
+      <c r="A13" t="n">
         <v>12</v>
       </c>
-      <c r="B13" s="2" t="inlineStr">
+      <c r="B13" t="inlineStr">
         <is>
           <t>丁字开</t>
         </is>
       </c>
-      <c r="C13" s="2" t="inlineStr">
+      <c r="C13" t="inlineStr">
         <is>
           <t>二、高意向客户</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr"/>
-      <c r="E13" s="2" t="inlineStr"/>
-      <c r="F13" s="2" t="inlineStr"/>
-      <c r="G13" s="3" t="inlineStr">
+      <c r="D13" t="inlineStr"/>
+      <c r="E13" t="inlineStr"/>
+      <c r="F13" t="inlineStr"/>
+      <c r="G13" t="inlineStr">
         <is>
           <t>通威、祥泰、海大</t>
         </is>
       </c>
-      <c r="H13" s="3" t="inlineStr"/>
-      <c r="I13" s="2" t="inlineStr"/>
-      <c r="J13" s="2" t="inlineStr"/>
-      <c r="K13" s="2" t="inlineStr">
+      <c r="H13" t="inlineStr"/>
+      <c r="I13" t="inlineStr"/>
+      <c r="J13" t="inlineStr"/>
+      <c r="K13" t="inlineStr">
         <is>
           <t>81</t>
         </is>
       </c>
-      <c r="L13" s="4" t="inlineStr">
+      <c r="L13" t="inlineStr">
         <is>
           <t>5号塘用祥泰、海大、通威混合料，打样报产81。苗塘准备分苗，已推荐小料，其有意将小孩塘口交给我们跟进。 【名字确认：与"丁字开"为同一人；10.05客情维护走访】 【10.08补充：其子丁世林塘口打样有涨——投料机塘0.6涨0.2，风送机塘0.7涨0.25（塘号未记）】</t>
         </is>
       </c>
-      <c r="M13" s="4" t="inlineStr">
+      <c r="M13" t="inlineStr">
         <is>
           <t>重点跟进，尽快促成拉料</t>
         </is>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="2" t="n">
+      <c r="A14" t="n">
         <v>13</v>
       </c>
-      <c r="B14" s="2" t="inlineStr">
+      <c r="B14" t="inlineStr">
         <is>
           <t>余中天</t>
         </is>
       </c>
-      <c r="C14" s="2" t="inlineStr">
+      <c r="C14" t="inlineStr">
         <is>
           <t>二、高意向客户</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr"/>
-      <c r="E14" s="2" t="inlineStr"/>
-      <c r="F14" s="2" t="inlineStr"/>
-      <c r="G14" s="3" t="inlineStr">
+      <c r="D14" t="inlineStr"/>
+      <c r="E14" t="inlineStr"/>
+      <c r="F14" t="inlineStr"/>
+      <c r="G14" t="inlineStr">
         <is>
           <t>百洋</t>
         </is>
       </c>
-      <c r="H14" s="3" t="inlineStr"/>
-      <c r="I14" s="2" t="inlineStr"/>
-      <c r="J14" s="2" t="inlineStr"/>
-      <c r="K14" s="2" t="inlineStr"/>
-      <c r="L14" s="4" t="inlineStr">
+      <c r="H14" t="inlineStr"/>
+      <c r="I14" t="inlineStr"/>
+      <c r="J14" t="inlineStr"/>
+      <c r="K14" t="inlineStr"/>
+      <c r="L14" t="inlineStr">
         <is>
           <t>百洋用户，存鱼七两左右。对价格政策敏感，表示有政策支持愿意用通威。</t>
         </is>
       </c>
-      <c r="M14" s="4" t="inlineStr">
+      <c r="M14" t="inlineStr">
         <is>
           <t>重点跟进，尽快促成拉料</t>
         </is>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="2" t="n">
+      <c r="A15" t="n">
         <v>14</v>
       </c>
-      <c r="B15" s="2" t="inlineStr">
+      <c r="B15" t="inlineStr">
         <is>
           <t>陶伟静</t>
         </is>
       </c>
-      <c r="C15" s="2" t="inlineStr">
+      <c r="C15" t="inlineStr">
         <is>
           <t>二、高意向客户</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr"/>
-      <c r="E15" s="2" t="inlineStr"/>
-      <c r="F15" s="2" t="inlineStr"/>
-      <c r="G15" s="3" t="inlineStr">
+      <c r="D15" t="inlineStr"/>
+      <c r="E15" t="inlineStr"/>
+      <c r="F15" t="inlineStr"/>
+      <c r="G15" t="inlineStr">
         <is>
           <t>海大2552</t>
         </is>
       </c>
-      <c r="H15" s="3" t="inlineStr">
+      <c r="H15" t="inlineStr">
         <is>
           <t>吴建龙</t>
         </is>
       </c>
-      <c r="I15" s="2" t="inlineStr"/>
-      <c r="J15" s="2" t="inlineStr"/>
-      <c r="K15" s="2" t="inlineStr"/>
-      <c r="L15" s="4" t="inlineStr">
+      <c r="I15" t="inlineStr"/>
+      <c r="J15" t="inlineStr"/>
+      <c r="K15" t="inlineStr"/>
+      <c r="L15" t="inlineStr">
         <is>
           <t>现用祥泰加海大，上半年用过通威，反馈效果可以。 【10.07走访，以客情维护为主：现用海大2552，跟吴建龙拿料；产量不太高，反感业务员问这问那；评估有转化机会】</t>
         </is>
       </c>
-      <c r="M15" s="4" t="inlineStr">
+      <c r="M15" t="inlineStr">
         <is>
           <t>有转化机会：多做服务少追问，靠实在帮助培养信任，持续客情跟进</t>
         </is>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="2" t="n">
+      <c r="A16" t="n">
         <v>15</v>
       </c>
-      <c r="B16" s="2" t="inlineStr">
+      <c r="B16" t="inlineStr">
         <is>
           <t>王建国</t>
         </is>
       </c>
-      <c r="C16" s="2" t="inlineStr">
+      <c r="C16" t="inlineStr">
         <is>
           <t>二、高意向客户</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr"/>
-      <c r="E16" s="2" t="inlineStr"/>
-      <c r="F16" s="2" t="inlineStr"/>
-      <c r="G16" s="3" t="inlineStr">
+      <c r="D16" t="inlineStr"/>
+      <c r="E16" t="inlineStr"/>
+      <c r="F16" t="inlineStr"/>
+      <c r="G16" t="inlineStr">
         <is>
           <t>百洋</t>
         </is>
       </c>
-      <c r="H16" s="3" t="inlineStr"/>
-      <c r="I16" s="2" t="inlineStr"/>
-      <c r="J16" s="2" t="inlineStr"/>
-      <c r="K16" s="2" t="inlineStr"/>
-      <c r="L16" s="4" t="inlineStr">
+      <c r="H16" t="inlineStr"/>
+      <c r="I16" t="inlineStr"/>
+      <c r="J16" t="inlineStr"/>
+      <c r="K16" t="inlineStr"/>
+      <c r="L16" t="inlineStr">
         <is>
           <t>百洋用户，有动保产品需求，可先从动保切入。</t>
         </is>
       </c>
-      <c r="M16" s="4" t="inlineStr">
+      <c r="M16" t="inlineStr">
         <is>
           <t>重点跟进，尽快促成拉料</t>
         </is>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="2" t="n">
+      <c r="A17" t="n">
         <v>16</v>
       </c>
-      <c r="B17" s="2" t="inlineStr">
+      <c r="B17" t="inlineStr">
         <is>
           <t>李兆松</t>
         </is>
       </c>
-      <c r="C17" s="2" t="inlineStr">
-        <is>
-          <t>三、潜力培育中</t>
-        </is>
-      </c>
-      <c r="D17" s="2" t="inlineStr"/>
-      <c r="E17" s="2" t="inlineStr"/>
-      <c r="F17" s="2" t="inlineStr"/>
-      <c r="G17" s="3" t="inlineStr">
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>三、潜力培育中</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr"/>
+      <c r="E17" t="inlineStr"/>
+      <c r="F17" t="inlineStr"/>
+      <c r="G17" t="inlineStr">
         <is>
           <t>祥泰</t>
         </is>
       </c>
-      <c r="H17" s="3" t="inlineStr">
+      <c r="H17" t="inlineStr">
         <is>
           <t>田永均</t>
         </is>
       </c>
-      <c r="I17" s="2" t="inlineStr"/>
-      <c r="J17" s="2" t="inlineStr"/>
-      <c r="K17" s="2" t="inlineStr"/>
-      <c r="L17" s="4" t="inlineStr">
+      <c r="I17" t="inlineStr"/>
+      <c r="J17" t="inlineStr"/>
+      <c r="K17" t="inlineStr"/>
+      <c r="L17" t="inlineStr">
         <is>
           <t>祥泰老用户，养二两鱼、罗非黄骨混养塘。长期为其做服务：测水、补网、培育光合菌，亚盐偏高时协助处理。鱼已抓完，下一造继续跟进。</t>
         </is>
       </c>
-      <c r="M17" s="4" t="inlineStr">
+      <c r="M17" t="inlineStr">
         <is>
           <t>持续服务培育，寻找切入时机</t>
         </is>
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="2" t="n">
+      <c r="A18" t="n">
         <v>17</v>
       </c>
-      <c r="B18" s="2" t="inlineStr">
+      <c r="B18" t="inlineStr">
         <is>
           <t>杨献东</t>
         </is>
       </c>
-      <c r="C18" s="2" t="inlineStr">
-        <is>
-          <t>三、潜力培育中</t>
-        </is>
-      </c>
-      <c r="D18" s="2" t="inlineStr"/>
-      <c r="E18" s="2" t="inlineStr"/>
-      <c r="F18" s="2" t="inlineStr"/>
-      <c r="G18" s="3" t="inlineStr">
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>三、潜力培育中</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr"/>
+      <c r="E18" t="inlineStr"/>
+      <c r="F18" t="inlineStr"/>
+      <c r="G18" t="inlineStr">
         <is>
           <t>百洋、祥泰</t>
         </is>
       </c>
-      <c r="H18" s="3" t="inlineStr"/>
-      <c r="I18" s="2" t="inlineStr"/>
-      <c r="J18" s="2" t="inlineStr"/>
-      <c r="K18" s="2" t="inlineStr"/>
-      <c r="L18" s="4" t="inlineStr">
+      <c r="H18" t="inlineStr"/>
+      <c r="I18" t="inlineStr"/>
+      <c r="J18" t="inlineStr"/>
+      <c r="K18" t="inlineStr"/>
+      <c r="L18" t="inlineStr">
         <is>
           <t>用百洋、祥泰等饲料。对通威印象很好，多次走访沟通。</t>
         </is>
       </c>
-      <c r="M18" s="4" t="inlineStr">
+      <c r="M18" t="inlineStr">
         <is>
           <t>持续服务培育，寻找切入时机</t>
         </is>
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="2" t="n">
+      <c r="A19" t="n">
         <v>18</v>
       </c>
-      <c r="B19" s="2" t="inlineStr">
+      <c r="B19" t="inlineStr">
         <is>
           <t>张水龙</t>
         </is>
       </c>
-      <c r="C19" s="2" t="inlineStr">
-        <is>
-          <t>三、潜力培育中</t>
-        </is>
-      </c>
-      <c r="D19" s="2" t="inlineStr"/>
-      <c r="E19" s="2" t="inlineStr"/>
-      <c r="F19" s="2" t="inlineStr"/>
-      <c r="G19" s="3" t="inlineStr"/>
-      <c r="H19" s="3" t="inlineStr"/>
-      <c r="I19" s="2" t="inlineStr"/>
-      <c r="J19" s="2" t="inlineStr"/>
-      <c r="K19" s="2" t="inlineStr"/>
-      <c r="L19" s="4" t="inlineStr">
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>三、潜力培育中</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr"/>
+      <c r="E19" t="inlineStr"/>
+      <c r="F19" t="inlineStr"/>
+      <c r="G19" t="inlineStr"/>
+      <c r="H19" t="inlineStr"/>
+      <c r="I19" t="inlineStr"/>
+      <c r="J19" t="inlineStr"/>
+      <c r="K19" t="inlineStr"/>
+      <c r="L19" t="inlineStr">
         <is>
           <t>电话联系测水打样，鱼七两左右、肥满度好。</t>
         </is>
       </c>
-      <c r="M19" s="4" t="inlineStr">
+      <c r="M19" t="inlineStr">
         <is>
           <t>持续服务培育，寻找切入时机</t>
         </is>
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="2" t="n">
+      <c r="A20" t="n">
         <v>19</v>
       </c>
-      <c r="B20" s="2" t="inlineStr">
+      <c r="B20" t="inlineStr">
         <is>
           <t>丁立强</t>
         </is>
       </c>
-      <c r="C20" s="2" t="inlineStr">
-        <is>
-          <t>三、潜力培育中</t>
-        </is>
-      </c>
-      <c r="D20" s="2" t="inlineStr"/>
-      <c r="E20" s="2" t="inlineStr"/>
-      <c r="F20" s="2" t="inlineStr"/>
-      <c r="G20" s="3" t="inlineStr"/>
-      <c r="H20" s="3" t="inlineStr"/>
-      <c r="I20" s="2" t="inlineStr"/>
-      <c r="J20" s="2" t="inlineStr"/>
-      <c r="K20" s="2" t="inlineStr"/>
-      <c r="L20" s="4" t="inlineStr">
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>三、潜力培育中</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr"/>
+      <c r="E20" t="inlineStr"/>
+      <c r="F20" t="inlineStr"/>
+      <c r="G20" t="inlineStr"/>
+      <c r="H20" t="inlineStr"/>
+      <c r="I20" t="inlineStr"/>
+      <c r="J20" t="inlineStr"/>
+      <c r="K20" t="inlineStr"/>
+      <c r="L20" t="inlineStr">
         <is>
           <t>有建设光合菌扩培系统的需求。使用我司动保产品后持续跟踪效果，打样鱼五两左右。</t>
         </is>
       </c>
-      <c r="M20" s="4" t="inlineStr">
+      <c r="M20" t="inlineStr">
         <is>
           <t>持续服务培育，寻找切入时机</t>
         </is>
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="2" t="n">
+      <c r="A21" t="n">
         <v>20</v>
       </c>
-      <c r="B21" s="2" t="inlineStr">
+      <c r="B21" t="inlineStr">
         <is>
           <t>丁敏强</t>
         </is>
       </c>
-      <c r="C21" s="2" t="inlineStr">
-        <is>
-          <t>三、潜力培育中</t>
-        </is>
-      </c>
-      <c r="D21" s="2" t="inlineStr"/>
-      <c r="E21" s="2" t="inlineStr"/>
-      <c r="F21" s="2" t="inlineStr"/>
-      <c r="G21" s="3" t="inlineStr"/>
-      <c r="H21" s="3" t="inlineStr"/>
-      <c r="I21" s="2" t="inlineStr"/>
-      <c r="J21" s="2" t="inlineStr"/>
-      <c r="K21" s="2" t="inlineStr"/>
-      <c r="L21" s="4" t="inlineStr">
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>三、潜力培育中</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr"/>
+      <c r="E21" t="inlineStr"/>
+      <c r="F21" t="inlineStr"/>
+      <c r="G21" t="inlineStr"/>
+      <c r="H21" t="inlineStr"/>
+      <c r="I21" t="inlineStr"/>
+      <c r="J21" t="inlineStr"/>
+      <c r="K21" t="inlineStr"/>
+      <c r="L21" t="inlineStr">
         <is>
           <t>鱼苗塘和3号塘亚盐偏高。小塘已抓鱼三万斤，大塘十月抓。 【10.05走访，用户暂不需要测水服务，择日再访】</t>
         </is>
       </c>
-      <c r="M21" s="4" t="inlineStr">
+      <c r="M21" t="inlineStr">
         <is>
           <t>持续服务培育，寻找切入时机</t>
         </is>
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="2" t="n">
+      <c r="A22" t="n">
         <v>21</v>
       </c>
-      <c r="B22" s="2" t="inlineStr">
+      <c r="B22" t="inlineStr">
         <is>
           <t>施睿钟</t>
         </is>
       </c>
-      <c r="C22" s="2" t="inlineStr">
-        <is>
-          <t>三、潜力培育中</t>
-        </is>
-      </c>
-      <c r="D22" s="2" t="inlineStr"/>
-      <c r="E22" s="2" t="inlineStr"/>
-      <c r="F22" s="2" t="inlineStr"/>
-      <c r="G22" s="3" t="inlineStr"/>
-      <c r="H22" s="3" t="inlineStr"/>
-      <c r="I22" s="2" t="inlineStr"/>
-      <c r="J22" s="2" t="inlineStr"/>
-      <c r="K22" s="2" t="inlineStr"/>
-      <c r="L22" s="4" t="inlineStr">
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>三、潜力培育中</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr"/>
+      <c r="E22" t="inlineStr"/>
+      <c r="F22" t="inlineStr"/>
+      <c r="G22" t="inlineStr"/>
+      <c r="H22" t="inlineStr"/>
+      <c r="I22" t="inlineStr"/>
+      <c r="J22" t="inlineStr"/>
+      <c r="K22" t="inlineStr"/>
+      <c r="L22" t="inlineStr">
         <is>
           <t>试用过一车通威料，现跟随周公宝用料。鱼已出塘。</t>
         </is>
       </c>
-      <c r="M22" s="4" t="inlineStr">
+      <c r="M22" t="inlineStr">
         <is>
           <t>持续服务培育，寻找切入时机</t>
         </is>
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="2" t="n">
+      <c r="A23" t="n">
         <v>22</v>
       </c>
-      <c r="B23" s="2" t="inlineStr">
+      <c r="B23" t="inlineStr">
         <is>
           <t>宋平</t>
         </is>
       </c>
-      <c r="C23" s="2" t="inlineStr">
-        <is>
-          <t>三、潜力培育中</t>
-        </is>
-      </c>
-      <c r="D23" s="2" t="inlineStr"/>
-      <c r="E23" s="2" t="n">
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>三、潜力培育中</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr"/>
+      <c r="E23" t="n">
         <v>7</v>
       </c>
-      <c r="F23" s="2" t="inlineStr"/>
-      <c r="G23" s="3" t="inlineStr">
+      <c r="F23" t="inlineStr"/>
+      <c r="G23" t="inlineStr">
         <is>
           <t>海大2552、混渝泰/粤海</t>
         </is>
       </c>
-      <c r="H23" s="3" t="inlineStr">
+      <c r="H23" t="inlineStr">
         <is>
           <t>周公宝</t>
         </is>
       </c>
-      <c r="I23" s="2" t="inlineStr"/>
-      <c r="J23" s="2" t="inlineStr"/>
-      <c r="K23" s="2" t="inlineStr"/>
-      <c r="L23" s="4" t="inlineStr">
+      <c r="I23" t="inlineStr"/>
+      <c r="J23" t="inlineStr"/>
+      <c r="K23" t="inlineStr"/>
+      <c r="L23" t="inlineStr">
         <is>
           <t>七口塘，计划安装料塔，对通威认可度较高；老婆湖南人（同乡圈）；主用海大2552、偶尔混渝泰、粤海；跟周公宝拿料；主动问价，转化机会明确。与唐行平（湖南老乡）互相认识，可借同乡关系交叉跟进。10.10客情走访。</t>
         </is>
       </c>
-      <c r="M23" s="4" t="inlineStr">
+      <c r="M23" t="inlineStr">
         <is>
           <t>趁其主动询价推通威小料/开口乐报价；借同乡关系（唐行平）交叉跟进。</t>
         </is>
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="2" t="n">
+      <c r="A24" t="n">
         <v>23</v>
       </c>
-      <c r="B24" s="2" t="inlineStr">
+      <c r="B24" t="inlineStr">
         <is>
           <t>曾古贤</t>
         </is>
       </c>
-      <c r="C24" s="2" t="inlineStr">
-        <is>
-          <t>三、潜力培育中</t>
-        </is>
-      </c>
-      <c r="D24" s="2" t="inlineStr"/>
-      <c r="E24" s="2" t="inlineStr"/>
-      <c r="F24" s="2" t="inlineStr"/>
-      <c r="G24" s="3" t="inlineStr"/>
-      <c r="H24" s="3" t="inlineStr"/>
-      <c r="I24" s="2" t="inlineStr"/>
-      <c r="J24" s="2" t="inlineStr"/>
-      <c r="K24" s="2" t="inlineStr"/>
-      <c r="L24" s="4" t="inlineStr">
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>三、潜力培育中</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr"/>
+      <c r="E24" t="inlineStr"/>
+      <c r="F24" t="inlineStr"/>
+      <c r="G24" t="inlineStr"/>
+      <c r="H24" t="inlineStr"/>
+      <c r="I24" t="inlineStr"/>
+      <c r="J24" t="inlineStr"/>
+      <c r="K24" t="inlineStr"/>
+      <c r="L24" t="inlineStr">
         <is>
           <t>多次交谈，对通威印象逐步好转，推进料塔推荐。</t>
         </is>
       </c>
-      <c r="M24" s="4" t="inlineStr">
+      <c r="M24" t="inlineStr">
         <is>
           <t>持续服务培育，寻找切入时机</t>
         </is>
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="2" t="n">
+      <c r="A25" t="n">
         <v>24</v>
       </c>
-      <c r="B25" s="2" t="inlineStr">
+      <c r="B25" t="inlineStr">
         <is>
           <t>丁伟峰</t>
         </is>
       </c>
-      <c r="C25" s="2" t="inlineStr">
-        <is>
-          <t>三、潜力培育中</t>
-        </is>
-      </c>
-      <c r="D25" s="2" t="inlineStr"/>
-      <c r="E25" s="2" t="inlineStr"/>
-      <c r="F25" s="2" t="inlineStr"/>
-      <c r="G25" s="3" t="inlineStr"/>
-      <c r="H25" s="3" t="inlineStr"/>
-      <c r="I25" s="2" t="inlineStr"/>
-      <c r="J25" s="2" t="inlineStr"/>
-      <c r="K25" s="2" t="inlineStr"/>
-      <c r="L25" s="4" t="inlineStr">
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>三、潜力培育中</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr"/>
+      <c r="E25" t="inlineStr"/>
+      <c r="F25" t="inlineStr"/>
+      <c r="G25" t="inlineStr"/>
+      <c r="H25" t="inlineStr"/>
+      <c r="I25" t="inlineStr"/>
+      <c r="J25" t="inlineStr"/>
+      <c r="K25" t="inlineStr"/>
+      <c r="L25" t="inlineStr">
         <is>
           <t>对光合菌培养感兴趣，已交流培养经验。</t>
         </is>
       </c>
-      <c r="M25" s="4" t="inlineStr">
+      <c r="M25" t="inlineStr">
         <is>
           <t>持续服务培育，寻找切入时机</t>
         </is>
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="2" t="n">
+      <c r="A26" t="n">
         <v>25</v>
       </c>
-      <c r="B26" s="2" t="inlineStr">
+      <c r="B26" t="inlineStr">
         <is>
           <t>韩海山</t>
         </is>
       </c>
-      <c r="C26" s="2" t="inlineStr">
-        <is>
-          <t>三、潜力培育中</t>
-        </is>
-      </c>
-      <c r="D26" s="2" t="inlineStr">
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>三、潜力培育中</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
         <is>
           <t>另一基地</t>
         </is>
       </c>
-      <c r="E26" s="2" t="inlineStr"/>
-      <c r="F26" s="2" t="inlineStr"/>
-      <c r="G26" s="3" t="inlineStr"/>
-      <c r="H26" s="3" t="inlineStr"/>
-      <c r="I26" s="2" t="inlineStr"/>
-      <c r="J26" s="2" t="inlineStr"/>
-      <c r="K26" s="2" t="inlineStr"/>
-      <c r="L26" s="4" t="inlineStr">
+      <c r="E26" t="inlineStr"/>
+      <c r="F26" t="inlineStr"/>
+      <c r="G26" t="inlineStr"/>
+      <c r="H26" t="inlineStr"/>
+      <c r="I26" t="inlineStr"/>
+      <c r="J26" t="inlineStr"/>
+      <c r="K26" t="inlineStr"/>
+      <c r="L26" t="inlineStr">
         <is>
           <t>用150型号小料，另一基地分苗后密度5000每亩。</t>
         </is>
       </c>
-      <c r="M26" s="4" t="inlineStr">
+      <c r="M26" t="inlineStr">
         <is>
           <t>持续服务培育，寻找切入时机</t>
         </is>
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="2" t="n">
+      <c r="A27" t="n">
         <v>26</v>
       </c>
-      <c r="B27" s="2" t="inlineStr">
+      <c r="B27" t="inlineStr">
         <is>
           <t>朱文勇</t>
         </is>
       </c>
-      <c r="C27" s="2" t="inlineStr">
-        <is>
-          <t>三、潜力培育中</t>
-        </is>
-      </c>
-      <c r="D27" s="2" t="inlineStr"/>
-      <c r="E27" s="2" t="inlineStr"/>
-      <c r="F27" s="2" t="inlineStr"/>
-      <c r="G27" s="3" t="inlineStr">
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>三、潜力培育中</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr"/>
+      <c r="E27" t="inlineStr"/>
+      <c r="F27" t="inlineStr"/>
+      <c r="G27" t="inlineStr">
         <is>
           <t>祥泰</t>
         </is>
       </c>
-      <c r="H27" s="3" t="inlineStr"/>
-      <c r="I27" s="2" t="inlineStr"/>
-      <c r="J27" s="2" t="inlineStr"/>
-      <c r="K27" s="2" t="inlineStr"/>
-      <c r="L27" s="4" t="inlineStr">
+      <c r="H27" t="inlineStr"/>
+      <c r="I27" t="inlineStr"/>
+      <c r="J27" t="inlineStr"/>
+      <c r="K27" t="inlineStr"/>
+      <c r="L27" t="inlineStr">
         <is>
           <t>祥泰混料，四五两鱼，预计十月中抓鱼。</t>
         </is>
       </c>
-      <c r="M27" s="4" t="inlineStr">
+      <c r="M27" t="inlineStr">
         <is>
           <t>持续服务培育，寻找切入时机</t>
         </is>
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="2" t="n">
+      <c r="A28" t="n">
         <v>27</v>
       </c>
-      <c r="B28" s="2" t="inlineStr">
+      <c r="B28" t="inlineStr">
         <is>
           <t>王国富</t>
         </is>
       </c>
-      <c r="C28" s="2" t="inlineStr">
-        <is>
-          <t>三、潜力培育中</t>
-        </is>
-      </c>
-      <c r="D28" s="2" t="inlineStr"/>
-      <c r="E28" s="2" t="inlineStr"/>
-      <c r="F28" s="2" t="inlineStr"/>
-      <c r="G28" s="3" t="inlineStr">
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>三、潜力培育中</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr"/>
+      <c r="E28" t="inlineStr"/>
+      <c r="F28" t="inlineStr"/>
+      <c r="G28" t="inlineStr">
         <is>
           <t>海大、添祥</t>
         </is>
       </c>
-      <c r="H28" s="3" t="inlineStr"/>
-      <c r="I28" s="2" t="inlineStr"/>
-      <c r="J28" s="2" t="inlineStr"/>
-      <c r="K28" s="2" t="inlineStr"/>
-      <c r="L28" s="4" t="inlineStr">
+      <c r="H28" t="inlineStr"/>
+      <c r="I28" t="inlineStr"/>
+      <c r="J28" t="inlineStr"/>
+      <c r="K28" t="inlineStr"/>
+      <c r="L28" t="inlineStr">
         <is>
           <t>添祥小料加海大混用，鱼七八两，宝路标苗八九成。</t>
         </is>
       </c>
-      <c r="M28" s="4" t="inlineStr">
+      <c r="M28" t="inlineStr">
         <is>
           <t>持续服务培育，寻找切入时机</t>
         </is>
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="2" t="n">
+      <c r="A29" t="n">
         <v>28</v>
       </c>
-      <c r="B29" s="2" t="inlineStr">
+      <c r="B29" t="inlineStr">
         <is>
           <t>傅厚熠</t>
         </is>
       </c>
-      <c r="C29" s="2" t="inlineStr">
-        <is>
-          <t>三、潜力培育中</t>
-        </is>
-      </c>
-      <c r="D29" s="2" t="inlineStr"/>
-      <c r="E29" s="2" t="n">
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>三、潜力培育中</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr"/>
+      <c r="E29" t="n">
         <v>4</v>
       </c>
-      <c r="F29" s="2" t="inlineStr"/>
-      <c r="G29" s="3" t="inlineStr">
+      <c r="F29" t="inlineStr"/>
+      <c r="G29" t="inlineStr">
         <is>
           <t>海大</t>
         </is>
       </c>
-      <c r="H29" s="3" t="inlineStr"/>
-      <c r="I29" s="2" t="inlineStr"/>
-      <c r="J29" s="2" t="inlineStr"/>
-      <c r="K29" s="2" t="inlineStr"/>
-      <c r="L29" s="4" t="inlineStr">
+      <c r="H29" t="inlineStr"/>
+      <c r="I29" t="inlineStr"/>
+      <c r="J29" t="inlineStr"/>
+      <c r="K29" t="inlineStr"/>
+      <c r="L29" t="inlineStr">
         <is>
           <t>海大用户，四口塘三口在养，成鱼塘五两。</t>
         </is>
       </c>
-      <c r="M29" s="4" t="inlineStr">
+      <c r="M29" t="inlineStr">
         <is>
           <t>持续服务培育，寻找切入时机</t>
         </is>
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="2" t="n">
+      <c r="A30" t="n">
         <v>29</v>
       </c>
-      <c r="B30" s="2" t="inlineStr">
+      <c r="B30" t="inlineStr">
         <is>
           <t>丁世林</t>
         </is>
       </c>
-      <c r="C30" s="2" t="inlineStr">
-        <is>
-          <t>三、潜力培育中</t>
-        </is>
-      </c>
-      <c r="D30" s="2" t="inlineStr"/>
-      <c r="E30" s="2" t="inlineStr"/>
-      <c r="F30" s="2" t="inlineStr"/>
-      <c r="G30" s="3" t="inlineStr">
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>三、潜力培育中</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr"/>
+      <c r="E30" t="inlineStr"/>
+      <c r="F30" t="inlineStr"/>
+      <c r="G30" t="inlineStr">
         <is>
           <t>祥泰</t>
         </is>
       </c>
-      <c r="H30" s="3" t="inlineStr"/>
-      <c r="I30" s="2" t="inlineStr"/>
-      <c r="J30" s="2" t="inlineStr"/>
-      <c r="K30" s="2" t="inlineStr">
+      <c r="H30" t="inlineStr"/>
+      <c r="I30" t="inlineStr"/>
+      <c r="J30" t="inlineStr"/>
+      <c r="K30" t="inlineStr">
         <is>
           <t>65</t>
         </is>
       </c>
-      <c r="L30" s="4" t="inlineStr">
+      <c r="L30" t="inlineStr">
         <is>
           <t>祥泰用户，预估包产65，反馈现用饲料包重偏轻。 【10.08走访维护客情：丁世林为丁字开之子；打样——投料机塘0.6上涨0.2，风送机塘0.7上涨0.25（塘号未记）（风送可能之前打样偏小）】</t>
         </is>
       </c>
-      <c r="M30" s="4" t="inlineStr">
+      <c r="M30" t="inlineStr">
         <is>
           <t>持续服务培育，寻找切入时机</t>
         </is>
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="2" t="n">
+      <c r="A31" t="n">
         <v>30</v>
       </c>
-      <c r="B31" s="2" t="inlineStr">
+      <c r="B31" t="inlineStr">
         <is>
           <t>朱建伟</t>
         </is>
       </c>
-      <c r="C31" s="2" t="inlineStr">
-        <is>
-          <t>三、潜力培育中</t>
-        </is>
-      </c>
-      <c r="D31" s="2" t="inlineStr"/>
-      <c r="E31" s="2" t="inlineStr"/>
-      <c r="F31" s="2" t="inlineStr"/>
-      <c r="G31" s="3" t="inlineStr">
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>三、潜力培育中</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr"/>
+      <c r="E31" t="inlineStr"/>
+      <c r="F31" t="inlineStr"/>
+      <c r="G31" t="inlineStr">
         <is>
           <t>鸿业</t>
         </is>
       </c>
-      <c r="H31" s="3" t="inlineStr">
+      <c r="H31" t="inlineStr">
         <is>
           <t>周公宝</t>
         </is>
       </c>
-      <c r="I31" s="2" t="inlineStr"/>
-      <c r="J31" s="2" t="inlineStr"/>
-      <c r="K31" s="2" t="inlineStr"/>
-      <c r="L31" s="4" t="inlineStr">
+      <c r="I31" t="inlineStr"/>
+      <c r="J31" t="inlineStr"/>
+      <c r="K31" t="inlineStr"/>
+      <c r="L31" t="inlineStr">
         <is>
           <t>鸿业用户，养殖周期长，欲安装料塔，现跟周公宝拿料。</t>
         </is>
       </c>
-      <c r="M31" s="4" t="inlineStr">
+      <c r="M31" t="inlineStr">
         <is>
           <t>持续服务培育，寻找切入时机</t>
         </is>
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="2" t="n">
+      <c r="A32" t="n">
         <v>31</v>
       </c>
-      <c r="B32" s="2" t="inlineStr">
+      <c r="B32" t="inlineStr">
         <is>
           <t>徐再苏</t>
         </is>
       </c>
-      <c r="C32" s="2" t="inlineStr">
-        <is>
-          <t>三、潜力培育中</t>
-        </is>
-      </c>
-      <c r="D32" s="2" t="inlineStr"/>
-      <c r="E32" s="2" t="inlineStr"/>
-      <c r="F32" s="2" t="inlineStr"/>
-      <c r="G32" s="3" t="inlineStr"/>
-      <c r="H32" s="3" t="inlineStr"/>
-      <c r="I32" s="2" t="inlineStr"/>
-      <c r="J32" s="2" t="inlineStr"/>
-      <c r="K32" s="2" t="inlineStr"/>
-      <c r="L32" s="4" t="inlineStr">
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>三、潜力培育中</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr"/>
+      <c r="E32" t="inlineStr"/>
+      <c r="F32" t="inlineStr"/>
+      <c r="G32" t="inlineStr"/>
+      <c r="H32" t="inlineStr"/>
+      <c r="I32" t="inlineStr"/>
+      <c r="J32" t="inlineStr"/>
+      <c r="K32" t="inlineStr"/>
+      <c r="L32" t="inlineStr">
         <is>
           <t>打样1.3斤成鱼，预计十月一出鱼。</t>
         </is>
       </c>
-      <c r="M32" s="4" t="inlineStr">
+      <c r="M32" t="inlineStr">
         <is>
           <t>持续服务培育，寻找切入时机</t>
         </is>
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="2" t="n">
+      <c r="A33" t="n">
         <v>32</v>
       </c>
-      <c r="B33" s="2" t="inlineStr">
+      <c r="B33" t="inlineStr">
         <is>
           <t>何老板</t>
         </is>
       </c>
-      <c r="C33" s="2" t="inlineStr">
-        <is>
-          <t>三、潜力培育中</t>
-        </is>
-      </c>
-      <c r="D33" s="2" t="inlineStr"/>
-      <c r="E33" s="2" t="inlineStr"/>
-      <c r="F33" s="2" t="inlineStr"/>
-      <c r="G33" s="3" t="inlineStr">
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>三、潜力培育中</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr"/>
+      <c r="E33" t="inlineStr"/>
+      <c r="F33" t="inlineStr"/>
+      <c r="G33" t="inlineStr">
         <is>
           <t>海大、歌颂</t>
         </is>
       </c>
-      <c r="H33" s="3" t="inlineStr">
+      <c r="H33" t="inlineStr">
         <is>
           <t>何经理</t>
         </is>
       </c>
-      <c r="I33" s="2" t="inlineStr"/>
-      <c r="J33" s="2" t="inlineStr"/>
-      <c r="K33" s="2" t="inlineStr"/>
-      <c r="L33" s="4" t="inlineStr">
+      <c r="I33" t="inlineStr"/>
+      <c r="J33" t="inlineStr"/>
+      <c r="K33" t="inlineStr"/>
+      <c r="L33" t="inlineStr">
         <is>
           <t>跟何经理拿料，用歌颂加海大，存塘鱼3两、2000尾每亩，未用过通威。</t>
         </is>
       </c>
-      <c r="M33" s="4" t="inlineStr">
+      <c r="M33" t="inlineStr">
         <is>
           <t>持续服务培育，寻找切入时机</t>
         </is>
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="2" t="n">
+      <c r="A34" t="n">
         <v>33</v>
       </c>
-      <c r="B34" s="2" t="inlineStr">
+      <c r="B34" t="inlineStr">
         <is>
           <t>杨振威</t>
         </is>
       </c>
-      <c r="C34" s="2" t="inlineStr">
-        <is>
-          <t>三、潜力培育中</t>
-        </is>
-      </c>
-      <c r="D34" s="2" t="inlineStr"/>
-      <c r="E34" s="2" t="inlineStr"/>
-      <c r="F34" s="2" t="inlineStr"/>
-      <c r="G34" s="3" t="inlineStr">
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>三、潜力培育中</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr"/>
+      <c r="E34" t="inlineStr"/>
+      <c r="F34" t="inlineStr"/>
+      <c r="G34" t="inlineStr">
         <is>
           <t>百洋</t>
         </is>
       </c>
-      <c r="H34" s="3" t="inlineStr"/>
-      <c r="I34" s="2" t="inlineStr"/>
-      <c r="J34" s="2" t="inlineStr"/>
-      <c r="K34" s="2" t="inlineStr"/>
-      <c r="L34" s="4" t="inlineStr">
+      <c r="H34" t="inlineStr"/>
+      <c r="I34" t="inlineStr"/>
+      <c r="J34" t="inlineStr"/>
+      <c r="K34" t="inlineStr"/>
+      <c r="L34" t="inlineStr">
         <is>
           <t>走访取样百洋三号料。</t>
         </is>
       </c>
-      <c r="M34" s="4" t="inlineStr">
+      <c r="M34" t="inlineStr">
         <is>
           <t>持续服务培育，寻找切入时机</t>
         </is>
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="2" t="n">
+      <c r="A35" t="n">
         <v>34</v>
       </c>
-      <c r="B35" s="2" t="inlineStr">
+      <c r="B35" t="inlineStr">
         <is>
           <t>李峰伟</t>
         </is>
       </c>
-      <c r="C35" s="2" t="inlineStr">
-        <is>
-          <t>三、潜力培育中</t>
-        </is>
-      </c>
-      <c r="D35" s="2" t="inlineStr">
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>三、潜力培育中</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
         <is>
           <t>水铁基地</t>
         </is>
       </c>
-      <c r="E35" s="2" t="inlineStr"/>
-      <c r="F35" s="2" t="inlineStr"/>
-      <c r="G35" s="3" t="inlineStr">
+      <c r="E35" t="inlineStr"/>
+      <c r="F35" t="inlineStr"/>
+      <c r="G35" t="inlineStr">
         <is>
           <t>海大2552</t>
         </is>
       </c>
-      <c r="H35" s="3" t="inlineStr"/>
-      <c r="I35" s="2" t="inlineStr"/>
-      <c r="J35" s="2" t="inlineStr"/>
-      <c r="K35" s="2" t="inlineStr"/>
-      <c r="L35" s="4" t="inlineStr">
+      <c r="H35" t="inlineStr"/>
+      <c r="I35" t="inlineStr"/>
+      <c r="J35" t="inlineStr"/>
+      <c r="K35" t="inlineStr"/>
+      <c r="L35" t="inlineStr">
         <is>
           <t>水铁基地，海大2552，存鱼7至8两，预计两个月后出鱼。</t>
         </is>
       </c>
-      <c r="M35" s="4" t="inlineStr">
+      <c r="M35" t="inlineStr">
         <is>
           <t>持续服务培育，寻找切入时机</t>
         </is>
       </c>
     </row>
     <row r="36">
-      <c r="A36" s="2" t="n">
+      <c r="A36" t="n">
         <v>35</v>
       </c>
-      <c r="B36" s="2" t="inlineStr">
+      <c r="B36" t="inlineStr">
         <is>
           <t>蒋建峰</t>
         </is>
       </c>
-      <c r="C36" s="2" t="inlineStr">
-        <is>
-          <t>三、潜力培育中</t>
-        </is>
-      </c>
-      <c r="D36" s="2" t="inlineStr"/>
-      <c r="E36" s="2" t="inlineStr"/>
-      <c r="F36" s="2" t="inlineStr"/>
-      <c r="G36" s="3" t="inlineStr">
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>三、潜力培育中</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr"/>
+      <c r="E36" t="inlineStr"/>
+      <c r="F36" t="inlineStr"/>
+      <c r="G36" t="inlineStr">
         <is>
           <t>海大</t>
         </is>
       </c>
-      <c r="H36" s="3" t="inlineStr"/>
-      <c r="I36" s="2" t="inlineStr"/>
-      <c r="J36" s="2" t="inlineStr"/>
-      <c r="K36" s="2" t="inlineStr"/>
-      <c r="L36" s="4" t="inlineStr">
+      <c r="H36" t="inlineStr"/>
+      <c r="I36" t="inlineStr"/>
+      <c r="J36" t="inlineStr"/>
+      <c r="K36" t="inlineStr"/>
+      <c r="L36" t="inlineStr">
         <is>
           <t>海大用户，大鱼一斤待抓、小鱼二两。</t>
         </is>
       </c>
-      <c r="M36" s="4" t="inlineStr">
+      <c r="M36" t="inlineStr">
         <is>
           <t>持续服务培育，寻找切入时机</t>
         </is>
       </c>
     </row>
     <row r="37">
-      <c r="A37" s="2" t="n">
+      <c r="A37" t="n">
         <v>36</v>
       </c>
-      <c r="B37" s="2" t="inlineStr">
+      <c r="B37" t="inlineStr">
         <is>
           <t>吴顺善</t>
         </is>
       </c>
-      <c r="C37" s="2" t="inlineStr">
-        <is>
-          <t>三、潜力培育中</t>
-        </is>
-      </c>
-      <c r="D37" s="2" t="inlineStr"/>
-      <c r="E37" s="2" t="inlineStr"/>
-      <c r="F37" s="2" t="inlineStr"/>
-      <c r="G37" s="3" t="inlineStr">
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>三、潜力培育中</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr"/>
+      <c r="E37" t="inlineStr"/>
+      <c r="F37" t="inlineStr"/>
+      <c r="G37" t="inlineStr">
         <is>
           <t>海壹</t>
         </is>
       </c>
-      <c r="H37" s="3" t="inlineStr"/>
-      <c r="I37" s="2" t="inlineStr"/>
-      <c r="J37" s="2" t="inlineStr"/>
-      <c r="K37" s="2" t="inlineStr"/>
-      <c r="L37" s="4" t="inlineStr">
+      <c r="H37" t="inlineStr"/>
+      <c r="I37" t="inlineStr"/>
+      <c r="J37" t="inlineStr"/>
+      <c r="K37" t="inlineStr"/>
+      <c r="L37" t="inlineStr">
         <is>
           <t>搭配少量海壹，存鱼一斤左右，本月集中出鱼。</t>
         </is>
       </c>
-      <c r="M37" s="4" t="inlineStr">
+      <c r="M37" t="inlineStr">
         <is>
           <t>持续服务培育，寻找切入时机</t>
         </is>
       </c>
     </row>
     <row r="38">
-      <c r="A38" s="2" t="n">
+      <c r="A38" t="n">
         <v>37</v>
       </c>
-      <c r="B38" s="2" t="inlineStr">
+      <c r="B38" t="inlineStr">
         <is>
           <t>陈勇林</t>
         </is>
       </c>
-      <c r="C38" s="2" t="inlineStr">
-        <is>
-          <t>三、潜力培育中</t>
-        </is>
-      </c>
-      <c r="D38" s="2" t="inlineStr"/>
-      <c r="E38" s="2" t="inlineStr"/>
-      <c r="F38" s="2" t="inlineStr"/>
-      <c r="G38" s="3" t="inlineStr">
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>三、潜力培育中</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr"/>
+      <c r="E38" t="inlineStr"/>
+      <c r="F38" t="inlineStr"/>
+      <c r="G38" t="inlineStr">
         <is>
           <t>混料</t>
         </is>
       </c>
-      <c r="H38" s="3" t="inlineStr"/>
-      <c r="I38" s="2" t="inlineStr"/>
-      <c r="J38" s="2" t="inlineStr"/>
-      <c r="K38" s="2" t="inlineStr"/>
-      <c r="L38" s="4" t="inlineStr">
+      <c r="H38" t="inlineStr"/>
+      <c r="I38" t="inlineStr"/>
+      <c r="J38" t="inlineStr"/>
+      <c r="K38" t="inlineStr"/>
+      <c r="L38" t="inlineStr">
         <is>
           <t>混料户，鱼塘死鱼时上门协助测水。</t>
         </is>
       </c>
-      <c r="M38" s="4" t="inlineStr">
+      <c r="M38" t="inlineStr">
         <is>
           <t>持续服务培育，寻找切入时机</t>
         </is>
       </c>
     </row>
     <row r="39">
-      <c r="A39" s="2" t="n">
+      <c r="A39" t="n">
         <v>38</v>
       </c>
-      <c r="B39" s="2" t="inlineStr">
+      <c r="B39" t="inlineStr">
         <is>
           <t>章建龙</t>
         </is>
       </c>
-      <c r="C39" s="2" t="inlineStr">
-        <is>
-          <t>三、潜力培育中</t>
-        </is>
-      </c>
-      <c r="D39" s="2" t="inlineStr"/>
-      <c r="E39" s="2" t="inlineStr"/>
-      <c r="F39" s="2" t="inlineStr"/>
-      <c r="G39" s="3" t="inlineStr"/>
-      <c r="H39" s="3" t="inlineStr">
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>三、潜力培育中</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr"/>
+      <c r="E39" t="inlineStr"/>
+      <c r="F39" t="inlineStr"/>
+      <c r="G39" t="inlineStr"/>
+      <c r="H39" t="inlineStr">
         <is>
           <t>马津深</t>
         </is>
       </c>
-      <c r="I39" s="2" t="inlineStr">
+      <c r="I39" t="inlineStr">
         <is>
           <t>与儿子一同经营</t>
         </is>
       </c>
-      <c r="J39" s="2" t="inlineStr"/>
-      <c r="K39" s="2" t="inlineStr"/>
-      <c r="L39" s="4" t="inlineStr">
+      <c r="J39" t="inlineStr"/>
+      <c r="K39" t="inlineStr"/>
+      <c r="L39" t="inlineStr">
         <is>
           <t>跟马津深拿料，塘向麻秋勇租。与儿子一同经营，新开四口新塘、基地在建，计划对接拉料。</t>
         </is>
       </c>
-      <c r="M39" s="4" t="inlineStr">
+      <c r="M39" t="inlineStr">
         <is>
           <t>持续服务培育，寻找切入时机</t>
         </is>
       </c>
     </row>
     <row r="40">
-      <c r="A40" s="2" t="n">
+      <c r="A40" t="n">
         <v>39</v>
       </c>
-      <c r="B40" s="2" t="inlineStr">
+      <c r="B40" t="inlineStr">
         <is>
           <t>丁志开</t>
         </is>
       </c>
-      <c r="C40" s="2" t="inlineStr">
-        <is>
-          <t>三、潜力培育中</t>
-        </is>
-      </c>
-      <c r="D40" s="2" t="inlineStr"/>
-      <c r="E40" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="F40" s="2" t="inlineStr"/>
-      <c r="G40" s="3" t="inlineStr">
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>三、潜力培育中</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr"/>
+      <c r="E40" t="n">
+        <v>5</v>
+      </c>
+      <c r="F40" t="inlineStr"/>
+      <c r="G40" t="inlineStr">
         <is>
           <t>翔泰、通威</t>
         </is>
       </c>
-      <c r="H40" s="3" t="inlineStr">
+      <c r="H40" t="inlineStr">
         <is>
           <t>马津深</t>
         </is>
       </c>
-      <c r="I40" s="2" t="inlineStr"/>
-      <c r="J40" s="2" t="inlineStr"/>
-      <c r="K40" s="2" t="inlineStr"/>
-      <c r="L40" s="4" t="inlineStr">
+      <c r="I40" t="inlineStr"/>
+      <c r="J40" t="inlineStr"/>
+      <c r="K40" t="inlineStr"/>
+      <c r="L40" t="inlineStr">
         <is>
           <t>5口在养鱼塘多处亚盐偏高；基本全程用翔泰、拉过一车通威；反映翔泰长得不行，后两月冲重量想拉通威，但经销商马津深（同音，马金生即马津深、已并）不给拉；准备拿苗原13号推迟至16号；其弟丁开福苗塘已放60万苗（约4800尾/斤），趁早刺激快速转料，便于后续用通威小料'开口乐'开口。10.10客情走访。</t>
         </is>
       </c>
-      <c r="M40" s="4" t="inlineStr">
+      <c r="M40" t="inlineStr">
         <is>
           <t>盯紧拿苗节点（16号），拿苗后趁冲重量需求推通威；借丁开福放苗刺激快速转料、推开口乐；渠道被马津深卡不给拉，需先打通通路。</t>
         </is>
       </c>
     </row>
     <row r="41">
-      <c r="A41" s="2" t="n">
+      <c r="A41" t="n">
         <v>40</v>
       </c>
-      <c r="B41" s="2" t="inlineStr">
+      <c r="B41" t="inlineStr">
         <is>
           <t>齐美娟</t>
         </is>
       </c>
-      <c r="C41" s="2" t="inlineStr">
-        <is>
-          <t>三、潜力培育中</t>
-        </is>
-      </c>
-      <c r="D41" s="2" t="inlineStr">
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>三、潜力培育中</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
         <is>
           <t>景山场地</t>
         </is>
       </c>
-      <c r="E41" s="2" t="inlineStr"/>
-      <c r="F41" s="2" t="inlineStr"/>
-      <c r="G41" s="3" t="inlineStr">
+      <c r="E41" t="inlineStr"/>
+      <c r="F41" t="inlineStr"/>
+      <c r="G41" t="inlineStr">
         <is>
           <t>祥泰、添祥</t>
         </is>
       </c>
-      <c r="H41" s="3" t="inlineStr"/>
-      <c r="I41" s="2" t="inlineStr">
+      <c r="H41" t="inlineStr"/>
+      <c r="I41" t="inlineStr">
         <is>
           <t>其儿子</t>
         </is>
       </c>
-      <c r="J41" s="2" t="inlineStr"/>
-      <c r="K41" s="2" t="inlineStr"/>
-      <c r="L41" s="4" t="inlineStr">
+      <c r="J41" t="inlineStr"/>
+      <c r="K41" t="inlineStr"/>
+      <c r="L41" t="inlineStr">
         <is>
           <t>用过粤海、鸿业一号，现用添祥。景山场地由儿子负责养殖及用料，反映祥泰料包重偏轻。</t>
         </is>
       </c>
-      <c r="M41" s="4" t="inlineStr">
+      <c r="M41" t="inlineStr">
         <is>
           <t>持续服务培育，寻找切入时机</t>
         </is>
       </c>
     </row>
     <row r="42">
-      <c r="A42" s="2" t="n">
+      <c r="A42" t="n">
         <v>41</v>
       </c>
-      <c r="B42" s="2" t="inlineStr">
+      <c r="B42" t="inlineStr">
         <is>
           <t>丁开福</t>
         </is>
       </c>
-      <c r="C42" s="2" t="inlineStr">
-        <is>
-          <t>三、潜力培育中</t>
-        </is>
-      </c>
-      <c r="D42" s="2" t="inlineStr"/>
-      <c r="E42" s="2" t="inlineStr"/>
-      <c r="F42" s="2" t="inlineStr"/>
-      <c r="G42" s="3" t="inlineStr">
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>三、潜力培育中</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr"/>
+      <c r="E42" t="inlineStr"/>
+      <c r="F42" t="inlineStr"/>
+      <c r="G42" t="inlineStr">
         <is>
           <t>百洋</t>
         </is>
       </c>
-      <c r="H42" s="3" t="inlineStr"/>
-      <c r="I42" s="2" t="inlineStr"/>
-      <c r="J42" s="2" t="inlineStr"/>
-      <c r="K42" s="2" t="inlineStr"/>
-      <c r="L42" s="4" t="inlineStr">
+      <c r="H42" t="inlineStr"/>
+      <c r="I42" t="inlineStr"/>
+      <c r="J42" t="inlineStr"/>
+      <c r="K42" t="inlineStr"/>
+      <c r="L42" t="inlineStr">
         <is>
           <t>原用通威9911，后被百洋切走，现用百洋，存鱼五两左右。【养殖关键节点】放苗：9月16日新抓60万尾苗放入，平均4800尾/斤（约125斤）。</t>
         </is>
       </c>
-      <c r="M42" s="4" t="inlineStr">
+      <c r="M42" t="inlineStr">
         <is>
           <t>持续服务培育，寻找切入时机；借其放苗（60万尾）刺激兄长丁志开快速转料、推通威开口乐。</t>
         </is>
       </c>
     </row>
     <row r="43">
-      <c r="A43" s="2" t="n">
+      <c r="A43" t="n">
         <v>42</v>
       </c>
-      <c r="B43" s="2" t="inlineStr">
+      <c r="B43" t="inlineStr">
         <is>
           <t>李土坤</t>
         </is>
       </c>
-      <c r="C43" s="2" t="inlineStr">
-        <is>
-          <t>三、潜力培育中</t>
-        </is>
-      </c>
-      <c r="D43" s="2" t="inlineStr"/>
-      <c r="E43" s="2" t="inlineStr"/>
-      <c r="F43" s="2" t="inlineStr">
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>三、潜力培育中</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr"/>
+      <c r="E43" t="inlineStr"/>
+      <c r="F43" t="inlineStr">
         <is>
           <t>80</t>
         </is>
       </c>
-      <c r="G43" s="3" t="inlineStr">
+      <c r="G43" t="inlineStr">
         <is>
           <t>祥泰</t>
         </is>
       </c>
-      <c r="H43" s="3" t="inlineStr">
+      <c r="H43" t="inlineStr">
         <is>
           <t>成江乾</t>
         </is>
       </c>
-      <c r="I43" s="2" t="inlineStr"/>
-      <c r="J43" s="2" t="inlineStr"/>
-      <c r="K43" s="2" t="inlineStr"/>
-      <c r="L43" s="4" t="inlineStr">
+      <c r="I43" t="inlineStr"/>
+      <c r="J43" t="inlineStr"/>
+      <c r="K43" t="inlineStr"/>
+      <c r="L43" t="inlineStr">
         <is>
           <t>80亩，祥泰，跟成江乾拿料，已出鱼。</t>
         </is>
       </c>
-      <c r="M43" s="4" t="inlineStr">
+      <c r="M43" t="inlineStr">
         <is>
           <t>持续服务培育，寻找切入时机</t>
         </is>
       </c>
     </row>
     <row r="44">
-      <c r="A44" s="2" t="n">
+      <c r="A44" t="n">
         <v>43</v>
       </c>
-      <c r="B44" s="2" t="inlineStr">
+      <c r="B44" t="inlineStr">
         <is>
           <t>符气导</t>
         </is>
       </c>
-      <c r="C44" s="2" t="inlineStr">
-        <is>
-          <t>三、潜力培育中</t>
-        </is>
-      </c>
-      <c r="D44" s="2" t="inlineStr"/>
-      <c r="E44" s="2" t="inlineStr"/>
-      <c r="F44" s="2" t="inlineStr">
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>三、潜力培育中</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr"/>
+      <c r="E44" t="inlineStr"/>
+      <c r="F44" t="inlineStr">
         <is>
           <t>60</t>
         </is>
       </c>
-      <c r="G44" s="3" t="inlineStr">
+      <c r="G44" t="inlineStr">
         <is>
           <t>歌颂</t>
         </is>
       </c>
-      <c r="H44" s="3" t="inlineStr">
+      <c r="H44" t="inlineStr">
         <is>
           <t>周公保</t>
         </is>
       </c>
-      <c r="I44" s="2" t="inlineStr"/>
-      <c r="J44" s="2" t="inlineStr"/>
-      <c r="K44" s="2" t="inlineStr"/>
-      <c r="L44" s="4" t="inlineStr">
+      <c r="I44" t="inlineStr"/>
+      <c r="J44" t="inlineStr"/>
+      <c r="K44" t="inlineStr"/>
+      <c r="L44" t="inlineStr">
         <is>
           <t>60亩，歌颂，跟周公保拿料，资金不足。</t>
         </is>
       </c>
-      <c r="M44" s="4" t="inlineStr">
+      <c r="M44" t="inlineStr">
         <is>
           <t>持续服务培育，寻找切入时机</t>
         </is>
       </c>
     </row>
     <row r="45">
-      <c r="A45" s="2" t="n">
+      <c r="A45" t="n">
         <v>44</v>
       </c>
-      <c r="B45" s="2" t="inlineStr">
+      <c r="B45" t="inlineStr">
         <is>
           <t>徐老板</t>
         </is>
       </c>
-      <c r="C45" s="2" t="inlineStr">
-        <is>
-          <t>三、潜力培育中</t>
-        </is>
-      </c>
-      <c r="D45" s="2" t="inlineStr"/>
-      <c r="E45" s="2" t="inlineStr"/>
-      <c r="F45" s="2" t="inlineStr"/>
-      <c r="G45" s="3" t="inlineStr">
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>三、潜力培育中</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr"/>
+      <c r="E45" t="inlineStr"/>
+      <c r="F45" t="inlineStr"/>
+      <c r="G45" t="inlineStr">
         <is>
           <t>祥泰</t>
         </is>
       </c>
-      <c r="H45" s="3" t="inlineStr"/>
-      <c r="I45" s="2" t="inlineStr"/>
-      <c r="J45" s="2" t="inlineStr"/>
-      <c r="K45" s="2" t="inlineStr"/>
-      <c r="L45" s="4" t="inlineStr">
+      <c r="H45" t="inlineStr"/>
+      <c r="I45" t="inlineStr"/>
+      <c r="J45" t="inlineStr"/>
+      <c r="K45" t="inlineStr"/>
+      <c r="L45" t="inlineStr">
         <is>
           <t>祥泰，存塘二两小鱼，有欠款。</t>
         </is>
       </c>
-      <c r="M45" s="4" t="inlineStr">
+      <c r="M45" t="inlineStr">
         <is>
           <t>持续服务培育，寻找切入时机</t>
         </is>
       </c>
     </row>
     <row r="46">
-      <c r="A46" s="2" t="n">
+      <c r="A46" t="n">
         <v>45</v>
       </c>
-      <c r="B46" s="2" t="inlineStr">
+      <c r="B46" t="inlineStr">
         <is>
           <t>郑明来</t>
         </is>
       </c>
-      <c r="C46" s="2" t="inlineStr">
-        <is>
-          <t>三、潜力培育中</t>
-        </is>
-      </c>
-      <c r="D46" s="2" t="inlineStr"/>
-      <c r="E46" s="2" t="inlineStr"/>
-      <c r="F46" s="2" t="inlineStr"/>
-      <c r="G46" s="3" t="inlineStr">
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>三、潜力培育中</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr"/>
+      <c r="E46" t="inlineStr"/>
+      <c r="F46" t="inlineStr"/>
+      <c r="G46" t="inlineStr">
         <is>
           <t>祥泰</t>
         </is>
       </c>
-      <c r="H46" s="3" t="inlineStr">
+      <c r="H46" t="inlineStr">
         <is>
           <t>朱康永</t>
         </is>
       </c>
-      <c r="I46" s="2" t="inlineStr"/>
-      <c r="J46" s="2" t="inlineStr"/>
-      <c r="K46" s="2" t="inlineStr"/>
-      <c r="L46" s="4" t="inlineStr">
+      <c r="I46" t="inlineStr"/>
+      <c r="J46" t="inlineStr"/>
+      <c r="K46" t="inlineStr"/>
+      <c r="L46" t="inlineStr">
         <is>
           <t>跟朱康永拿料，祥泰，资金周转困难。</t>
         </is>
       </c>
-      <c r="M46" s="4" t="inlineStr">
+      <c r="M46" t="inlineStr">
         <is>
           <t>持续服务培育，寻找切入时机</t>
         </is>
       </c>
     </row>
     <row r="47">
-      <c r="A47" s="2" t="n">
+      <c r="A47" t="n">
         <v>46</v>
       </c>
-      <c r="B47" s="2" t="inlineStr">
+      <c r="B47" t="inlineStr">
         <is>
           <t>方岳勇</t>
         </is>
       </c>
-      <c r="C47" s="2" t="inlineStr">
-        <is>
-          <t>三、潜力培育中</t>
-        </is>
-      </c>
-      <c r="D47" s="2" t="inlineStr"/>
-      <c r="E47" s="2" t="n">
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>三、潜力培育中</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr"/>
+      <c r="E47" t="n">
         <v>3</v>
       </c>
-      <c r="F47" s="2" t="inlineStr"/>
-      <c r="G47" s="3" t="inlineStr">
+      <c r="F47" t="inlineStr"/>
+      <c r="G47" t="inlineStr">
         <is>
           <t>祥泰</t>
         </is>
       </c>
-      <c r="H47" s="3" t="inlineStr">
+      <c r="H47" t="inlineStr">
         <is>
           <t>符策锋</t>
         </is>
       </c>
-      <c r="I47" s="2" t="inlineStr"/>
-      <c r="J47" s="2" t="inlineStr"/>
-      <c r="K47" s="2" t="inlineStr">
+      <c r="I47" t="inlineStr"/>
+      <c r="J47" t="inlineStr"/>
+      <c r="K47" t="inlineStr">
         <is>
           <t>40</t>
         </is>
       </c>
-      <c r="L47" s="4" t="inlineStr">
+      <c r="L47" t="inlineStr">
         <is>
           <t>祥泰客户，三口塘，跟符策锋拿料，鱼苗跟朱康飞拿。上一兆抓40，暂对转料不感兴趣。</t>
         </is>
       </c>
-      <c r="M47" s="4" t="inlineStr">
+      <c r="M47" t="inlineStr">
         <is>
           <t>持续服务培育，寻找切入时机</t>
         </is>
       </c>
     </row>
     <row r="48">
-      <c r="A48" s="2" t="n">
+      <c r="A48" t="n">
         <v>47</v>
       </c>
-      <c r="B48" s="2" t="inlineStr">
+      <c r="B48" t="inlineStr">
         <is>
           <t>麻秋勇</t>
         </is>
       </c>
-      <c r="C48" s="2" t="inlineStr">
-        <is>
-          <t>三、潜力培育中</t>
-        </is>
-      </c>
-      <c r="D48" s="2" t="inlineStr"/>
-      <c r="E48" s="2" t="inlineStr"/>
-      <c r="F48" s="2" t="inlineStr"/>
-      <c r="G48" s="3" t="inlineStr"/>
-      <c r="H48" s="3" t="inlineStr"/>
-      <c r="I48" s="2" t="inlineStr"/>
-      <c r="J48" s="2" t="inlineStr"/>
-      <c r="K48" s="2" t="inlineStr"/>
-      <c r="L48" s="4" t="inlineStr">
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>三、潜力培育中</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr"/>
+      <c r="E48" t="inlineStr"/>
+      <c r="F48" t="inlineStr"/>
+      <c r="G48" t="inlineStr"/>
+      <c r="H48" t="inlineStr"/>
+      <c r="I48" t="inlineStr"/>
+      <c r="J48" t="inlineStr"/>
+      <c r="K48" t="inlineStr"/>
+      <c r="L48" t="inlineStr">
         <is>
           <t>经销商，转用通威需折扣支持。</t>
         </is>
       </c>
-      <c r="M48" s="4" t="inlineStr">
+      <c r="M48" t="inlineStr">
         <is>
           <t>持续服务培育，寻找切入时机</t>
         </is>
       </c>
     </row>
     <row r="49">
-      <c r="A49" s="2" t="n">
+      <c r="A49" t="n">
         <v>48</v>
       </c>
-      <c r="B49" s="2" t="inlineStr">
+      <c r="B49" t="inlineStr">
         <is>
           <t>田锡光</t>
         </is>
       </c>
-      <c r="C49" s="2" t="inlineStr">
-        <is>
-          <t>三、潜力培育中</t>
-        </is>
-      </c>
-      <c r="D49" s="2" t="inlineStr"/>
-      <c r="E49" s="2" t="inlineStr"/>
-      <c r="F49" s="2" t="inlineStr"/>
-      <c r="G49" s="3" t="inlineStr">
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>三、潜力培育中</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr"/>
+      <c r="E49" t="inlineStr"/>
+      <c r="F49" t="inlineStr"/>
+      <c r="G49" t="inlineStr">
         <is>
           <t>粤海</t>
         </is>
       </c>
-      <c r="H49" s="3" t="inlineStr"/>
-      <c r="I49" s="2" t="inlineStr"/>
-      <c r="J49" s="2" t="inlineStr"/>
-      <c r="K49" s="2" t="inlineStr"/>
-      <c r="L49" s="4" t="inlineStr">
+      <c r="H49" t="inlineStr"/>
+      <c r="I49" t="inlineStr"/>
+      <c r="J49" t="inlineStr"/>
+      <c r="K49" t="inlineStr"/>
+      <c r="L49" t="inlineStr">
         <is>
           <t>之前做料商，自存一批粤海料。</t>
         </is>
       </c>
-      <c r="M49" s="4" t="inlineStr">
+      <c r="M49" t="inlineStr">
         <is>
           <t>持续服务培育，寻找切入时机</t>
         </is>
       </c>
     </row>
     <row r="50">
-      <c r="A50" s="2" t="n">
+      <c r="A50" t="n">
         <v>49</v>
       </c>
-      <c r="B50" s="2" t="inlineStr">
+      <c r="B50" t="inlineStr">
         <is>
           <t>崔勇林</t>
         </is>
       </c>
-      <c r="C50" s="2" t="inlineStr">
-        <is>
-          <t>三、潜力培育中</t>
-        </is>
-      </c>
-      <c r="D50" s="2" t="inlineStr"/>
-      <c r="E50" s="2" t="inlineStr"/>
-      <c r="F50" s="2" t="inlineStr"/>
-      <c r="G50" s="3" t="inlineStr"/>
-      <c r="H50" s="3" t="inlineStr">
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>三、潜力培育中</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr"/>
+      <c r="E50" t="inlineStr"/>
+      <c r="F50" t="inlineStr"/>
+      <c r="G50" t="inlineStr"/>
+      <c r="H50" t="inlineStr">
         <is>
           <t>郑标远</t>
         </is>
       </c>
-      <c r="I50" s="2" t="inlineStr"/>
-      <c r="J50" s="2" t="inlineStr"/>
-      <c r="K50" s="2" t="inlineStr"/>
-      <c r="L50" s="4" t="inlineStr">
+      <c r="I50" t="inlineStr"/>
+      <c r="J50" t="inlineStr"/>
+      <c r="K50" t="inlineStr"/>
+      <c r="L50" t="inlineStr">
         <is>
           <t>跟郑标远拿料，未用通威。</t>
         </is>
       </c>
-      <c r="M50" s="4" t="inlineStr">
+      <c r="M50" t="inlineStr">
         <is>
           <t>持续服务培育，寻找切入时机</t>
         </is>
       </c>
     </row>
     <row r="51">
-      <c r="A51" s="2" t="n">
+      <c r="A51" t="n">
         <v>50</v>
       </c>
-      <c r="B51" s="2" t="inlineStr">
+      <c r="B51" t="inlineStr">
         <is>
           <t>吴仙福</t>
         </is>
       </c>
-      <c r="C51" s="2" t="inlineStr">
-        <is>
-          <t>三、潜力培育中</t>
-        </is>
-      </c>
-      <c r="D51" s="2" t="inlineStr"/>
-      <c r="E51" s="2" t="inlineStr"/>
-      <c r="F51" s="2" t="inlineStr"/>
-      <c r="G51" s="3" t="inlineStr">
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>三、潜力培育中</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr"/>
+      <c r="E51" t="inlineStr"/>
+      <c r="F51" t="inlineStr"/>
+      <c r="G51" t="inlineStr">
         <is>
           <t>海大</t>
         </is>
       </c>
-      <c r="H51" s="3" t="inlineStr">
+      <c r="H51" t="inlineStr">
         <is>
           <t>王焕忠</t>
         </is>
       </c>
-      <c r="I51" s="2" t="inlineStr"/>
-      <c r="J51" s="2" t="inlineStr"/>
-      <c r="K51" s="2" t="inlineStr"/>
-      <c r="L51" s="4" t="inlineStr">
+      <c r="I51" t="inlineStr"/>
+      <c r="J51" t="inlineStr"/>
+      <c r="K51" t="inlineStr"/>
+      <c r="L51" t="inlineStr">
         <is>
           <t>跟王焕忠拿料，海大老用户，换料意愿低。</t>
         </is>
       </c>
-      <c r="M51" s="4" t="inlineStr">
+      <c r="M51" t="inlineStr">
         <is>
           <t>持续服务培育，寻找切入时机</t>
         </is>
       </c>
     </row>
     <row r="52">
-      <c r="A52" s="2" t="n">
+      <c r="A52" t="n">
         <v>51</v>
       </c>
-      <c r="B52" s="2" t="inlineStr">
+      <c r="B52" t="inlineStr">
         <is>
           <t>吴卫明</t>
         </is>
       </c>
-      <c r="C52" s="2" t="inlineStr">
-        <is>
-          <t>三、潜力培育中</t>
-        </is>
-      </c>
-      <c r="D52" s="2" t="inlineStr"/>
-      <c r="E52" s="2" t="inlineStr"/>
-      <c r="F52" s="2" t="inlineStr"/>
-      <c r="G52" s="3" t="inlineStr">
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>三、潜力培育中</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr"/>
+      <c r="E52" t="inlineStr"/>
+      <c r="F52" t="inlineStr"/>
+      <c r="G52" t="inlineStr">
         <is>
           <t>新希望</t>
         </is>
       </c>
-      <c r="H52" s="3" t="inlineStr"/>
-      <c r="I52" s="2" t="inlineStr"/>
-      <c r="J52" s="2" t="inlineStr"/>
-      <c r="K52" s="2" t="inlineStr"/>
-      <c r="L52" s="4" t="inlineStr">
+      <c r="H52" t="inlineStr"/>
+      <c r="I52" t="inlineStr"/>
+      <c r="J52" t="inlineStr"/>
+      <c r="K52" t="inlineStr"/>
+      <c r="L52" t="inlineStr">
         <is>
           <t>新希望老用户。</t>
         </is>
       </c>
-      <c r="M52" s="4" t="inlineStr">
+      <c r="M52" t="inlineStr">
         <is>
           <t>持续服务培育，寻找切入时机</t>
         </is>
       </c>
     </row>
     <row r="53">
-      <c r="A53" s="2" t="n">
+      <c r="A53" t="n">
         <v>52</v>
       </c>
-      <c r="B53" s="2" t="inlineStr">
+      <c r="B53" t="inlineStr">
         <is>
           <t>陈春枝</t>
         </is>
       </c>
-      <c r="C53" s="2" t="inlineStr">
-        <is>
-          <t>三、潜力培育中</t>
-        </is>
-      </c>
-      <c r="D53" s="2" t="inlineStr"/>
-      <c r="E53" s="2" t="inlineStr"/>
-      <c r="F53" s="2" t="inlineStr"/>
-      <c r="G53" s="3" t="inlineStr"/>
-      <c r="H53" s="3" t="inlineStr">
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>三、潜力培育中</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr"/>
+      <c r="E53" t="inlineStr"/>
+      <c r="F53" t="inlineStr"/>
+      <c r="G53" t="inlineStr"/>
+      <c r="H53" t="inlineStr">
         <is>
           <t>符侧锋暂不拿货</t>
         </is>
       </c>
-      <c r="I53" s="2" t="inlineStr"/>
-      <c r="J53" s="2" t="inlineStr"/>
-      <c r="K53" s="2" t="inlineStr"/>
-      <c r="L53" s="4" t="inlineStr">
+      <c r="I53" t="inlineStr"/>
+      <c r="J53" t="inlineStr"/>
+      <c r="K53" t="inlineStr"/>
+      <c r="L53" t="inlineStr">
         <is>
           <t>现经销商符侧锋暂不拿货，引导更换经销商中。</t>
         </is>
       </c>
-      <c r="M53" s="4" t="inlineStr">
+      <c r="M53" t="inlineStr">
         <is>
           <t>持续服务培育，寻找切入时机</t>
         </is>
       </c>
     </row>
     <row r="54">
-      <c r="A54" s="2" t="n">
+      <c r="A54" t="n">
         <v>53</v>
       </c>
-      <c r="B54" s="2" t="inlineStr">
+      <c r="B54" t="inlineStr">
         <is>
           <t>章春莲</t>
         </is>
       </c>
-      <c r="C54" s="2" t="inlineStr">
-        <is>
-          <t>三、潜力培育中</t>
-        </is>
-      </c>
-      <c r="D54" s="2" t="inlineStr"/>
-      <c r="E54" s="2" t="inlineStr"/>
-      <c r="F54" s="2" t="inlineStr"/>
-      <c r="G54" s="3" t="inlineStr"/>
-      <c r="H54" s="3" t="inlineStr"/>
-      <c r="I54" s="2" t="inlineStr"/>
-      <c r="J54" s="2" t="inlineStr"/>
-      <c r="K54" s="2" t="inlineStr"/>
-      <c r="L54" s="4" t="inlineStr">
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>三、潜力培育中</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr"/>
+      <c r="E54" t="inlineStr"/>
+      <c r="F54" t="inlineStr"/>
+      <c r="G54" t="inlineStr"/>
+      <c r="H54" t="inlineStr"/>
+      <c r="I54" t="inlineStr"/>
+      <c r="J54" t="inlineStr"/>
+      <c r="K54" t="inlineStr"/>
+      <c r="L54" t="inlineStr">
         <is>
           <t>走访时用户不在家。</t>
         </is>
       </c>
-      <c r="M54" s="4" t="inlineStr">
+      <c r="M54" t="inlineStr">
         <is>
           <t>持续服务培育，寻找切入时机</t>
         </is>
       </c>
     </row>
     <row r="55">
-      <c r="A55" s="2" t="n">
+      <c r="A55" t="n">
         <v>54</v>
       </c>
-      <c r="B55" s="2" t="inlineStr">
+      <c r="B55" t="inlineStr">
         <is>
           <t>刘欧忠</t>
         </is>
       </c>
-      <c r="C55" s="2" t="inlineStr">
-        <is>
-          <t>三、潜力培育中</t>
-        </is>
-      </c>
-      <c r="D55" s="2" t="inlineStr"/>
-      <c r="E55" s="2" t="inlineStr"/>
-      <c r="F55" s="2" t="inlineStr"/>
-      <c r="G55" s="3" t="inlineStr"/>
-      <c r="H55" s="3" t="inlineStr"/>
-      <c r="I55" s="2" t="inlineStr"/>
-      <c r="J55" s="2" t="inlineStr"/>
-      <c r="K55" s="2" t="inlineStr"/>
-      <c r="L55" s="4" t="inlineStr">
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>三、潜力培育中</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr"/>
+      <c r="E55" t="inlineStr"/>
+      <c r="F55" t="inlineStr"/>
+      <c r="G55" t="inlineStr"/>
+      <c r="H55" t="inlineStr"/>
+      <c r="I55" t="inlineStr"/>
+      <c r="J55" t="inlineStr"/>
+      <c r="K55" t="inlineStr"/>
+      <c r="L55" t="inlineStr">
         <is>
           <t>当地声望高，片区影响力大。</t>
         </is>
       </c>
-      <c r="M55" s="4" t="inlineStr">
+      <c r="M55" t="inlineStr">
         <is>
           <t>持续服务培育，寻找切入时机</t>
         </is>
       </c>
     </row>
     <row r="56">
-      <c r="A56" s="2" t="n">
+      <c r="A56" t="n">
         <v>55</v>
       </c>
-      <c r="B56" s="2" t="inlineStr">
+      <c r="B56" t="inlineStr">
         <is>
           <t>章水龙</t>
         </is>
       </c>
-      <c r="C56" s="2" t="inlineStr">
-        <is>
-          <t>三、潜力培育中</t>
-        </is>
-      </c>
-      <c r="D56" s="2" t="inlineStr"/>
-      <c r="E56" s="2" t="inlineStr"/>
-      <c r="F56" s="2" t="inlineStr"/>
-      <c r="G56" s="3" t="inlineStr"/>
-      <c r="H56" s="3" t="inlineStr"/>
-      <c r="I56" s="2" t="inlineStr"/>
-      <c r="J56" s="2" t="inlineStr"/>
-      <c r="K56" s="2" t="inlineStr"/>
-      <c r="L56" s="4" t="inlineStr">
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>三、潜力培育中</t>
+        </is>
+      </c>
+      <c r="D56" t="inlineStr"/>
+      <c r="E56" t="inlineStr"/>
+      <c r="F56" t="inlineStr"/>
+      <c r="G56" t="inlineStr"/>
+      <c r="H56" t="inlineStr"/>
+      <c r="I56" t="inlineStr"/>
+      <c r="J56" t="inlineStr"/>
+      <c r="K56" t="inlineStr"/>
+      <c r="L56" t="inlineStr">
         <is>
           <t>协助运送动保。</t>
         </is>
       </c>
-      <c r="M56" s="4" t="inlineStr">
+      <c r="M56" t="inlineStr">
         <is>
           <t>持续服务培育，寻找切入时机</t>
         </is>
       </c>
     </row>
     <row r="57">
-      <c r="A57" s="2" t="n">
+      <c r="A57" t="n">
         <v>56</v>
       </c>
-      <c r="B57" s="2" t="inlineStr">
+      <c r="B57" t="inlineStr">
         <is>
           <t>韩冠</t>
         </is>
       </c>
-      <c r="C57" s="2" t="inlineStr">
-        <is>
-          <t>三、潜力培育中</t>
-        </is>
-      </c>
-      <c r="D57" s="2" t="inlineStr"/>
-      <c r="E57" s="2" t="inlineStr"/>
-      <c r="F57" s="2" t="inlineStr"/>
-      <c r="G57" s="3" t="inlineStr">
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>三、潜力培育中</t>
+        </is>
+      </c>
+      <c r="D57" t="inlineStr"/>
+      <c r="E57" t="inlineStr"/>
+      <c r="F57" t="inlineStr"/>
+      <c r="G57" t="inlineStr">
         <is>
           <t>海大</t>
         </is>
       </c>
-      <c r="H57" s="3" t="inlineStr"/>
-      <c r="I57" s="2" t="inlineStr"/>
-      <c r="J57" s="2" t="inlineStr"/>
-      <c r="K57" s="2" t="inlineStr"/>
-      <c r="L57" s="4" t="inlineStr">
+      <c r="H57" t="inlineStr"/>
+      <c r="I57" t="inlineStr"/>
+      <c r="J57" t="inlineStr"/>
+      <c r="K57" t="inlineStr"/>
+      <c r="L57" t="inlineStr">
         <is>
           <t>对接海大动保业务人员。</t>
         </is>
       </c>
-      <c r="M57" s="4" t="inlineStr">
+      <c r="M57" t="inlineStr">
         <is>
           <t>持续服务培育，寻找切入时机</t>
         </is>
       </c>
     </row>
     <row r="58">
-      <c r="A58" s="2" t="n">
+      <c r="A58" t="n">
         <v>57</v>
       </c>
-      <c r="B58" s="2" t="inlineStr">
+      <c r="B58" t="inlineStr">
         <is>
           <t>攀塘周</t>
         </is>
       </c>
-      <c r="C58" s="2" t="inlineStr">
-        <is>
-          <t>三、潜力培育中</t>
-        </is>
-      </c>
-      <c r="D58" s="2" t="inlineStr"/>
-      <c r="E58" s="2" t="inlineStr"/>
-      <c r="F58" s="2" t="inlineStr"/>
-      <c r="G58" s="3" t="inlineStr"/>
-      <c r="H58" s="3" t="inlineStr"/>
-      <c r="I58" s="2" t="inlineStr"/>
-      <c r="J58" s="2" t="inlineStr"/>
-      <c r="K58" s="2" t="inlineStr"/>
-      <c r="L58" s="4" t="inlineStr">
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>三、潜力培育中</t>
+        </is>
+      </c>
+      <c r="D58" t="inlineStr"/>
+      <c r="E58" t="inlineStr"/>
+      <c r="F58" t="inlineStr"/>
+      <c r="G58" t="inlineStr"/>
+      <c r="H58" t="inlineStr"/>
+      <c r="I58" t="inlineStr"/>
+      <c r="J58" t="inlineStr"/>
+      <c r="K58" t="inlineStr"/>
+      <c r="L58" t="inlineStr">
         <is>
           <t>换料意愿不强。</t>
         </is>
       </c>
-      <c r="M58" s="4" t="inlineStr">
+      <c r="M58" t="inlineStr">
         <is>
           <t>持续服务培育，寻找切入时机</t>
         </is>
       </c>
     </row>
     <row r="59">
-      <c r="A59" s="2" t="n">
+      <c r="A59" t="n">
         <v>58</v>
       </c>
-      <c r="B59" s="2" t="inlineStr">
+      <c r="B59" t="inlineStr">
         <is>
           <t>王旭升</t>
         </is>
       </c>
-      <c r="C59" s="2" t="inlineStr">
-        <is>
-          <t>三、潜力培育中</t>
-        </is>
-      </c>
-      <c r="D59" s="2" t="inlineStr"/>
-      <c r="E59" s="2" t="inlineStr"/>
-      <c r="F59" s="2" t="inlineStr"/>
-      <c r="G59" s="3" t="inlineStr"/>
-      <c r="H59" s="3" t="inlineStr"/>
-      <c r="I59" s="2" t="inlineStr"/>
-      <c r="J59" s="2" t="inlineStr"/>
-      <c r="K59" s="2" t="inlineStr"/>
-      <c r="L59" s="4" t="inlineStr">
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>三、潜力培育中</t>
+        </is>
+      </c>
+      <c r="D59" t="inlineStr"/>
+      <c r="E59" t="inlineStr"/>
+      <c r="F59" t="inlineStr"/>
+      <c r="G59" t="inlineStr"/>
+      <c r="H59" t="inlineStr"/>
+      <c r="I59" t="inlineStr"/>
+      <c r="J59" t="inlineStr"/>
+      <c r="K59" t="inlineStr"/>
+      <c r="L59" t="inlineStr">
         <is>
           <t>测水跟进养殖情况。</t>
         </is>
       </c>
-      <c r="M59" s="4" t="inlineStr">
+      <c r="M59" t="inlineStr">
         <is>
           <t>持续服务培育，寻找切入时机</t>
         </is>
       </c>
     </row>
     <row r="60">
-      <c r="A60" s="2" t="n">
+      <c r="A60" t="n">
         <v>59</v>
       </c>
-      <c r="B60" s="2" t="inlineStr">
+      <c r="B60" t="inlineStr">
         <is>
           <t>周先达</t>
         </is>
       </c>
-      <c r="C60" s="2" t="inlineStr">
-        <is>
-          <t>三、潜力培育中</t>
-        </is>
-      </c>
-      <c r="D60" s="2" t="inlineStr"/>
-      <c r="E60" s="2" t="inlineStr"/>
-      <c r="F60" s="2" t="inlineStr"/>
-      <c r="G60" s="3" t="inlineStr">
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>三、潜力培育中</t>
+        </is>
+      </c>
+      <c r="D60" t="inlineStr"/>
+      <c r="E60" t="inlineStr"/>
+      <c r="F60" t="inlineStr"/>
+      <c r="G60" t="inlineStr">
         <is>
           <t>粤农</t>
         </is>
       </c>
-      <c r="H60" s="3" t="inlineStr"/>
-      <c r="I60" s="2" t="inlineStr"/>
-      <c r="J60" s="2" t="inlineStr"/>
-      <c r="K60" s="2" t="inlineStr"/>
-      <c r="L60" s="4" t="inlineStr">
+      <c r="H60" t="inlineStr"/>
+      <c r="I60" t="inlineStr"/>
+      <c r="J60" t="inlineStr"/>
+      <c r="K60" t="inlineStr"/>
+      <c r="L60" t="inlineStr">
         <is>
           <t>用粤农鸭料。</t>
         </is>
       </c>
-      <c r="M60" s="4" t="inlineStr">
+      <c r="M60" t="inlineStr">
         <is>
           <t>持续服务培育，寻找切入时机</t>
         </is>
       </c>
     </row>
     <row r="61">
-      <c r="A61" s="2" t="n">
+      <c r="A61" t="n">
         <v>60</v>
       </c>
-      <c r="B61" s="2" t="inlineStr">
+      <c r="B61" t="inlineStr">
         <is>
           <t>陶老板</t>
         </is>
       </c>
-      <c r="C61" s="2" t="inlineStr">
-        <is>
-          <t>三、潜力培育中</t>
-        </is>
-      </c>
-      <c r="D61" s="2" t="inlineStr"/>
-      <c r="E61" s="2" t="inlineStr"/>
-      <c r="F61" s="2" t="inlineStr"/>
-      <c r="G61" s="3" t="inlineStr">
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>三、潜力培育中</t>
+        </is>
+      </c>
+      <c r="D61" t="inlineStr"/>
+      <c r="E61" t="inlineStr"/>
+      <c r="F61" t="inlineStr"/>
+      <c r="G61" t="inlineStr">
         <is>
           <t>蜀海</t>
         </is>
       </c>
-      <c r="H61" s="3" t="inlineStr"/>
-      <c r="I61" s="2" t="inlineStr"/>
-      <c r="J61" s="2" t="inlineStr"/>
-      <c r="K61" s="2" t="inlineStr"/>
-      <c r="L61" s="4" t="inlineStr">
+      <c r="H61" t="inlineStr"/>
+      <c r="I61" t="inlineStr"/>
+      <c r="J61" t="inlineStr"/>
+      <c r="K61" t="inlineStr"/>
+      <c r="L61" t="inlineStr">
         <is>
           <t>多基地混养草鱼、鲢鳙，蜀海料加发酵料加鸭料，看重性价比。</t>
         </is>
       </c>
-      <c r="M61" s="4" t="inlineStr">
+      <c r="M61" t="inlineStr">
         <is>
           <t>持续服务培育，寻找切入时机</t>
         </is>
       </c>
     </row>
     <row r="62">
-      <c r="A62" s="2" t="n">
+      <c r="A62" t="n">
         <v>61</v>
       </c>
-      <c r="B62" s="2" t="inlineStr">
+      <c r="B62" t="inlineStr">
         <is>
           <t>白茅村吴老板</t>
         </is>
       </c>
-      <c r="C62" s="2" t="inlineStr">
-        <is>
-          <t>三、潜力培育中</t>
-        </is>
-      </c>
-      <c r="D62" s="2" t="inlineStr"/>
-      <c r="E62" s="2" t="n">
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>三、潜力培育中</t>
+        </is>
+      </c>
+      <c r="D62" t="inlineStr"/>
+      <c r="E62" t="n">
         <v>6</v>
       </c>
-      <c r="F62" s="2" t="inlineStr"/>
-      <c r="G62" s="3" t="inlineStr">
+      <c r="F62" t="inlineStr"/>
+      <c r="G62" t="inlineStr">
         <is>
           <t>金长城</t>
         </is>
       </c>
-      <c r="H62" s="3" t="inlineStr"/>
-      <c r="I62" s="2" t="inlineStr"/>
-      <c r="J62" s="2" t="inlineStr"/>
-      <c r="K62" s="2" t="inlineStr"/>
-      <c r="L62" s="4" t="inlineStr">
+      <c r="H62" t="inlineStr"/>
+      <c r="I62" t="inlineStr"/>
+      <c r="J62" t="inlineStr"/>
+      <c r="K62" t="inlineStr"/>
+      <c r="L62" t="inlineStr">
         <is>
           <t>六口虾塘，金长城虾料。</t>
         </is>
       </c>
-      <c r="M62" s="4" t="inlineStr">
+      <c r="M62" t="inlineStr">
         <is>
           <t>持续服务培育，寻找切入时机</t>
         </is>
       </c>
     </row>
     <row r="63">
-      <c r="A63" s="2" t="n">
+      <c r="A63" t="n">
         <v>62</v>
       </c>
-      <c r="B63" s="2" t="inlineStr">
+      <c r="B63" t="inlineStr">
         <is>
           <t>张燕</t>
         </is>
       </c>
-      <c r="C63" s="2" t="inlineStr">
-        <is>
-          <t>三、潜力培育中</t>
-        </is>
-      </c>
-      <c r="D63" s="2" t="inlineStr"/>
-      <c r="E63" s="2" t="inlineStr"/>
-      <c r="F63" s="2" t="inlineStr"/>
-      <c r="G63" s="3" t="inlineStr"/>
-      <c r="H63" s="3" t="inlineStr"/>
-      <c r="I63" s="2" t="inlineStr"/>
-      <c r="J63" s="2" t="inlineStr"/>
-      <c r="K63" s="2" t="inlineStr"/>
-      <c r="L63" s="4" t="inlineStr">
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>三、潜力培育中</t>
+        </is>
+      </c>
+      <c r="D63" t="inlineStr"/>
+      <c r="E63" t="inlineStr"/>
+      <c r="F63" t="inlineStr"/>
+      <c r="G63" t="inlineStr"/>
+      <c r="H63" t="inlineStr"/>
+      <c r="I63" t="inlineStr"/>
+      <c r="J63" t="inlineStr"/>
+      <c r="K63" t="inlineStr"/>
+      <c r="L63" t="inlineStr">
         <is>
           <t>塘口租期临近，暂不考虑装料塔，经营药店。</t>
         </is>
       </c>
-      <c r="M63" s="4" t="inlineStr">
+      <c r="M63" t="inlineStr">
         <is>
           <t>持续服务培育，寻找切入时机</t>
         </is>
       </c>
     </row>
     <row r="64">
-      <c r="A64" s="2" t="n">
+      <c r="A64" t="n">
         <v>63</v>
       </c>
-      <c r="B64" s="2" t="inlineStr">
+      <c r="B64" t="inlineStr">
         <is>
           <t>李新建</t>
         </is>
       </c>
-      <c r="C64" s="2" t="inlineStr">
-        <is>
-          <t>三、潜力培育中</t>
-        </is>
-      </c>
-      <c r="D64" s="2" t="inlineStr"/>
-      <c r="E64" s="2" t="inlineStr"/>
-      <c r="F64" s="2" t="inlineStr"/>
-      <c r="G64" s="3" t="inlineStr">
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>三、潜力培育中</t>
+        </is>
+      </c>
+      <c r="D64" t="inlineStr"/>
+      <c r="E64" t="inlineStr"/>
+      <c r="F64" t="inlineStr"/>
+      <c r="G64" t="inlineStr">
         <is>
           <t>祥泰</t>
         </is>
       </c>
-      <c r="H64" s="3" t="inlineStr"/>
-      <c r="I64" s="2" t="inlineStr"/>
-      <c r="J64" s="2" t="inlineStr"/>
-      <c r="K64" s="2" t="inlineStr"/>
-      <c r="L64" s="4" t="inlineStr">
+      <c r="H64" t="inlineStr"/>
+      <c r="I64" t="inlineStr"/>
+      <c r="J64" t="inlineStr"/>
+      <c r="K64" t="inlineStr"/>
+      <c r="L64" t="inlineStr">
         <is>
           <t>仓库存放祥泰饲料。</t>
         </is>
       </c>
-      <c r="M64" s="4" t="inlineStr">
+      <c r="M64" t="inlineStr">
         <is>
           <t>持续服务培育，寻找切入时机</t>
         </is>
       </c>
     </row>
     <row r="65">
-      <c r="A65" s="2" t="n">
+      <c r="A65" t="n">
         <v>64</v>
       </c>
-      <c r="B65" s="2" t="inlineStr">
+      <c r="B65" t="inlineStr">
         <is>
           <t>许国莲</t>
         </is>
       </c>
-      <c r="C65" s="2" t="inlineStr">
-        <is>
-          <t>三、潜力培育中</t>
-        </is>
-      </c>
-      <c r="D65" s="2" t="inlineStr"/>
-      <c r="E65" s="2" t="inlineStr"/>
-      <c r="F65" s="2" t="inlineStr"/>
-      <c r="G65" s="3" t="inlineStr"/>
-      <c r="H65" s="3" t="inlineStr"/>
-      <c r="I65" s="2" t="inlineStr"/>
-      <c r="J65" s="2" t="inlineStr"/>
-      <c r="K65" s="2" t="inlineStr"/>
-      <c r="L65" s="4" t="inlineStr">
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>三、潜力培育中</t>
+        </is>
+      </c>
+      <c r="D65" t="inlineStr"/>
+      <c r="E65" t="inlineStr"/>
+      <c r="F65" t="inlineStr"/>
+      <c r="G65" t="inlineStr"/>
+      <c r="H65" t="inlineStr"/>
+      <c r="I65" t="inlineStr"/>
+      <c r="J65" t="inlineStr"/>
+      <c r="K65" t="inlineStr"/>
+      <c r="L65" t="inlineStr">
         <is>
           <t>鱼价低迷，暂时停养。</t>
         </is>
       </c>
-      <c r="M65" s="4" t="inlineStr">
+      <c r="M65" t="inlineStr">
         <is>
           <t>持续服务培育，寻找切入时机</t>
         </is>
       </c>
     </row>
     <row r="66">
-      <c r="A66" s="2" t="n">
+      <c r="A66" t="n">
         <v>65</v>
       </c>
-      <c r="B66" s="2" t="inlineStr">
+      <c r="B66" t="inlineStr">
         <is>
           <t>符方宝</t>
         </is>
       </c>
-      <c r="C66" s="2" t="inlineStr">
-        <is>
-          <t>三、潜力培育中</t>
-        </is>
-      </c>
-      <c r="D66" s="2" t="inlineStr"/>
-      <c r="E66" s="2" t="inlineStr"/>
-      <c r="F66" s="2" t="inlineStr"/>
-      <c r="G66" s="3" t="inlineStr"/>
-      <c r="H66" s="3" t="inlineStr"/>
-      <c r="I66" s="2" t="inlineStr"/>
-      <c r="J66" s="2" t="inlineStr"/>
-      <c r="K66" s="2" t="inlineStr"/>
-      <c r="L66" s="4" t="inlineStr">
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>三、潜力培育中</t>
+        </is>
+      </c>
+      <c r="D66" t="inlineStr"/>
+      <c r="E66" t="inlineStr"/>
+      <c r="F66" t="inlineStr"/>
+      <c r="G66" t="inlineStr"/>
+      <c r="H66" t="inlineStr"/>
+      <c r="I66" t="inlineStr"/>
+      <c r="J66" t="inlineStr"/>
+      <c r="K66" t="inlineStr"/>
+      <c r="L66" t="inlineStr">
         <is>
           <t>已退出，之前养石斑鱼，现转养罗非。</t>
         </is>
       </c>
-      <c r="M66" s="4" t="inlineStr">
+      <c r="M66" t="inlineStr">
         <is>
           <t>持续服务培育，寻找切入时机</t>
         </is>
       </c>
     </row>
     <row r="67">
-      <c r="A67" s="2" t="n">
+      <c r="A67" t="n">
         <v>66</v>
       </c>
-      <c r="B67" s="2" t="inlineStr">
+      <c r="B67" t="inlineStr">
         <is>
           <t>王建斌</t>
         </is>
       </c>
-      <c r="C67" s="2" t="inlineStr">
-        <is>
-          <t>三、潜力培育中</t>
-        </is>
-      </c>
-      <c r="D67" s="2" t="inlineStr"/>
-      <c r="E67" s="2" t="inlineStr"/>
-      <c r="F67" s="2" t="inlineStr"/>
-      <c r="G67" s="3" t="inlineStr"/>
-      <c r="H67" s="3" t="inlineStr"/>
-      <c r="I67" s="2" t="inlineStr"/>
-      <c r="J67" s="2" t="inlineStr"/>
-      <c r="K67" s="2" t="inlineStr"/>
-      <c r="L67" s="4" t="inlineStr">
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>三、潜力培育中</t>
+        </is>
+      </c>
+      <c r="D67" t="inlineStr"/>
+      <c r="E67" t="inlineStr"/>
+      <c r="F67" t="inlineStr"/>
+      <c r="G67" t="inlineStr"/>
+      <c r="H67" t="inlineStr"/>
+      <c r="I67" t="inlineStr"/>
+      <c r="J67" t="inlineStr"/>
+      <c r="K67" t="inlineStr"/>
+      <c r="L67" t="inlineStr">
         <is>
           <t>塘口已更换老板。</t>
         </is>
       </c>
-      <c r="M67" s="4" t="inlineStr">
+      <c r="M67" t="inlineStr">
         <is>
           <t>持续服务培育，寻找切入时机</t>
         </is>
       </c>
     </row>
     <row r="68">
-      <c r="A68" s="2" t="n">
+      <c r="A68" t="n">
         <v>67</v>
       </c>
-      <c r="B68" s="2" t="inlineStr">
+      <c r="B68" t="inlineStr">
         <is>
           <t>云永虎</t>
         </is>
       </c>
-      <c r="C68" s="2" t="inlineStr">
-        <is>
-          <t>三、潜力培育中</t>
-        </is>
-      </c>
-      <c r="D68" s="2" t="inlineStr"/>
-      <c r="E68" s="2" t="n">
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>三、潜力培育中</t>
+        </is>
+      </c>
+      <c r="D68" t="inlineStr"/>
+      <c r="E68" t="n">
         <v>2</v>
       </c>
-      <c r="F68" s="2" t="inlineStr">
+      <c r="F68" t="inlineStr">
         <is>
           <t>50</t>
         </is>
       </c>
-      <c r="G68" s="3" t="inlineStr"/>
-      <c r="H68" s="3" t="inlineStr">
+      <c r="G68" t="inlineStr"/>
+      <c r="H68" t="inlineStr">
         <is>
           <t>黄友孝</t>
         </is>
       </c>
-      <c r="I68" s="2" t="inlineStr"/>
-      <c r="J68" s="2" t="inlineStr"/>
-      <c r="K68" s="2" t="inlineStr"/>
-      <c r="L68" s="4" t="inlineStr">
+      <c r="I68" t="inlineStr"/>
+      <c r="J68" t="inlineStr"/>
+      <c r="K68" t="inlineStr"/>
+      <c r="L68" t="inlineStr">
         <is>
           <t>转做畜禽养殖，两口塘约50亩，跟黄友孝拿料。</t>
         </is>
       </c>
-      <c r="M68" s="4" t="inlineStr">
+      <c r="M68" t="inlineStr">
         <is>
           <t>持续服务培育，寻找切入时机</t>
         </is>
       </c>
     </row>
     <row r="69">
-      <c r="A69" s="2" t="n">
+      <c r="A69" t="n">
         <v>68</v>
       </c>
-      <c r="B69" s="2" t="inlineStr">
+      <c r="B69" t="inlineStr">
         <is>
           <t>施君华</t>
         </is>
       </c>
-      <c r="C69" s="2" t="inlineStr">
-        <is>
-          <t>三、潜力培育中</t>
-        </is>
-      </c>
-      <c r="D69" s="2" t="inlineStr"/>
-      <c r="E69" s="2" t="inlineStr"/>
-      <c r="F69" s="2" t="inlineStr"/>
-      <c r="G69" s="3" t="inlineStr">
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>三、潜力培育中</t>
+        </is>
+      </c>
+      <c r="D69" t="inlineStr"/>
+      <c r="E69" t="inlineStr"/>
+      <c r="F69" t="inlineStr"/>
+      <c r="G69" t="inlineStr">
         <is>
           <t>唐人神（小料）、天翔819（大料）</t>
         </is>
       </c>
-      <c r="H69" s="3" t="inlineStr">
+      <c r="H69" t="inlineStr">
         <is>
           <t>原添祥、郑海杰，现待问清</t>
         </is>
       </c>
-      <c r="I69" s="2" t="inlineStr"/>
-      <c r="J69" s="2" t="inlineStr"/>
-      <c r="K69" s="2" t="inlineStr"/>
-      <c r="L69" s="4" t="inlineStr">
+      <c r="I69" t="inlineStr"/>
+      <c r="J69" t="inlineStr"/>
+      <c r="K69" t="inlineStr"/>
+      <c r="L69" t="inlineStr">
         <is>
           <t>10.09走访：用料已更换，现小料唐人神、大料天翔819（挂账价114，属低档料，判断难养出效果）；现跟谁拿料待问清。鱼苗和大头混养，宝路苗，鱼现八两左右，预计11月初出鱼。【名字确认：名单原“施军华”“司君华”均为同一人施君华；10.05客情维护走访】</t>
         </is>
       </c>
-      <c r="M69" s="4" t="inlineStr">
+      <c r="M69" t="inlineStr">
         <is>
           <t>11月初出鱼后回访，核实天翔819这造包产；问清现拿料对象；持续服务培育，寻找切入时机</t>
         </is>
       </c>
     </row>
     <row r="70">
-      <c r="A70" s="2" t="n">
+      <c r="A70" t="n">
         <v>69</v>
       </c>
-      <c r="B70" s="2" t="inlineStr">
+      <c r="B70" t="inlineStr">
         <is>
           <t>马小敏</t>
         </is>
       </c>
-      <c r="C70" s="2" t="inlineStr">
-        <is>
-          <t>三、潜力培育中</t>
-        </is>
-      </c>
-      <c r="D70" s="2" t="inlineStr"/>
-      <c r="E70" s="2" t="inlineStr"/>
-      <c r="F70" s="2" t="inlineStr"/>
-      <c r="G70" s="3" t="inlineStr"/>
-      <c r="H70" s="3" t="inlineStr"/>
-      <c r="I70" s="2" t="inlineStr"/>
-      <c r="J70" s="2" t="inlineStr"/>
-      <c r="K70" s="2" t="inlineStr"/>
-      <c r="L70" s="4" t="inlineStr">
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>三、潜力培育中</t>
+        </is>
+      </c>
+      <c r="D70" t="inlineStr"/>
+      <c r="E70" t="inlineStr"/>
+      <c r="F70" t="inlineStr"/>
+      <c r="G70" t="inlineStr"/>
+      <c r="H70" t="inlineStr"/>
+      <c r="I70" t="inlineStr"/>
+      <c r="J70" t="inlineStr"/>
+      <c r="K70" t="inlineStr"/>
+      <c r="L70" t="inlineStr">
         <is>
           <t>老客户维护。</t>
         </is>
       </c>
-      <c r="M70" s="4" t="inlineStr">
+      <c r="M70" t="inlineStr">
         <is>
           <t>持续服务培育，寻找切入时机</t>
         </is>
       </c>
     </row>
     <row r="71">
-      <c r="A71" s="2" t="n">
+      <c r="A71" t="n">
         <v>70</v>
       </c>
-      <c r="B71" s="2" t="inlineStr">
+      <c r="B71" t="inlineStr">
         <is>
           <t>朱龙军</t>
         </is>
       </c>
-      <c r="C71" s="2" t="inlineStr">
-        <is>
-          <t>三、潜力培育中</t>
-        </is>
-      </c>
-      <c r="D71" s="2" t="inlineStr"/>
-      <c r="E71" s="2" t="inlineStr"/>
-      <c r="F71" s="2" t="inlineStr"/>
-      <c r="G71" s="3" t="inlineStr"/>
-      <c r="H71" s="3" t="inlineStr"/>
-      <c r="I71" s="2" t="inlineStr"/>
-      <c r="J71" s="2" t="inlineStr"/>
-      <c r="K71" s="2" t="inlineStr"/>
-      <c r="L71" s="4" t="inlineStr">
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>三、潜力培育中</t>
+        </is>
+      </c>
+      <c r="D71" t="inlineStr"/>
+      <c r="E71" t="inlineStr"/>
+      <c r="F71" t="inlineStr"/>
+      <c r="G71" t="inlineStr"/>
+      <c r="H71" t="inlineStr"/>
+      <c r="I71" t="inlineStr"/>
+      <c r="J71" t="inlineStr"/>
+      <c r="K71" t="inlineStr"/>
+      <c r="L71" t="inlineStr">
         <is>
           <t>老客户维护。</t>
         </is>
       </c>
-      <c r="M71" s="4" t="inlineStr">
+      <c r="M71" t="inlineStr">
         <is>
           <t>持续服务培育，寻找切入时机</t>
         </is>
       </c>
     </row>
     <row r="72">
-      <c r="A72" s="2" t="n">
+      <c r="A72" t="n">
         <v>71</v>
       </c>
-      <c r="B72" s="2" t="inlineStr">
+      <c r="B72" t="inlineStr">
         <is>
           <t>应富伟</t>
         </is>
       </c>
-      <c r="C72" s="2" t="inlineStr">
-        <is>
-          <t>三、潜力培育中</t>
-        </is>
-      </c>
-      <c r="D72" s="2" t="inlineStr"/>
-      <c r="E72" s="2" t="inlineStr"/>
-      <c r="F72" s="2" t="inlineStr"/>
-      <c r="G72" s="3" t="inlineStr"/>
-      <c r="H72" s="3" t="inlineStr">
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>三、潜力培育中</t>
+        </is>
+      </c>
+      <c r="D72" t="inlineStr"/>
+      <c r="E72" t="inlineStr"/>
+      <c r="F72" t="inlineStr"/>
+      <c r="G72" t="inlineStr"/>
+      <c r="H72" t="inlineStr">
         <is>
           <t>马津深</t>
         </is>
       </c>
-      <c r="I72" s="2" t="inlineStr">
+      <c r="I72" t="inlineStr">
         <is>
           <t>父母及工人</t>
         </is>
       </c>
-      <c r="J72" s="2" t="inlineStr"/>
-      <c r="K72" s="2" t="inlineStr"/>
-      <c r="L72" s="4" t="inlineStr">
+      <c r="J72" t="inlineStr"/>
+      <c r="K72" t="inlineStr"/>
+      <c r="L72" t="inlineStr">
         <is>
           <t>跟马津深拿料，本人已回浙江，塘口由父母及工人负责。</t>
         </is>
       </c>
-      <c r="M72" s="4" t="inlineStr">
+      <c r="M72" t="inlineStr">
         <is>
           <t>持续服务培育，寻找切入时机</t>
         </is>
       </c>
     </row>
     <row r="73">
-      <c r="A73" s="2" t="n">
+      <c r="A73" t="n">
         <v>72</v>
       </c>
-      <c r="B73" s="2" t="inlineStr">
+      <c r="B73" t="inlineStr">
         <is>
           <t>朱龙君</t>
         </is>
       </c>
-      <c r="C73" s="2" t="inlineStr">
-        <is>
-          <t>三、潜力培育中</t>
-        </is>
-      </c>
-      <c r="D73" s="2" t="inlineStr"/>
-      <c r="E73" s="2" t="inlineStr"/>
-      <c r="F73" s="2" t="inlineStr"/>
-      <c r="G73" s="3" t="inlineStr">
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>三、潜力培育中</t>
+        </is>
+      </c>
+      <c r="D73" t="inlineStr"/>
+      <c r="E73" t="inlineStr"/>
+      <c r="F73" t="inlineStr"/>
+      <c r="G73" t="inlineStr">
         <is>
           <t>祥泰</t>
         </is>
       </c>
-      <c r="H73" s="3" t="inlineStr"/>
-      <c r="I73" s="2" t="inlineStr"/>
-      <c r="J73" s="2" t="inlineStr"/>
-      <c r="K73" s="2" t="inlineStr"/>
-      <c r="L73" s="4" t="inlineStr">
+      <c r="H73" t="inlineStr"/>
+      <c r="I73" t="inlineStr"/>
+      <c r="J73" t="inlineStr"/>
+      <c r="K73" t="inlineStr"/>
+      <c r="L73" t="inlineStr">
         <is>
           <t>祥泰料，老板不在。</t>
         </is>
       </c>
-      <c r="M73" s="4" t="inlineStr">
+      <c r="M73" t="inlineStr">
         <is>
           <t>持续服务培育，寻找切入时机</t>
         </is>
       </c>
     </row>
     <row r="74">
-      <c r="A74" s="2" t="n">
+      <c r="A74" t="n">
         <v>73</v>
       </c>
-      <c r="B74" s="2" t="inlineStr">
+      <c r="B74" t="inlineStr">
         <is>
           <t>陈焕新</t>
         </is>
       </c>
-      <c r="C74" s="2" t="inlineStr">
-        <is>
-          <t>三、潜力培育中</t>
-        </is>
-      </c>
-      <c r="D74" s="2" t="inlineStr"/>
-      <c r="E74" s="2" t="inlineStr"/>
-      <c r="F74" s="2" t="inlineStr"/>
-      <c r="G74" s="3" t="inlineStr">
+      <c r="C74" t="inlineStr">
+        <is>
+          <t>三、潜力培育中</t>
+        </is>
+      </c>
+      <c r="D74" t="inlineStr"/>
+      <c r="E74" t="inlineStr"/>
+      <c r="F74" t="inlineStr"/>
+      <c r="G74" t="inlineStr">
         <is>
           <t>百洋</t>
         </is>
       </c>
-      <c r="H74" s="3" t="inlineStr"/>
-      <c r="I74" s="2" t="inlineStr"/>
-      <c r="J74" s="2" t="inlineStr"/>
-      <c r="K74" s="2" t="inlineStr"/>
-      <c r="L74" s="4" t="inlineStr">
+      <c r="H74" t="inlineStr"/>
+      <c r="I74" t="inlineStr"/>
+      <c r="J74" t="inlineStr"/>
+      <c r="K74" t="inlineStr"/>
+      <c r="L74" t="inlineStr">
         <is>
           <t>用过通威、嫌贵，现用百洋。</t>
         </is>
       </c>
-      <c r="M74" s="4" t="inlineStr">
+      <c r="M74" t="inlineStr">
         <is>
           <t>持续服务培育，寻找切入时机</t>
         </is>
       </c>
     </row>
     <row r="75">
-      <c r="A75" s="2" t="n">
+      <c r="A75" t="n">
         <v>74</v>
       </c>
-      <c r="B75" s="2" t="inlineStr">
+      <c r="B75" t="inlineStr">
         <is>
           <t>陈金伟</t>
         </is>
       </c>
-      <c r="C75" s="2" t="inlineStr">
-        <is>
-          <t>三、潜力培育中</t>
-        </is>
-      </c>
-      <c r="D75" s="2" t="inlineStr"/>
-      <c r="E75" s="2" t="inlineStr"/>
-      <c r="F75" s="2" t="inlineStr"/>
-      <c r="G75" s="3" t="inlineStr"/>
-      <c r="H75" s="3" t="inlineStr"/>
-      <c r="I75" s="2" t="inlineStr"/>
-      <c r="J75" s="2" t="inlineStr"/>
-      <c r="K75" s="2" t="inlineStr"/>
-      <c r="L75" s="4" t="inlineStr">
+      <c r="C75" t="inlineStr">
+        <is>
+          <t>三、潜力培育中</t>
+        </is>
+      </c>
+      <c r="D75" t="inlineStr"/>
+      <c r="E75" t="inlineStr"/>
+      <c r="F75" t="inlineStr"/>
+      <c r="G75" t="inlineStr"/>
+      <c r="H75" t="inlineStr"/>
+      <c r="I75" t="inlineStr"/>
+      <c r="J75" t="inlineStr"/>
+      <c r="K75" t="inlineStr"/>
+      <c r="L75" t="inlineStr">
         <is>
           <t>外出不在。</t>
         </is>
       </c>
-      <c r="M75" s="4" t="inlineStr">
+      <c r="M75" t="inlineStr">
         <is>
           <t>持续服务培育，寻找切入时机</t>
         </is>
       </c>
     </row>
     <row r="76">
-      <c r="A76" s="2" t="n">
+      <c r="A76" t="n">
         <v>75</v>
       </c>
-      <c r="B76" s="2" t="inlineStr">
+      <c r="B76" t="inlineStr">
         <is>
           <t>郭仁和</t>
         </is>
       </c>
-      <c r="C76" s="2" t="inlineStr">
-        <is>
-          <t>三、潜力培育中</t>
-        </is>
-      </c>
-      <c r="D76" s="2" t="inlineStr"/>
-      <c r="E76" s="2" t="inlineStr"/>
-      <c r="F76" s="2" t="inlineStr"/>
-      <c r="G76" s="3" t="inlineStr">
+      <c r="C76" t="inlineStr">
+        <is>
+          <t>三、潜力培育中</t>
+        </is>
+      </c>
+      <c r="D76" t="inlineStr"/>
+      <c r="E76" t="inlineStr"/>
+      <c r="F76" t="inlineStr"/>
+      <c r="G76" t="inlineStr">
         <is>
           <t>通力</t>
         </is>
       </c>
-      <c r="H76" s="3" t="inlineStr"/>
-      <c r="I76" s="2" t="inlineStr"/>
-      <c r="J76" s="2" t="inlineStr"/>
-      <c r="K76" s="2" t="inlineStr"/>
-      <c r="L76" s="4" t="inlineStr">
+      <c r="H76" t="inlineStr"/>
+      <c r="I76" t="inlineStr"/>
+      <c r="J76" t="inlineStr"/>
+      <c r="K76" t="inlineStr"/>
+      <c r="L76" t="inlineStr">
         <is>
           <t>畜禽养殖，通力413。</t>
         </is>
       </c>
-      <c r="M76" s="4" t="inlineStr">
+      <c r="M76" t="inlineStr">
         <is>
           <t>持续服务培育，寻找切入时机</t>
         </is>
       </c>
     </row>
     <row r="77">
-      <c r="A77" s="2" t="n">
+      <c r="A77" t="n">
         <v>76</v>
       </c>
-      <c r="B77" s="2" t="inlineStr">
+      <c r="B77" t="inlineStr">
         <is>
           <t>周精明</t>
         </is>
       </c>
-      <c r="C77" s="2" t="inlineStr">
-        <is>
-          <t>三、潜力培育中</t>
-        </is>
-      </c>
-      <c r="D77" s="2" t="inlineStr"/>
-      <c r="E77" s="2" t="inlineStr"/>
-      <c r="F77" s="2" t="inlineStr"/>
-      <c r="G77" s="3" t="inlineStr">
+      <c r="C77" t="inlineStr">
+        <is>
+          <t>三、潜力培育中</t>
+        </is>
+      </c>
+      <c r="D77" t="inlineStr"/>
+      <c r="E77" t="inlineStr"/>
+      <c r="F77" t="inlineStr"/>
+      <c r="G77" t="inlineStr">
         <is>
           <t>鸿业</t>
         </is>
       </c>
-      <c r="H77" s="3" t="inlineStr"/>
-      <c r="I77" s="2" t="inlineStr"/>
-      <c r="J77" s="2" t="inlineStr"/>
-      <c r="K77" s="2" t="inlineStr"/>
-      <c r="L77" s="4" t="inlineStr">
+      <c r="H77" t="inlineStr"/>
+      <c r="I77" t="inlineStr"/>
+      <c r="J77" t="inlineStr"/>
+      <c r="K77" t="inlineStr"/>
+      <c r="L77" t="inlineStr">
         <is>
           <t>做种苗，海南一号种苗，鸿业粉料。</t>
         </is>
       </c>
-      <c r="M77" s="4" t="inlineStr">
+      <c r="M77" t="inlineStr">
         <is>
           <t>持续服务培育，寻找切入时机</t>
         </is>
       </c>
     </row>
     <row r="78">
-      <c r="A78" s="2" t="n">
+      <c r="A78" t="n">
         <v>77</v>
       </c>
-      <c r="B78" s="2" t="inlineStr">
+      <c r="B78" t="inlineStr">
         <is>
           <t>李哥</t>
         </is>
       </c>
-      <c r="C78" s="2" t="inlineStr">
-        <is>
-          <t>三、潜力培育中</t>
-        </is>
-      </c>
-      <c r="D78" s="2" t="inlineStr"/>
-      <c r="E78" s="2" t="inlineStr"/>
-      <c r="F78" s="2" t="inlineStr">
+      <c r="C78" t="inlineStr">
+        <is>
+          <t>三、潜力培育中</t>
+        </is>
+      </c>
+      <c r="D78" t="inlineStr"/>
+      <c r="E78" t="inlineStr"/>
+      <c r="F78" t="inlineStr">
         <is>
           <t>40</t>
         </is>
       </c>
-      <c r="G78" s="3" t="inlineStr"/>
-      <c r="H78" s="3" t="inlineStr">
+      <c r="G78" t="inlineStr"/>
+      <c r="H78" t="inlineStr">
         <is>
           <t>周公保</t>
         </is>
       </c>
-      <c r="I78" s="2" t="inlineStr"/>
-      <c r="J78" s="2" t="inlineStr"/>
-      <c r="K78" s="2" t="inlineStr"/>
-      <c r="L78" s="4" t="inlineStr">
+      <c r="I78" t="inlineStr"/>
+      <c r="J78" t="inlineStr"/>
+      <c r="K78" t="inlineStr"/>
+      <c r="L78" t="inlineStr">
         <is>
           <t>40亩左右，跟周公保拿料。</t>
         </is>
       </c>
-      <c r="M78" s="4" t="inlineStr">
+      <c r="M78" t="inlineStr">
         <is>
           <t>持续服务培育，寻找切入时机</t>
         </is>
       </c>
     </row>
     <row r="79">
-      <c r="A79" s="2" t="n">
+      <c r="A79" t="n">
         <v>78</v>
       </c>
-      <c r="B79" s="2" t="inlineStr">
+      <c r="B79" t="inlineStr">
         <is>
           <t>冯学新</t>
         </is>
       </c>
-      <c r="C79" s="2" t="inlineStr">
-        <is>
-          <t>三、潜力培育中</t>
-        </is>
-      </c>
-      <c r="D79" s="2" t="inlineStr"/>
-      <c r="E79" s="2" t="inlineStr"/>
-      <c r="F79" s="2" t="inlineStr"/>
-      <c r="G79" s="3" t="inlineStr">
+      <c r="C79" t="inlineStr">
+        <is>
+          <t>三、潜力培育中</t>
+        </is>
+      </c>
+      <c r="D79" t="inlineStr"/>
+      <c r="E79" t="inlineStr"/>
+      <c r="F79" t="inlineStr"/>
+      <c r="G79" t="inlineStr">
         <is>
           <t>百洋5602</t>
         </is>
       </c>
-      <c r="H79" s="3" t="inlineStr"/>
-      <c r="I79" s="2" t="inlineStr"/>
-      <c r="J79" s="2" t="inlineStr"/>
-      <c r="K79" s="2" t="inlineStr"/>
-      <c r="L79" s="4" t="inlineStr">
+      <c r="H79" t="inlineStr"/>
+      <c r="I79" t="inlineStr"/>
+      <c r="J79" t="inlineStr"/>
+      <c r="K79" t="inlineStr"/>
+      <c r="L79" t="inlineStr">
         <is>
           <t>百洋5602，二两鱼。 【10.07补充：冯学新兼做歌颂料渠道，吴杨松跟其拿现金料105元/包；其本人仍用百洋5602】</t>
         </is>
       </c>
-      <c r="M79" s="4" t="inlineStr">
+      <c r="M79" t="inlineStr">
         <is>
           <t>持续服务培育，寻找切入时机</t>
         </is>
       </c>
     </row>
     <row r="80">
-      <c r="A80" s="2" t="n">
+      <c r="A80" t="n">
         <v>79</v>
       </c>
-      <c r="B80" s="2" t="inlineStr">
+      <c r="B80" t="inlineStr">
         <is>
           <t>张桂平</t>
         </is>
       </c>
-      <c r="C80" s="2" t="inlineStr">
-        <is>
-          <t>三、潜力培育中</t>
-        </is>
-      </c>
-      <c r="D80" s="2" t="inlineStr"/>
-      <c r="E80" s="2" t="inlineStr"/>
-      <c r="F80" s="2" t="inlineStr"/>
-      <c r="G80" s="3" t="inlineStr">
+      <c r="C80" t="inlineStr">
+        <is>
+          <t>三、潜力培育中</t>
+        </is>
+      </c>
+      <c r="D80" t="inlineStr"/>
+      <c r="E80" t="inlineStr"/>
+      <c r="F80" t="inlineStr"/>
+      <c r="G80" t="inlineStr">
         <is>
           <t>百洋</t>
         </is>
       </c>
-      <c r="H80" s="3" t="inlineStr"/>
-      <c r="I80" s="2" t="inlineStr"/>
-      <c r="J80" s="2" t="inlineStr"/>
-      <c r="K80" s="2" t="inlineStr"/>
-      <c r="L80" s="4" t="inlineStr">
+      <c r="H80" t="inlineStr"/>
+      <c r="I80" t="inlineStr"/>
+      <c r="J80" t="inlineStr"/>
+      <c r="K80" t="inlineStr"/>
+      <c r="L80" t="inlineStr">
         <is>
           <t>百洋，二两鱼。</t>
         </is>
       </c>
-      <c r="M80" s="4" t="inlineStr">
+      <c r="M80" t="inlineStr">
         <is>
           <t>持续服务培育，寻找切入时机</t>
         </is>
       </c>
     </row>
     <row r="81">
-      <c r="A81" s="2" t="n">
+      <c r="A81" t="n">
         <v>80</v>
       </c>
-      <c r="B81" s="2" t="inlineStr">
+      <c r="B81" t="inlineStr">
         <is>
           <t>沈方勇</t>
         </is>
       </c>
-      <c r="C81" s="2" t="inlineStr">
-        <is>
-          <t>三、潜力培育中</t>
-        </is>
-      </c>
-      <c r="D81" s="2" t="inlineStr"/>
-      <c r="E81" s="2" t="inlineStr"/>
-      <c r="F81" s="2" t="inlineStr"/>
-      <c r="G81" s="3" t="inlineStr">
+      <c r="C81" t="inlineStr">
+        <is>
+          <t>三、潜力培育中</t>
+        </is>
+      </c>
+      <c r="D81" t="inlineStr"/>
+      <c r="E81" t="inlineStr"/>
+      <c r="F81" t="inlineStr"/>
+      <c r="G81" t="inlineStr">
         <is>
           <t>百洋5602</t>
         </is>
       </c>
-      <c r="H81" s="3" t="inlineStr"/>
-      <c r="I81" s="2" t="inlineStr"/>
-      <c r="J81" s="2" t="inlineStr"/>
-      <c r="K81" s="2" t="inlineStr"/>
-      <c r="L81" s="4" t="inlineStr">
+      <c r="H81" t="inlineStr"/>
+      <c r="I81" t="inlineStr"/>
+      <c r="J81" t="inlineStr"/>
+      <c r="K81" t="inlineStr"/>
+      <c r="L81" t="inlineStr">
         <is>
           <t>百洋5602和百洋小料。</t>
         </is>
       </c>
-      <c r="M81" s="4" t="inlineStr">
+      <c r="M81" t="inlineStr">
         <is>
           <t>持续服务培育，寻找切入时机</t>
         </is>
       </c>
     </row>
     <row r="82">
-      <c r="A82" s="2" t="n">
+      <c r="A82" t="n">
         <v>81</v>
       </c>
-      <c r="B82" s="2" t="inlineStr">
+      <c r="B82" t="inlineStr">
         <is>
           <t>麻振威</t>
         </is>
       </c>
-      <c r="C82" s="2" t="inlineStr">
-        <is>
-          <t>三、潜力培育中</t>
-        </is>
-      </c>
-      <c r="D82" s="2" t="inlineStr"/>
-      <c r="E82" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="F82" s="2" t="inlineStr"/>
-      <c r="G82" s="3" t="inlineStr">
+      <c r="C82" t="inlineStr">
+        <is>
+          <t>三、潜力培育中</t>
+        </is>
+      </c>
+      <c r="D82" t="inlineStr"/>
+      <c r="E82" t="n">
+        <v>5</v>
+      </c>
+      <c r="F82" t="inlineStr"/>
+      <c r="G82" t="inlineStr">
         <is>
           <t>百洋5602</t>
         </is>
       </c>
-      <c r="H82" s="3" t="inlineStr"/>
-      <c r="I82" s="2" t="inlineStr"/>
-      <c r="J82" s="2" t="inlineStr"/>
-      <c r="K82" s="2" t="inlineStr"/>
-      <c r="L82" s="4" t="inlineStr">
+      <c r="H82" t="inlineStr"/>
+      <c r="I82" t="inlineStr"/>
+      <c r="J82" t="inlineStr"/>
+      <c r="K82" t="inlineStr"/>
+      <c r="L82" t="inlineStr">
         <is>
           <t>百洋5602，5口塘加1口苗塘，鱼1.2斤，宝路苗。</t>
         </is>
       </c>
-      <c r="M82" s="4" t="inlineStr">
+      <c r="M82" t="inlineStr">
         <is>
           <t>持续服务培育，寻找切入时机</t>
         </is>
       </c>
     </row>
     <row r="83">
-      <c r="A83" s="2" t="n">
+      <c r="A83" t="n">
         <v>82</v>
       </c>
-      <c r="B83" s="2" t="inlineStr">
+      <c r="B83" t="inlineStr">
         <is>
           <t>齐陈夫妇</t>
         </is>
       </c>
-      <c r="C83" s="2" t="inlineStr">
-        <is>
-          <t>三、潜力培育中</t>
-        </is>
-      </c>
-      <c r="D83" s="2" t="inlineStr"/>
-      <c r="E83" s="2" t="inlineStr"/>
-      <c r="F83" s="2" t="inlineStr"/>
-      <c r="G83" s="3" t="inlineStr">
+      <c r="C83" t="inlineStr">
+        <is>
+          <t>三、潜力培育中</t>
+        </is>
+      </c>
+      <c r="D83" t="inlineStr"/>
+      <c r="E83" t="inlineStr"/>
+      <c r="F83" t="inlineStr"/>
+      <c r="G83" t="inlineStr">
         <is>
           <t>粤海2号</t>
         </is>
       </c>
-      <c r="H83" s="3" t="inlineStr">
+      <c r="H83" t="inlineStr">
         <is>
           <t>符策锋</t>
         </is>
       </c>
-      <c r="I83" s="2" t="inlineStr"/>
-      <c r="J83" s="2" t="inlineStr"/>
-      <c r="K83" s="2" t="inlineStr"/>
-      <c r="L83" s="4" t="inlineStr">
+      <c r="I83" t="inlineStr"/>
+      <c r="J83" t="inlineStr"/>
+      <c r="K83" t="inlineStr"/>
+      <c r="L83" t="inlineStr">
         <is>
           <t>跟符策锋拿料，粤海2号料，之前在锦山养亏较多。</t>
         </is>
       </c>
-      <c r="M83" s="4" t="inlineStr">
+      <c r="M83" t="inlineStr">
         <is>
           <t>持续服务培育，寻找切入时机</t>
         </is>
       </c>
     </row>
     <row r="84">
-      <c r="A84" s="2" t="n">
+      <c r="A84" t="n">
         <v>83</v>
       </c>
-      <c r="B84" s="2" t="inlineStr">
+      <c r="B84" t="inlineStr">
         <is>
           <t>何龙之</t>
         </is>
       </c>
-      <c r="C84" s="2" t="inlineStr">
-        <is>
-          <t>三、潜力培育中</t>
-        </is>
-      </c>
-      <c r="D84" s="2" t="inlineStr"/>
-      <c r="E84" s="2" t="n">
+      <c r="C84" t="inlineStr">
+        <is>
+          <t>三、潜力培育中</t>
+        </is>
+      </c>
+      <c r="D84" t="inlineStr"/>
+      <c r="E84" t="n">
         <v>2</v>
       </c>
-      <c r="F84" s="2" t="inlineStr"/>
-      <c r="G84" s="3" t="inlineStr">
+      <c r="F84" t="inlineStr"/>
+      <c r="G84" t="inlineStr">
         <is>
           <t>粤海</t>
         </is>
       </c>
-      <c r="H84" s="3" t="inlineStr"/>
-      <c r="I84" s="2" t="inlineStr"/>
-      <c r="J84" s="2" t="inlineStr"/>
-      <c r="K84" s="2" t="inlineStr">
+      <c r="H84" t="inlineStr"/>
+      <c r="I84" t="inlineStr"/>
+      <c r="J84" t="inlineStr"/>
+      <c r="K84" t="inlineStr">
         <is>
           <t>41</t>
         </is>
       </c>
-      <c r="L84" s="4" t="inlineStr">
+      <c r="L84" t="inlineStr">
         <is>
           <t>粤海，两口塘，一口抓41。</t>
         </is>
       </c>
-      <c r="M84" s="4" t="inlineStr">
+      <c r="M84" t="inlineStr">
         <is>
           <t>持续服务培育，寻找切入时机</t>
         </is>
       </c>
     </row>
     <row r="85">
-      <c r="A85" s="2" t="n">
+      <c r="A85" t="n">
         <v>84</v>
       </c>
-      <c r="B85" s="2" t="inlineStr">
+      <c r="B85" t="inlineStr">
         <is>
           <t>符叔宝</t>
         </is>
       </c>
-      <c r="C85" s="2" t="inlineStr">
-        <is>
-          <t>三、潜力培育中</t>
-        </is>
-      </c>
-      <c r="D85" s="2" t="inlineStr"/>
-      <c r="E85" s="2" t="inlineStr"/>
-      <c r="F85" s="2" t="inlineStr"/>
-      <c r="G85" s="3" t="inlineStr">
+      <c r="C85" t="inlineStr">
+        <is>
+          <t>三、潜力培育中</t>
+        </is>
+      </c>
+      <c r="D85" t="inlineStr"/>
+      <c r="E85" t="inlineStr"/>
+      <c r="F85" t="inlineStr"/>
+      <c r="G85" t="inlineStr">
         <is>
           <t>海大2552</t>
         </is>
       </c>
-      <c r="H85" s="3" t="inlineStr"/>
-      <c r="I85" s="2" t="inlineStr"/>
-      <c r="J85" s="2" t="inlineStr"/>
-      <c r="K85" s="2" t="inlineStr"/>
-      <c r="L85" s="4" t="inlineStr">
+      <c r="H85" t="inlineStr"/>
+      <c r="I85" t="inlineStr"/>
+      <c r="J85" t="inlineStr"/>
+      <c r="K85" t="inlineStr"/>
+      <c r="L85" t="inlineStr">
         <is>
           <t>海大2552，八两鱼。</t>
         </is>
       </c>
-      <c r="M85" s="4" t="inlineStr">
+      <c r="M85" t="inlineStr">
         <is>
           <t>持续服务培育，寻找切入时机</t>
         </is>
       </c>
     </row>
     <row r="86">
-      <c r="A86" s="2" t="n">
+      <c r="A86" t="n">
         <v>85</v>
       </c>
-      <c r="B86" s="2" t="inlineStr">
+      <c r="B86" t="inlineStr">
         <is>
           <t>丁缙南</t>
         </is>
       </c>
-      <c r="C86" s="2" t="inlineStr">
-        <is>
-          <t>三、潜力培育中</t>
-        </is>
-      </c>
-      <c r="D86" s="2" t="inlineStr"/>
-      <c r="E86" s="2" t="n">
+      <c r="C86" t="inlineStr">
+        <is>
+          <t>三、潜力培育中</t>
+        </is>
+      </c>
+      <c r="D86" t="inlineStr"/>
+      <c r="E86" t="n">
         <v>6</v>
       </c>
-      <c r="F86" s="2" t="inlineStr"/>
-      <c r="G86" s="3" t="inlineStr">
+      <c r="F86" t="inlineStr"/>
+      <c r="G86" t="inlineStr">
         <is>
           <t>粤海</t>
         </is>
       </c>
-      <c r="H86" s="3" t="inlineStr"/>
-      <c r="I86" s="2" t="inlineStr"/>
-      <c r="J86" s="2" t="inlineStr"/>
-      <c r="K86" s="2" t="inlineStr">
+      <c r="H86" t="inlineStr"/>
+      <c r="I86" t="inlineStr"/>
+      <c r="J86" t="inlineStr"/>
+      <c r="K86" t="inlineStr">
         <is>
           <t>40</t>
         </is>
       </c>
-      <c r="L86" s="4" t="inlineStr">
+      <c r="L86" t="inlineStr">
         <is>
           <t>经销商，粤海混料，六口塘，三两鱼，上一兆40出头不理想。</t>
         </is>
       </c>
-      <c r="M86" s="4" t="inlineStr">
+      <c r="M86" t="inlineStr">
         <is>
           <t>持续服务培育，寻找切入时机</t>
         </is>
       </c>
     </row>
     <row r="87">
-      <c r="A87" s="2" t="n">
+      <c r="A87" t="n">
         <v>86</v>
       </c>
-      <c r="B87" s="2" t="inlineStr">
+      <c r="B87" t="inlineStr">
         <is>
           <t>唐富顺</t>
         </is>
       </c>
-      <c r="C87" s="2" t="inlineStr">
-        <is>
-          <t>三、潜力培育中</t>
-        </is>
-      </c>
-      <c r="D87" s="2" t="inlineStr">
+      <c r="C87" t="inlineStr">
+        <is>
+          <t>三、潜力培育中</t>
+        </is>
+      </c>
+      <c r="D87" t="inlineStr">
         <is>
           <t>抱罗基地</t>
         </is>
       </c>
-      <c r="E87" s="2" t="inlineStr"/>
-      <c r="F87" s="2" t="inlineStr">
+      <c r="E87" t="inlineStr"/>
+      <c r="F87" t="inlineStr">
         <is>
           <t>100多</t>
         </is>
       </c>
-      <c r="G87" s="3" t="inlineStr">
+      <c r="G87" t="inlineStr">
         <is>
           <t>海一</t>
         </is>
       </c>
-      <c r="H87" s="3" t="inlineStr"/>
-      <c r="I87" s="2" t="inlineStr"/>
-      <c r="J87" s="2" t="inlineStr"/>
-      <c r="K87" s="2" t="inlineStr"/>
-      <c r="L87" s="4" t="inlineStr">
+      <c r="H87" t="inlineStr"/>
+      <c r="I87" t="inlineStr"/>
+      <c r="J87" t="inlineStr"/>
+      <c r="K87" t="inlineStr"/>
+      <c r="L87" t="inlineStr">
         <is>
           <t>100多亩，抱罗基地已换海一料。</t>
         </is>
       </c>
-      <c r="M87" s="4" t="inlineStr">
+      <c r="M87" t="inlineStr">
         <is>
           <t>持续服务培育，寻找切入时机</t>
         </is>
       </c>
     </row>
     <row r="88">
-      <c r="A88" s="2" t="n">
+      <c r="A88" t="n">
         <v>87</v>
       </c>
-      <c r="B88" s="2" t="inlineStr">
+      <c r="B88" t="inlineStr">
         <is>
           <t>何景东</t>
         </is>
       </c>
-      <c r="C88" s="2" t="inlineStr">
-        <is>
-          <t>三、潜力培育中</t>
-        </is>
-      </c>
-      <c r="D88" s="2" t="inlineStr"/>
-      <c r="E88" s="2" t="inlineStr"/>
-      <c r="F88" s="2" t="inlineStr">
+      <c r="C88" t="inlineStr">
+        <is>
+          <t>三、潜力培育中</t>
+        </is>
+      </c>
+      <c r="D88" t="inlineStr"/>
+      <c r="E88" t="inlineStr"/>
+      <c r="F88" t="inlineStr">
         <is>
           <t>25</t>
         </is>
       </c>
-      <c r="G88" s="3" t="inlineStr"/>
-      <c r="H88" s="3" t="inlineStr"/>
-      <c r="I88" s="2" t="inlineStr"/>
-      <c r="J88" s="2" t="inlineStr"/>
-      <c r="K88" s="2" t="inlineStr"/>
-      <c r="L88" s="4" t="inlineStr">
+      <c r="G88" t="inlineStr"/>
+      <c r="H88" t="inlineStr"/>
+      <c r="I88" t="inlineStr"/>
+      <c r="J88" t="inlineStr"/>
+      <c r="K88" t="inlineStr"/>
+      <c r="L88" t="inlineStr">
         <is>
           <t>罗非母鱼塘25亩，用料少。</t>
         </is>
       </c>
-      <c r="M88" s="4" t="inlineStr">
+      <c r="M88" t="inlineStr">
         <is>
           <t>持续服务培育，寻找切入时机</t>
         </is>
       </c>
     </row>
     <row r="89">
-      <c r="A89" s="2" t="n">
+      <c r="A89" t="n">
         <v>88</v>
       </c>
-      <c r="B89" s="2" t="inlineStr">
+      <c r="B89" t="inlineStr">
         <is>
           <t>周公宝基地</t>
         </is>
       </c>
-      <c r="C89" s="2" t="inlineStr">
-        <is>
-          <t>三、潜力培育中</t>
-        </is>
-      </c>
-      <c r="D89" s="2" t="inlineStr"/>
-      <c r="E89" s="2" t="n">
+      <c r="C89" t="inlineStr">
+        <is>
+          <t>三、潜力培育中</t>
+        </is>
+      </c>
+      <c r="D89" t="inlineStr"/>
+      <c r="E89" t="n">
         <v>1</v>
       </c>
-      <c r="F89" s="2" t="inlineStr">
+      <c r="F89" t="inlineStr">
         <is>
           <t>45</t>
         </is>
       </c>
-      <c r="G89" s="3" t="inlineStr"/>
-      <c r="H89" s="3" t="inlineStr"/>
-      <c r="I89" s="2" t="inlineStr"/>
-      <c r="J89" s="2" t="inlineStr"/>
-      <c r="K89" s="2" t="inlineStr"/>
-      <c r="L89" s="4" t="inlineStr">
+      <c r="G89" t="inlineStr"/>
+      <c r="H89" t="inlineStr"/>
+      <c r="I89" t="inlineStr"/>
+      <c r="J89" t="inlineStr"/>
+      <c r="K89" t="inlineStr"/>
+      <c r="L89" t="inlineStr">
         <is>
           <t>45亩一口塘，老板指定拿料。</t>
         </is>
       </c>
-      <c r="M89" s="4" t="inlineStr">
+      <c r="M89" t="inlineStr">
         <is>
           <t>持续服务培育，寻找切入时机</t>
         </is>
       </c>
     </row>
     <row r="90">
-      <c r="A90" s="2" t="n">
+      <c r="A90" t="n">
         <v>89</v>
       </c>
-      <c r="B90" s="2" t="inlineStr">
+      <c r="B90" t="inlineStr">
         <is>
           <t>郑海杰</t>
         </is>
       </c>
-      <c r="C90" s="2" t="inlineStr">
-        <is>
-          <t>三、潜力培育中</t>
-        </is>
-      </c>
-      <c r="D90" s="2" t="inlineStr"/>
-      <c r="E90" s="2" t="inlineStr"/>
-      <c r="F90" s="2" t="inlineStr"/>
-      <c r="G90" s="3" t="inlineStr">
+      <c r="C90" t="inlineStr">
+        <is>
+          <t>三、潜力培育中</t>
+        </is>
+      </c>
+      <c r="D90" t="inlineStr"/>
+      <c r="E90" t="inlineStr"/>
+      <c r="F90" t="inlineStr"/>
+      <c r="G90" t="inlineStr">
         <is>
           <t>祥泰</t>
         </is>
       </c>
-      <c r="H90" s="3" t="inlineStr"/>
-      <c r="I90" s="2" t="inlineStr"/>
-      <c r="J90" s="2" t="inlineStr"/>
-      <c r="K90" s="2" t="inlineStr"/>
-      <c r="L90" s="4" t="inlineStr">
+      <c r="H90" t="inlineStr"/>
+      <c r="I90" t="inlineStr"/>
+      <c r="J90" t="inlineStr"/>
+      <c r="K90" t="inlineStr"/>
+      <c r="L90" t="inlineStr">
         <is>
           <t>经销商，主营叉尾，祥泰料，上一造效果不理想。</t>
         </is>
       </c>
-      <c r="M90" s="4" t="inlineStr">
+      <c r="M90" t="inlineStr">
         <is>
           <t>持续服务培育，寻找切入时机</t>
         </is>
       </c>
     </row>
     <row r="91">
-      <c r="A91" s="2" t="n">
+      <c r="A91" t="n">
         <v>90</v>
       </c>
-      <c r="B91" s="2" t="inlineStr">
+      <c r="B91" t="inlineStr">
         <is>
           <t>陶敏川</t>
         </is>
       </c>
-      <c r="C91" s="2" t="inlineStr">
-        <is>
-          <t>三、潜力培育中</t>
-        </is>
-      </c>
-      <c r="D91" s="2" t="inlineStr">
+      <c r="C91" t="inlineStr">
+        <is>
+          <t>三、潜力培育中</t>
+        </is>
+      </c>
+      <c r="D91" t="inlineStr">
         <is>
           <t>凤尾</t>
         </is>
       </c>
-      <c r="E91" s="2" t="n">
+      <c r="E91" t="n">
         <v>1</v>
       </c>
-      <c r="F91" s="2" t="inlineStr"/>
-      <c r="G91" s="3" t="inlineStr">
+      <c r="F91" t="inlineStr"/>
+      <c r="G91" t="inlineStr">
         <is>
           <t>百洋</t>
         </is>
       </c>
-      <c r="H91" s="3" t="inlineStr"/>
-      <c r="I91" s="2" t="inlineStr"/>
-      <c r="J91" s="2" t="inlineStr"/>
-      <c r="K91" s="2" t="inlineStr"/>
-      <c r="L91" s="4" t="inlineStr">
+      <c r="H91" t="inlineStr"/>
+      <c r="I91" t="inlineStr"/>
+      <c r="J91" t="inlineStr"/>
+      <c r="K91" t="inlineStr"/>
+      <c r="L91" t="inlineStr">
         <is>
           <t>百洋用户，另有一口塘在凤尾在建。</t>
         </is>
       </c>
-      <c r="M91" s="4" t="inlineStr">
+      <c r="M91" t="inlineStr">
         <is>
           <t>持续服务培育，寻找切入时机</t>
         </is>
       </c>
     </row>
     <row r="92">
-      <c r="A92" s="2" t="n">
+      <c r="A92" t="n">
         <v>91</v>
       </c>
-      <c r="B92" s="2" t="inlineStr">
+      <c r="B92" t="inlineStr">
         <is>
           <t>陈承旺</t>
         </is>
       </c>
-      <c r="C92" s="2" t="inlineStr">
-        <is>
-          <t>三、潜力培育中</t>
-        </is>
-      </c>
-      <c r="D92" s="2" t="inlineStr">
+      <c r="C92" t="inlineStr">
+        <is>
+          <t>三、潜力培育中</t>
+        </is>
+      </c>
+      <c r="D92" t="inlineStr">
         <is>
           <t>海大基地</t>
         </is>
       </c>
-      <c r="E92" s="2" t="inlineStr"/>
-      <c r="F92" s="2" t="inlineStr"/>
-      <c r="G92" s="3" t="inlineStr">
+      <c r="E92" t="inlineStr"/>
+      <c r="F92" t="inlineStr"/>
+      <c r="G92" t="inlineStr">
         <is>
           <t>海大</t>
         </is>
       </c>
-      <c r="H92" s="3" t="inlineStr"/>
-      <c r="I92" s="2" t="inlineStr"/>
-      <c r="J92" s="2" t="inlineStr"/>
-      <c r="K92" s="2" t="inlineStr"/>
-      <c r="L92" s="4" t="inlineStr">
+      <c r="H92" t="inlineStr"/>
+      <c r="I92" t="inlineStr"/>
+      <c r="J92" t="inlineStr"/>
+      <c r="K92" t="inlineStr"/>
+      <c r="L92" t="inlineStr">
         <is>
           <t>海大基地，虾塘改造为罗非鱼苗塘。</t>
         </is>
       </c>
-      <c r="M92" s="4" t="inlineStr">
+      <c r="M92" t="inlineStr">
         <is>
           <t>持续服务培育，寻找切入时机</t>
         </is>
@@ -4013,7 +3955,7 @@
       <c r="A93" t="n">
         <v>92</v>
       </c>
-      <c r="B93" s="6" t="inlineStr">
+      <c r="B93" t="inlineStr">
         <is>
           <t>张秋海</t>
         </is>
@@ -4023,11 +3965,18 @@
           <t>三、潜力培育中</t>
         </is>
       </c>
+      <c r="D93" t="inlineStr"/>
+      <c r="E93" t="inlineStr"/>
+      <c r="F93" t="inlineStr"/>
       <c r="G93" t="inlineStr">
         <is>
           <t>疑似海大动保</t>
         </is>
       </c>
+      <c r="H93" t="inlineStr"/>
+      <c r="I93" t="inlineStr"/>
+      <c r="J93" t="inlineStr"/>
+      <c r="K93" t="inlineStr"/>
       <c r="L93" t="inlineStr">
         <is>
           <t>【10.07走访，用户不在场，见塘口有无人机作业；塘口约三口，规模偏小，推断无人机非自购，疑为海大动保飞防服务（海大动保有无人机直服）；用料情况待核实】 【名字确认：张秋海】</t>
@@ -4043,7 +3992,7 @@
       <c r="A94" t="n">
         <v>93</v>
       </c>
-      <c r="B94" s="6" t="inlineStr">
+      <c r="B94" t="inlineStr">
         <is>
           <t>吴杨松</t>
         </is>
@@ -4058,6 +4007,8 @@
           <t>锦山</t>
         </is>
       </c>
+      <c r="E94" t="inlineStr"/>
+      <c r="F94" t="inlineStr"/>
       <c r="G94" t="inlineStr">
         <is>
           <t>歌颂</t>
@@ -4068,6 +4019,9 @@
           <t>冯学新</t>
         </is>
       </c>
+      <c r="I94" t="inlineStr"/>
+      <c r="J94" t="inlineStr"/>
+      <c r="K94" t="inlineStr"/>
       <c r="L94" t="inlineStr">
         <is>
           <t>【10.07走访：现用歌颂饲料，跟冯学新拿现金料，105元/包（正常价121元）；很早之前用过通威沉水颗粒料，后用过百洋（反馈一般），现转歌颂；自"建一"出来（口述，具体所指待确认）后一直跟冯学新拿料】</t>
@@ -4083,7 +4037,7 @@
       <c r="A95" t="n">
         <v>94</v>
       </c>
-      <c r="B95" s="6" t="inlineStr">
+      <c r="B95" t="inlineStr">
         <is>
           <t>应伟飞</t>
         </is>
@@ -4093,6 +4047,9 @@
           <t>三、潜力培育中</t>
         </is>
       </c>
+      <c r="D95" t="inlineStr"/>
+      <c r="E95" t="inlineStr"/>
+      <c r="F95" t="inlineStr"/>
       <c r="G95" t="inlineStr">
         <is>
           <t>祥泰</t>
@@ -4103,6 +4060,8 @@
           <t>田永均</t>
         </is>
       </c>
+      <c r="I95" t="inlineStr"/>
+      <c r="J95" t="inlineStr"/>
       <c r="K95" t="inlineStr">
         <is>
           <t>43-44</t>
@@ -4113,12 +4072,13 @@
           <t>【10.07走访，老板不在，向工人了解情况：一直在用祥泰，跟田永均（店面在抱罗）拿料，半现金结算；存塘鱼五两左右，预计元旦前出鱼，工人反馈包产43-44；老板在等价格】（10.07走访未写入当日日志，留待下次汇报）</t>
         </is>
       </c>
+      <c r="M95" t="inlineStr"/>
     </row>
     <row r="96">
       <c r="A96" t="n">
         <v>95</v>
       </c>
-      <c r="B96" s="6" t="inlineStr">
+      <c r="B96" t="inlineStr">
         <is>
           <t>韩利光</t>
         </is>
@@ -4128,6 +4088,9 @@
           <t>三、潜力培育中</t>
         </is>
       </c>
+      <c r="D96" t="inlineStr"/>
+      <c r="E96" t="inlineStr"/>
+      <c r="F96" t="inlineStr"/>
       <c r="G96" t="inlineStr">
         <is>
           <t>金长城、百洋、海大</t>
@@ -4138,17 +4101,21 @@
           <t>昌盛</t>
         </is>
       </c>
+      <c r="I96" t="inlineStr"/>
+      <c r="J96" t="inlineStr"/>
+      <c r="K96" t="inlineStr"/>
       <c r="L96" t="inlineStr">
         <is>
           <t>【10.07走访：跟昌盛（其同学）拿料，现混用金长城+百洋+海大；塘口在修投料机，此前停养一段时间，现打算恢复养殖】</t>
         </is>
       </c>
+      <c r="M96" t="inlineStr"/>
     </row>
     <row r="97">
       <c r="A97" t="n">
         <v>96</v>
       </c>
-      <c r="B97" s="6" t="inlineStr">
+      <c r="B97" t="inlineStr">
         <is>
           <t>马津深</t>
         </is>
@@ -4163,17 +4130,25 @@
           <t>海口市美兰区三江镇212省道</t>
         </is>
       </c>
+      <c r="E97" t="inlineStr"/>
+      <c r="F97" t="inlineStr"/>
+      <c r="G97" t="inlineStr"/>
+      <c r="H97" t="inlineStr"/>
+      <c r="I97" t="inlineStr"/>
+      <c r="J97" t="inlineStr"/>
+      <c r="K97" t="inlineStr"/>
       <c r="L97" t="inlineStr">
         <is>
           <t>【10.08走访基地测水（10:47）：基地剩一口大鱼塘，预计下周出鱼，其余为苗塘；测水数据待补录。注：马津深同时为经销商渠道，章建龙、应富伟跟其拿料】</t>
         </is>
       </c>
+      <c r="M97" t="inlineStr"/>
     </row>
     <row r="98">
       <c r="A98" t="n">
         <v>97</v>
       </c>
-      <c r="B98" s="6" t="inlineStr">
+      <c r="B98" t="inlineStr">
         <is>
           <t>林帅</t>
         </is>
@@ -4183,22 +4158,30 @@
           <t>三、潜力培育中</t>
         </is>
       </c>
+      <c r="D98" t="inlineStr"/>
+      <c r="E98" t="inlineStr"/>
+      <c r="F98" t="inlineStr"/>
       <c r="G98" t="inlineStr">
         <is>
           <t>海大2552</t>
         </is>
       </c>
+      <c r="H98" t="inlineStr"/>
+      <c r="I98" t="inlineStr"/>
+      <c r="J98" t="inlineStr"/>
+      <c r="K98" t="inlineStr"/>
       <c r="L98" t="inlineStr">
         <is>
           <t>【10.08走访：用户不在鱼塘，仓库内见海大2552料，择日再访】</t>
         </is>
       </c>
+      <c r="M98" t="inlineStr"/>
     </row>
     <row r="99">
       <c r="A99" t="n">
         <v>98</v>
       </c>
-      <c r="B99" s="6" t="inlineStr">
+      <c r="B99" t="inlineStr">
         <is>
           <t>谭老板</t>
         </is>
@@ -4208,6 +4191,9 @@
           <t>三、潜力培育中</t>
         </is>
       </c>
+      <c r="D99" t="inlineStr"/>
+      <c r="E99" t="inlineStr"/>
+      <c r="F99" t="inlineStr"/>
       <c r="G99" t="inlineStr">
         <is>
           <t>歌颂、璃元</t>
@@ -4218,6 +4204,8 @@
           <t>陈儒、三弟</t>
         </is>
       </c>
+      <c r="I99" t="inlineStr"/>
+      <c r="J99" t="inlineStr"/>
       <c r="K99" t="inlineStr">
         <is>
           <t>43左右</t>
@@ -4228,6 +4216,7 @@
           <t>【10.08走访，交谈养殖情况：现金料用户，现用歌颂和璃元（本地料），包产43左右，跟陈儒和三弟拿料；对通威印象最近变差，认为价格偏高】</t>
         </is>
       </c>
+      <c r="M99" t="inlineStr"/>
     </row>
     <row r="100">
       <c r="A100" t="n">
@@ -4243,6 +4232,14 @@
           <t>三、潜力培育中</t>
         </is>
       </c>
+      <c r="D100" t="inlineStr"/>
+      <c r="E100" t="inlineStr"/>
+      <c r="F100" t="inlineStr"/>
+      <c r="G100" t="inlineStr"/>
+      <c r="H100" t="inlineStr"/>
+      <c r="I100" t="inlineStr"/>
+      <c r="J100" t="inlineStr"/>
+      <c r="K100" t="inlineStr"/>
       <c r="L100" t="inlineStr">
         <is>
           <t>10.09走访不在家，未交谈。</t>
@@ -4268,6 +4265,14 @@
           <t>三、潜力培育中</t>
         </is>
       </c>
+      <c r="D101" t="inlineStr"/>
+      <c r="E101" t="inlineStr"/>
+      <c r="F101" t="inlineStr"/>
+      <c r="G101" t="inlineStr"/>
+      <c r="H101" t="inlineStr"/>
+      <c r="I101" t="inlineStr"/>
+      <c r="J101" t="inlineStr"/>
+      <c r="K101" t="inlineStr"/>
       <c r="L101" t="inlineStr">
         <is>
           <t>10.09走访不在家，未交谈。</t>
@@ -4293,6 +4298,14 @@
           <t>三、潜力培育中</t>
         </is>
       </c>
+      <c r="D102" t="inlineStr"/>
+      <c r="E102" t="inlineStr"/>
+      <c r="F102" t="inlineStr"/>
+      <c r="G102" t="inlineStr"/>
+      <c r="H102" t="inlineStr"/>
+      <c r="I102" t="inlineStr"/>
+      <c r="J102" t="inlineStr"/>
+      <c r="K102" t="inlineStr"/>
       <c r="L102" t="inlineStr">
         <is>
           <t>10.09走访不在家，未交谈。</t>
@@ -4318,6 +4331,9 @@
           <t>三、潜力培育中</t>
         </is>
       </c>
+      <c r="D103" t="inlineStr"/>
+      <c r="E103" t="inlineStr"/>
+      <c r="F103" t="inlineStr"/>
       <c r="G103" t="inlineStr">
         <is>
           <t>祥泰</t>
@@ -4328,6 +4344,9 @@
           <t>田永均</t>
         </is>
       </c>
+      <c r="I103" t="inlineStr"/>
+      <c r="J103" t="inlineStr"/>
+      <c r="K103" t="inlineStr"/>
       <c r="L103" t="inlineStr">
         <is>
           <t>10.09拜访：跟田永均拿料，田永均不拉通威、用户也没法拉；本人之前用过通威但用得少；聊天意愿低。</t>
@@ -4353,11 +4372,18 @@
           <t>三、潜力培育中</t>
         </is>
       </c>
+      <c r="D104" t="inlineStr"/>
+      <c r="E104" t="inlineStr"/>
+      <c r="F104" t="inlineStr"/>
+      <c r="G104" t="inlineStr"/>
       <c r="H104" t="inlineStr">
         <is>
           <t>田永均</t>
         </is>
       </c>
+      <c r="I104" t="inlineStr"/>
+      <c r="J104" t="inlineStr"/>
+      <c r="K104" t="inlineStr"/>
       <c r="L104" t="inlineStr">
         <is>
           <t>10.09拜访：用户不愿意交谈。</t>
@@ -4383,9 +4409,11 @@
           <t>一、通威现有用户</t>
         </is>
       </c>
+      <c r="D105" t="inlineStr"/>
       <c r="E105" t="n">
         <v>2</v>
       </c>
+      <c r="F105" t="inlineStr"/>
       <c r="G105" t="inlineStr">
         <is>
           <t>通威（本兆前段用一点翔泰、后转通威）</t>
@@ -4396,6 +4424,9 @@
           <t>—（公司饲料活动拿料）</t>
         </is>
       </c>
+      <c r="I105" t="inlineStr"/>
+      <c r="J105" t="inlineStr"/>
+      <c r="K105" t="inlineStr"/>
       <c r="L105" t="inlineStr">
         <is>
           <t>8月即作为通威用户参加公司饲料活动拿料；本兆前面用过一点翔泰、后面才转用通威；上次活动拉了一点通威用到现在，下一兆提了一嘴要用全程通威。测水：14:20塘亚盐0.15、14:23塘亚盐0.10，pH均7.4。塘口位置待确认。10.10新增用户走访。</t>
@@ -4421,6 +4452,9 @@
           <t>三、潜力培育中</t>
         </is>
       </c>
+      <c r="D106" t="inlineStr"/>
+      <c r="E106" t="inlineStr"/>
+      <c r="F106" t="inlineStr"/>
       <c r="G106" t="inlineStr">
         <is>
           <t>百洋（最低端）</t>
@@ -4431,6 +4465,9 @@
           <t>—（百洋直供，不经经销商）</t>
         </is>
       </c>
+      <c r="I106" t="inlineStr"/>
+      <c r="J106" t="inlineStr"/>
+      <c r="K106" t="inlineStr"/>
       <c r="L106" t="inlineStr">
         <is>
           <t>百洋直供用户，直接从厂里拿料，不经经销商；用百洋最低端料，包产不高；因直供价低转料意愿不强。其租的塘明年5月到期，届时需另找养户租塘续养、不找经销商（找经销商租塘就被绑定按经销商意思拿料、比百洋直供贵、不划算）。10.10客情走访。</t>
@@ -4456,6 +4493,14 @@
           <t>三、潜力培育中</t>
         </is>
       </c>
+      <c r="D107" t="inlineStr"/>
+      <c r="E107" t="inlineStr"/>
+      <c r="F107" t="inlineStr"/>
+      <c r="G107" t="inlineStr"/>
+      <c r="H107" t="inlineStr"/>
+      <c r="I107" t="inlineStr"/>
+      <c r="J107" t="inlineStr"/>
+      <c r="K107" t="inlineStr"/>
       <c r="L107" t="inlineStr">
         <is>
           <t>【养殖关键节点】出鱼/抓鱼：2026-10-10（出鱼期，抓鱼中）；放苗时间：待出鱼后回访补全。
@@ -4482,11 +4527,17 @@
           <t>三、潜力培育中</t>
         </is>
       </c>
+      <c r="D108" t="inlineStr"/>
+      <c r="E108" t="inlineStr"/>
+      <c r="F108" t="inlineStr"/>
       <c r="G108" t="inlineStr">
         <is>
           <t>翔泰</t>
         </is>
       </c>
+      <c r="H108" t="inlineStr"/>
+      <c r="I108" t="inlineStr"/>
+      <c r="J108" t="inlineStr"/>
       <c r="K108" t="inlineStr">
         <is>
           <t>稳定且较高（陈南高亲述）</t>
@@ -4500,6 +4551,80 @@
       <c r="M108" t="inlineStr">
         <is>
           <t>作为翔泰高产样板用户经营客情，借其高产口碑做转介绍突破；择机推介通威。</t>
+        </is>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" t="n">
+        <v>108</v>
+      </c>
+      <c r="B109" t="inlineStr">
+        <is>
+          <t>陈姐</t>
+        </is>
+      </c>
+      <c r="C109" t="inlineStr">
+        <is>
+          <t>三、潜力培育中</t>
+        </is>
+      </c>
+      <c r="D109" t="inlineStr">
+        <is>
+          <t>锦山镇039乡道（陈尧光对面）</t>
+        </is>
+      </c>
+      <c r="E109" t="inlineStr"/>
+      <c r="F109" t="inlineStr"/>
+      <c r="G109" t="inlineStr"/>
+      <c r="H109" t="inlineStr"/>
+      <c r="I109" t="inlineStr"/>
+      <c r="J109" t="inlineStr"/>
+      <c r="K109" t="inlineStr"/>
+      <c r="L109" t="inlineStr">
+        <is>
+          <t>新养殖户，爱通威地图未标；塘位于陈尧光对面（锦山镇039乡道）。2026-10-12 测水：pH 7.0、氨氮 0.20、亚盐 0.10，三项正常。目前仅测水服务，尚未走访了解养殖规模与用料。</t>
+        </is>
+      </c>
+      <c r="M109" t="inlineStr">
+        <is>
+          <t>实地走访了解养殖规模、现用料与拿料对象，建立客情，靠测水/动保服务切入培育。</t>
+        </is>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" t="n">
+        <v>109</v>
+      </c>
+      <c r="B110" t="inlineStr">
+        <is>
+          <t>陈尧光</t>
+        </is>
+      </c>
+      <c r="C110" t="inlineStr">
+        <is>
+          <t>三、潜力培育中</t>
+        </is>
+      </c>
+      <c r="D110" t="inlineStr">
+        <is>
+          <t>锦山镇039乡道（陈姐塘位于其对面）</t>
+        </is>
+      </c>
+      <c r="E110" t="inlineStr"/>
+      <c r="F110" t="inlineStr"/>
+      <c r="G110" t="inlineStr"/>
+      <c r="H110" t="inlineStr"/>
+      <c r="I110" t="inlineStr"/>
+      <c r="J110" t="inlineStr"/>
+      <c r="K110" t="inlineStr"/>
+      <c r="L110" t="inlineStr">
+        <is>
+          <t>位置参照点：陈姐塘位于其对面（锦山镇039乡道）；尚未走访了解养殖情况。</t>
+        </is>
+      </c>
+      <c r="M110" t="inlineStr">
+        <is>
+          <t>待走访了解养殖规模与用料，确认是否目标客户。</t>
         </is>
       </c>
     </row>
@@ -4516,18 +4641,14 @@
   </sheetPr>
   <dimension ref="A1:B5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="20" customWidth="1" min="1" max="1"/>
-    <col width="10" customWidth="1" min="2" max="2"/>
-  </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="5" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>客户分类</t>
         </is>
       </c>
-      <c r="B1" s="5" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>户数</t>
         </is>
@@ -4560,7 +4681,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>91</v>
+        <v>93</v>
       </c>
     </row>
     <row r="5">

--- a/数据/用户摸牌表.xlsx
+++ b/数据/用户摸牌表.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M110"/>
+  <dimension ref="A1:N113"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -498,18 +498,11 @@
           <t>一、通威现有用户</t>
         </is>
       </c>
-      <c r="D2" t="inlineStr"/>
-      <c r="E2" t="inlineStr"/>
-      <c r="F2" t="inlineStr"/>
       <c r="G2" t="inlineStr">
         <is>
           <t>通威9912</t>
         </is>
       </c>
-      <c r="H2" t="inlineStr"/>
-      <c r="I2" t="inlineStr"/>
-      <c r="J2" t="inlineStr"/>
-      <c r="K2" t="inlineStr"/>
       <c r="L2" t="inlineStr">
         <is>
           <t>通威9912饲料用户，合作稳定。日常测水、走访维护，持续沟通后续用料。</t>
@@ -535,18 +528,11 @@
           <t>一、通威现有用户</t>
         </is>
       </c>
-      <c r="D3" t="inlineStr"/>
-      <c r="E3" t="inlineStr"/>
-      <c r="F3" t="inlineStr"/>
       <c r="G3" t="inlineStr">
         <is>
           <t>通威</t>
         </is>
       </c>
-      <c r="H3" t="inlineStr"/>
-      <c r="I3" t="inlineStr"/>
-      <c r="J3" t="inlineStr"/>
-      <c r="K3" t="inlineStr"/>
       <c r="L3" t="inlineStr">
         <is>
           <t>通威老客户，全程使用通威产品。节日走访并赠送礼品。</t>
@@ -572,18 +558,11 @@
           <t>一、通威现有用户</t>
         </is>
       </c>
-      <c r="D4" t="inlineStr"/>
-      <c r="E4" t="inlineStr"/>
-      <c r="F4" t="inlineStr"/>
       <c r="G4" t="inlineStr">
         <is>
           <t>通威</t>
         </is>
       </c>
-      <c r="H4" t="inlineStr"/>
-      <c r="I4" t="inlineStr"/>
-      <c r="J4" t="inlineStr"/>
-      <c r="K4" t="inlineStr"/>
       <c r="L4" t="inlineStr">
         <is>
           <t>通威用户，客情维护中。</t>
@@ -609,18 +588,11 @@
           <t>一、通威现有用户</t>
         </is>
       </c>
-      <c r="D5" t="inlineStr"/>
-      <c r="E5" t="inlineStr"/>
-      <c r="F5" t="inlineStr"/>
       <c r="G5" t="inlineStr">
         <is>
           <t>通威</t>
         </is>
       </c>
-      <c r="H5" t="inlineStr"/>
-      <c r="I5" t="inlineStr"/>
-      <c r="J5" t="inlineStr"/>
-      <c r="K5" t="inlineStr"/>
       <c r="L5" t="inlineStr">
         <is>
           <t>已转用通威。有效塘口1、2、3、6、7号已完成两轮打样：9月7/8日至9月29日，1号塘0.50增至0.72、2号塘0.31增至0.50、3号塘0.25增至0.54、6号塘0.55增至0.72、7号塘0.45增至0.66，总增重1.08，平均增重约0.22。期间曾出现死鱼、亚硝酸盐严重超标，协助处理后当日见效，次日回访恢复正常。目前养殖情况稳定，持续跟进中。 【10.05走访秋溪尾基地、10.07走访大致坡基地，均测水做服务；两处均反馈喂料后水面有大片油膜，用户为1053专用料户；】 【10.07大致坡基地测水7口塘：2号、3号塘亚盐0.8超量程⚠️（鱼易浮头，重点处理）；1号、7号塘氨氮0.90偏高；4号、5号塘正常；6号塘氨氮0.50、亚盐0.20；油膜问题待核实塘口还是饲料原因】</t>
@@ -646,7 +618,6 @@
           <t>二、高意向客户</t>
         </is>
       </c>
-      <c r="D6" t="inlineStr"/>
       <c r="E6" t="n">
         <v>2</v>
       </c>
@@ -665,9 +636,6 @@
           <t>吴建龙</t>
         </is>
       </c>
-      <c r="I6" t="inlineStr"/>
-      <c r="J6" t="inlineStr"/>
-      <c r="K6" t="inlineStr"/>
       <c r="L6" t="inlineStr">
         <is>
           <t>养殖两口塘约30亩。用百洋，多次为其测水、检藻、推广动保产品。现跟吴建龙拿料，已确认10月起拉通威料，上一茬鱼已抓完，放苗后即转料。</t>
@@ -693,18 +661,11 @@
           <t>二、高意向客户</t>
         </is>
       </c>
-      <c r="D7" t="inlineStr"/>
-      <c r="E7" t="inlineStr"/>
-      <c r="F7" t="inlineStr"/>
       <c r="G7" t="inlineStr">
         <is>
           <t>混料</t>
         </is>
       </c>
-      <c r="H7" t="inlineStr"/>
-      <c r="I7" t="inlineStr"/>
-      <c r="J7" t="inlineStr"/>
-      <c r="K7" t="inlineStr"/>
       <c r="L7" t="inlineStr">
         <is>
           <t>混料，不拿通威，老板平时不在塘口。</t>
@@ -730,18 +691,11 @@
           <t>二、高意向客户</t>
         </is>
       </c>
-      <c r="D8" t="inlineStr"/>
-      <c r="E8" t="inlineStr"/>
-      <c r="F8" t="inlineStr"/>
       <c r="G8" t="inlineStr">
         <is>
           <t>祥泰</t>
         </is>
       </c>
-      <c r="H8" t="inlineStr"/>
-      <c r="I8" t="inlineStr"/>
-      <c r="J8" t="inlineStr"/>
-      <c r="K8" t="inlineStr"/>
       <c r="L8" t="inlineStr">
         <is>
           <t>祥泰现金料用户，曾到通威饲料厂参观，合作意向较好。</t>
@@ -767,18 +721,11 @@
           <t>二、高意向客户</t>
         </is>
       </c>
-      <c r="D9" t="inlineStr"/>
-      <c r="E9" t="inlineStr"/>
       <c r="F9" t="inlineStr">
         <is>
           <t>30</t>
         </is>
       </c>
-      <c r="G9" t="inlineStr"/>
-      <c r="H9" t="inlineStr"/>
-      <c r="I9" t="inlineStr"/>
-      <c r="J9" t="inlineStr"/>
-      <c r="K9" t="inlineStr"/>
       <c r="L9" t="inlineStr">
         <is>
           <t>30亩、密度2500尾每亩，上一茬已干塘，下一造有换料意向，已推荐通威小料。</t>
@@ -809,7 +756,6 @@
           <t>昌洒基地</t>
         </is>
       </c>
-      <c r="E10" t="inlineStr"/>
       <c r="F10" t="inlineStr">
         <is>
           <t>100多</t>
@@ -820,14 +766,11 @@
           <t>海一、海大、鸿业</t>
         </is>
       </c>
-      <c r="H10" t="inlineStr"/>
       <c r="I10" t="inlineStr">
         <is>
           <t>其儿子</t>
         </is>
       </c>
-      <c r="J10" t="inlineStr"/>
-      <c r="K10" t="inlineStr"/>
       <c r="L10" t="inlineStr">
         <is>
           <t>100多亩大户，现用鸿业料加海大混料。昌洒基地由其儿子负责、约120亩，用海一料，有合作意向，重点跟进。</t>
@@ -853,17 +796,11 @@
           <t>二、高意向客户</t>
         </is>
       </c>
-      <c r="D11" t="inlineStr"/>
-      <c r="E11" t="inlineStr"/>
-      <c r="F11" t="inlineStr"/>
       <c r="G11" t="inlineStr">
         <is>
           <t>祥泰</t>
         </is>
       </c>
-      <c r="H11" t="inlineStr"/>
-      <c r="I11" t="inlineStr"/>
-      <c r="J11" t="inlineStr"/>
       <c r="K11" t="inlineStr">
         <is>
           <t>40</t>
@@ -899,21 +836,16 @@
           <t>竹堆基地</t>
         </is>
       </c>
-      <c r="E12" t="inlineStr"/>
-      <c r="F12" t="inlineStr"/>
       <c r="G12" t="inlineStr">
         <is>
           <t>唐人神、桂美达</t>
         </is>
       </c>
-      <c r="H12" t="inlineStr"/>
-      <c r="I12" t="inlineStr"/>
       <c r="J12" t="inlineStr">
         <is>
           <t>600包（已采购）</t>
         </is>
       </c>
-      <c r="K12" t="inlineStr"/>
       <c r="L12" t="inlineStr">
         <is>
           <t>竹堆基地，部分塘口投喂唐人神、桂美达苗料，已采购600包9912，存鱼出塘收尾中。</t>
@@ -939,17 +871,11 @@
           <t>二、高意向客户</t>
         </is>
       </c>
-      <c r="D13" t="inlineStr"/>
-      <c r="E13" t="inlineStr"/>
-      <c r="F13" t="inlineStr"/>
       <c r="G13" t="inlineStr">
         <is>
           <t>通威、祥泰、海大</t>
         </is>
       </c>
-      <c r="H13" t="inlineStr"/>
-      <c r="I13" t="inlineStr"/>
-      <c r="J13" t="inlineStr"/>
       <c r="K13" t="inlineStr">
         <is>
           <t>81</t>
@@ -980,18 +906,11 @@
           <t>二、高意向客户</t>
         </is>
       </c>
-      <c r="D14" t="inlineStr"/>
-      <c r="E14" t="inlineStr"/>
-      <c r="F14" t="inlineStr"/>
       <c r="G14" t="inlineStr">
         <is>
           <t>百洋</t>
         </is>
       </c>
-      <c r="H14" t="inlineStr"/>
-      <c r="I14" t="inlineStr"/>
-      <c r="J14" t="inlineStr"/>
-      <c r="K14" t="inlineStr"/>
       <c r="L14" t="inlineStr">
         <is>
           <t>百洋用户，存鱼七两左右。对价格政策敏感，表示有政策支持愿意用通威。</t>
@@ -1017,9 +936,6 @@
           <t>二、高意向客户</t>
         </is>
       </c>
-      <c r="D15" t="inlineStr"/>
-      <c r="E15" t="inlineStr"/>
-      <c r="F15" t="inlineStr"/>
       <c r="G15" t="inlineStr">
         <is>
           <t>海大2552</t>
@@ -1030,9 +946,6 @@
           <t>吴建龙</t>
         </is>
       </c>
-      <c r="I15" t="inlineStr"/>
-      <c r="J15" t="inlineStr"/>
-      <c r="K15" t="inlineStr"/>
       <c r="L15" t="inlineStr">
         <is>
           <t>现用祥泰加海大，上半年用过通威，反馈效果可以。 【10.07走访，以客情维护为主：现用海大2552，跟吴建龙拿料；产量不太高，反感业务员问这问那；评估有转化机会】</t>
@@ -1058,18 +971,11 @@
           <t>二、高意向客户</t>
         </is>
       </c>
-      <c r="D16" t="inlineStr"/>
-      <c r="E16" t="inlineStr"/>
-      <c r="F16" t="inlineStr"/>
       <c r="G16" t="inlineStr">
         <is>
           <t>百洋</t>
         </is>
       </c>
-      <c r="H16" t="inlineStr"/>
-      <c r="I16" t="inlineStr"/>
-      <c r="J16" t="inlineStr"/>
-      <c r="K16" t="inlineStr"/>
       <c r="L16" t="inlineStr">
         <is>
           <t>百洋用户，有动保产品需求，可先从动保切入。</t>
@@ -1095,9 +1001,6 @@
           <t>三、潜力培育中</t>
         </is>
       </c>
-      <c r="D17" t="inlineStr"/>
-      <c r="E17" t="inlineStr"/>
-      <c r="F17" t="inlineStr"/>
       <c r="G17" t="inlineStr">
         <is>
           <t>祥泰</t>
@@ -1108,9 +1011,6 @@
           <t>田永均</t>
         </is>
       </c>
-      <c r="I17" t="inlineStr"/>
-      <c r="J17" t="inlineStr"/>
-      <c r="K17" t="inlineStr"/>
       <c r="L17" t="inlineStr">
         <is>
           <t>祥泰老用户，养二两鱼、罗非黄骨混养塘。长期为其做服务：测水、补网、培育光合菌，亚盐偏高时协助处理。鱼已抓完，下一造继续跟进。</t>
@@ -1136,18 +1036,11 @@
           <t>三、潜力培育中</t>
         </is>
       </c>
-      <c r="D18" t="inlineStr"/>
-      <c r="E18" t="inlineStr"/>
-      <c r="F18" t="inlineStr"/>
       <c r="G18" t="inlineStr">
         <is>
           <t>百洋、祥泰</t>
         </is>
       </c>
-      <c r="H18" t="inlineStr"/>
-      <c r="I18" t="inlineStr"/>
-      <c r="J18" t="inlineStr"/>
-      <c r="K18" t="inlineStr"/>
       <c r="L18" t="inlineStr">
         <is>
           <t>用百洋、祥泰等饲料。对通威印象很好，多次走访沟通。</t>
@@ -1173,14 +1066,6 @@
           <t>三、潜力培育中</t>
         </is>
       </c>
-      <c r="D19" t="inlineStr"/>
-      <c r="E19" t="inlineStr"/>
-      <c r="F19" t="inlineStr"/>
-      <c r="G19" t="inlineStr"/>
-      <c r="H19" t="inlineStr"/>
-      <c r="I19" t="inlineStr"/>
-      <c r="J19" t="inlineStr"/>
-      <c r="K19" t="inlineStr"/>
       <c r="L19" t="inlineStr">
         <is>
           <t>电话联系测水打样，鱼七两左右、肥满度好。</t>
@@ -1206,14 +1091,6 @@
           <t>三、潜力培育中</t>
         </is>
       </c>
-      <c r="D20" t="inlineStr"/>
-      <c r="E20" t="inlineStr"/>
-      <c r="F20" t="inlineStr"/>
-      <c r="G20" t="inlineStr"/>
-      <c r="H20" t="inlineStr"/>
-      <c r="I20" t="inlineStr"/>
-      <c r="J20" t="inlineStr"/>
-      <c r="K20" t="inlineStr"/>
       <c r="L20" t="inlineStr">
         <is>
           <t>有建设光合菌扩培系统的需求。使用我司动保产品后持续跟踪效果，打样鱼五两左右。</t>
@@ -1239,14 +1116,6 @@
           <t>三、潜力培育中</t>
         </is>
       </c>
-      <c r="D21" t="inlineStr"/>
-      <c r="E21" t="inlineStr"/>
-      <c r="F21" t="inlineStr"/>
-      <c r="G21" t="inlineStr"/>
-      <c r="H21" t="inlineStr"/>
-      <c r="I21" t="inlineStr"/>
-      <c r="J21" t="inlineStr"/>
-      <c r="K21" t="inlineStr"/>
       <c r="L21" t="inlineStr">
         <is>
           <t>鱼苗塘和3号塘亚盐偏高。小塘已抓鱼三万斤，大塘十月抓。 【10.05走访，用户暂不需要测水服务，择日再访】</t>
@@ -1272,14 +1141,6 @@
           <t>三、潜力培育中</t>
         </is>
       </c>
-      <c r="D22" t="inlineStr"/>
-      <c r="E22" t="inlineStr"/>
-      <c r="F22" t="inlineStr"/>
-      <c r="G22" t="inlineStr"/>
-      <c r="H22" t="inlineStr"/>
-      <c r="I22" t="inlineStr"/>
-      <c r="J22" t="inlineStr"/>
-      <c r="K22" t="inlineStr"/>
       <c r="L22" t="inlineStr">
         <is>
           <t>试用过一车通威料，现跟随周公宝用料。鱼已出塘。</t>
@@ -1305,11 +1166,9 @@
           <t>三、潜力培育中</t>
         </is>
       </c>
-      <c r="D23" t="inlineStr"/>
       <c r="E23" t="n">
         <v>7</v>
       </c>
-      <c r="F23" t="inlineStr"/>
       <c r="G23" t="inlineStr">
         <is>
           <t>海大2552、混渝泰/粤海</t>
@@ -1320,9 +1179,6 @@
           <t>周公宝</t>
         </is>
       </c>
-      <c r="I23" t="inlineStr"/>
-      <c r="J23" t="inlineStr"/>
-      <c r="K23" t="inlineStr"/>
       <c r="L23" t="inlineStr">
         <is>
           <t>七口塘，计划安装料塔，对通威认可度较高；老婆湖南人（同乡圈）；主用海大2552、偶尔混渝泰、粤海；跟周公宝拿料；主动问价，转化机会明确。与唐行平（湖南老乡）互相认识，可借同乡关系交叉跟进。10.10客情走访。</t>
@@ -1348,14 +1204,6 @@
           <t>三、潜力培育中</t>
         </is>
       </c>
-      <c r="D24" t="inlineStr"/>
-      <c r="E24" t="inlineStr"/>
-      <c r="F24" t="inlineStr"/>
-      <c r="G24" t="inlineStr"/>
-      <c r="H24" t="inlineStr"/>
-      <c r="I24" t="inlineStr"/>
-      <c r="J24" t="inlineStr"/>
-      <c r="K24" t="inlineStr"/>
       <c r="L24" t="inlineStr">
         <is>
           <t>多次交谈，对通威印象逐步好转，推进料塔推荐。</t>
@@ -1381,14 +1229,6 @@
           <t>三、潜力培育中</t>
         </is>
       </c>
-      <c r="D25" t="inlineStr"/>
-      <c r="E25" t="inlineStr"/>
-      <c r="F25" t="inlineStr"/>
-      <c r="G25" t="inlineStr"/>
-      <c r="H25" t="inlineStr"/>
-      <c r="I25" t="inlineStr"/>
-      <c r="J25" t="inlineStr"/>
-      <c r="K25" t="inlineStr"/>
       <c r="L25" t="inlineStr">
         <is>
           <t>对光合菌培养感兴趣，已交流培养经验。</t>
@@ -1419,13 +1259,6 @@
           <t>另一基地</t>
         </is>
       </c>
-      <c r="E26" t="inlineStr"/>
-      <c r="F26" t="inlineStr"/>
-      <c r="G26" t="inlineStr"/>
-      <c r="H26" t="inlineStr"/>
-      <c r="I26" t="inlineStr"/>
-      <c r="J26" t="inlineStr"/>
-      <c r="K26" t="inlineStr"/>
       <c r="L26" t="inlineStr">
         <is>
           <t>用150型号小料，另一基地分苗后密度5000每亩。</t>
@@ -1451,18 +1284,11 @@
           <t>三、潜力培育中</t>
         </is>
       </c>
-      <c r="D27" t="inlineStr"/>
-      <c r="E27" t="inlineStr"/>
-      <c r="F27" t="inlineStr"/>
       <c r="G27" t="inlineStr">
         <is>
           <t>祥泰</t>
         </is>
       </c>
-      <c r="H27" t="inlineStr"/>
-      <c r="I27" t="inlineStr"/>
-      <c r="J27" t="inlineStr"/>
-      <c r="K27" t="inlineStr"/>
       <c r="L27" t="inlineStr">
         <is>
           <t>祥泰混料，四五两鱼，预计十月中抓鱼。</t>
@@ -1488,18 +1314,11 @@
           <t>三、潜力培育中</t>
         </is>
       </c>
-      <c r="D28" t="inlineStr"/>
-      <c r="E28" t="inlineStr"/>
-      <c r="F28" t="inlineStr"/>
       <c r="G28" t="inlineStr">
         <is>
           <t>海大、添祥</t>
         </is>
       </c>
-      <c r="H28" t="inlineStr"/>
-      <c r="I28" t="inlineStr"/>
-      <c r="J28" t="inlineStr"/>
-      <c r="K28" t="inlineStr"/>
       <c r="L28" t="inlineStr">
         <is>
           <t>添祥小料加海大混用，鱼七八两，宝路标苗八九成。</t>
@@ -1525,20 +1344,14 @@
           <t>三、潜力培育中</t>
         </is>
       </c>
-      <c r="D29" t="inlineStr"/>
       <c r="E29" t="n">
         <v>4</v>
       </c>
-      <c r="F29" t="inlineStr"/>
       <c r="G29" t="inlineStr">
         <is>
           <t>海大</t>
         </is>
       </c>
-      <c r="H29" t="inlineStr"/>
-      <c r="I29" t="inlineStr"/>
-      <c r="J29" t="inlineStr"/>
-      <c r="K29" t="inlineStr"/>
       <c r="L29" t="inlineStr">
         <is>
           <t>海大用户，四口塘三口在养，成鱼塘五两。</t>
@@ -1564,17 +1377,11 @@
           <t>三、潜力培育中</t>
         </is>
       </c>
-      <c r="D30" t="inlineStr"/>
-      <c r="E30" t="inlineStr"/>
-      <c r="F30" t="inlineStr"/>
       <c r="G30" t="inlineStr">
         <is>
           <t>祥泰</t>
         </is>
       </c>
-      <c r="H30" t="inlineStr"/>
-      <c r="I30" t="inlineStr"/>
-      <c r="J30" t="inlineStr"/>
       <c r="K30" t="inlineStr">
         <is>
           <t>65</t>
@@ -1605,9 +1412,6 @@
           <t>三、潜力培育中</t>
         </is>
       </c>
-      <c r="D31" t="inlineStr"/>
-      <c r="E31" t="inlineStr"/>
-      <c r="F31" t="inlineStr"/>
       <c r="G31" t="inlineStr">
         <is>
           <t>鸿业</t>
@@ -1618,9 +1422,6 @@
           <t>周公宝</t>
         </is>
       </c>
-      <c r="I31" t="inlineStr"/>
-      <c r="J31" t="inlineStr"/>
-      <c r="K31" t="inlineStr"/>
       <c r="L31" t="inlineStr">
         <is>
           <t>鸿业用户，养殖周期长，欲安装料塔，现跟周公宝拿料。</t>
@@ -1646,14 +1447,6 @@
           <t>三、潜力培育中</t>
         </is>
       </c>
-      <c r="D32" t="inlineStr"/>
-      <c r="E32" t="inlineStr"/>
-      <c r="F32" t="inlineStr"/>
-      <c r="G32" t="inlineStr"/>
-      <c r="H32" t="inlineStr"/>
-      <c r="I32" t="inlineStr"/>
-      <c r="J32" t="inlineStr"/>
-      <c r="K32" t="inlineStr"/>
       <c r="L32" t="inlineStr">
         <is>
           <t>打样1.3斤成鱼，预计十月一出鱼。</t>
@@ -1679,9 +1472,6 @@
           <t>三、潜力培育中</t>
         </is>
       </c>
-      <c r="D33" t="inlineStr"/>
-      <c r="E33" t="inlineStr"/>
-      <c r="F33" t="inlineStr"/>
       <c r="G33" t="inlineStr">
         <is>
           <t>海大、歌颂</t>
@@ -1692,9 +1482,6 @@
           <t>何经理</t>
         </is>
       </c>
-      <c r="I33" t="inlineStr"/>
-      <c r="J33" t="inlineStr"/>
-      <c r="K33" t="inlineStr"/>
       <c r="L33" t="inlineStr">
         <is>
           <t>跟何经理拿料，用歌颂加海大，存塘鱼3两、2000尾每亩，未用过通威。</t>
@@ -1720,18 +1507,11 @@
           <t>三、潜力培育中</t>
         </is>
       </c>
-      <c r="D34" t="inlineStr"/>
-      <c r="E34" t="inlineStr"/>
-      <c r="F34" t="inlineStr"/>
       <c r="G34" t="inlineStr">
         <is>
           <t>百洋</t>
         </is>
       </c>
-      <c r="H34" t="inlineStr"/>
-      <c r="I34" t="inlineStr"/>
-      <c r="J34" t="inlineStr"/>
-      <c r="K34" t="inlineStr"/>
       <c r="L34" t="inlineStr">
         <is>
           <t>走访取样百洋三号料。</t>
@@ -1762,17 +1542,11 @@
           <t>水铁基地</t>
         </is>
       </c>
-      <c r="E35" t="inlineStr"/>
-      <c r="F35" t="inlineStr"/>
       <c r="G35" t="inlineStr">
         <is>
           <t>海大2552</t>
         </is>
       </c>
-      <c r="H35" t="inlineStr"/>
-      <c r="I35" t="inlineStr"/>
-      <c r="J35" t="inlineStr"/>
-      <c r="K35" t="inlineStr"/>
       <c r="L35" t="inlineStr">
         <is>
           <t>水铁基地，海大2552，存鱼7至8两，预计两个月后出鱼。</t>
@@ -1798,18 +1572,11 @@
           <t>三、潜力培育中</t>
         </is>
       </c>
-      <c r="D36" t="inlineStr"/>
-      <c r="E36" t="inlineStr"/>
-      <c r="F36" t="inlineStr"/>
       <c r="G36" t="inlineStr">
         <is>
           <t>海大</t>
         </is>
       </c>
-      <c r="H36" t="inlineStr"/>
-      <c r="I36" t="inlineStr"/>
-      <c r="J36" t="inlineStr"/>
-      <c r="K36" t="inlineStr"/>
       <c r="L36" t="inlineStr">
         <is>
           <t>海大用户，大鱼一斤待抓、小鱼二两。</t>
@@ -1835,18 +1602,11 @@
           <t>三、潜力培育中</t>
         </is>
       </c>
-      <c r="D37" t="inlineStr"/>
-      <c r="E37" t="inlineStr"/>
-      <c r="F37" t="inlineStr"/>
       <c r="G37" t="inlineStr">
         <is>
           <t>海壹</t>
         </is>
       </c>
-      <c r="H37" t="inlineStr"/>
-      <c r="I37" t="inlineStr"/>
-      <c r="J37" t="inlineStr"/>
-      <c r="K37" t="inlineStr"/>
       <c r="L37" t="inlineStr">
         <is>
           <t>搭配少量海壹，存鱼一斤左右，本月集中出鱼。</t>
@@ -1872,18 +1632,11 @@
           <t>三、潜力培育中</t>
         </is>
       </c>
-      <c r="D38" t="inlineStr"/>
-      <c r="E38" t="inlineStr"/>
-      <c r="F38" t="inlineStr"/>
       <c r="G38" t="inlineStr">
         <is>
           <t>混料</t>
         </is>
       </c>
-      <c r="H38" t="inlineStr"/>
-      <c r="I38" t="inlineStr"/>
-      <c r="J38" t="inlineStr"/>
-      <c r="K38" t="inlineStr"/>
       <c r="L38" t="inlineStr">
         <is>
           <t>混料户，鱼塘死鱼时上门协助测水。</t>
@@ -1909,10 +1662,6 @@
           <t>三、潜力培育中</t>
         </is>
       </c>
-      <c r="D39" t="inlineStr"/>
-      <c r="E39" t="inlineStr"/>
-      <c r="F39" t="inlineStr"/>
-      <c r="G39" t="inlineStr"/>
       <c r="H39" t="inlineStr">
         <is>
           <t>马津深</t>
@@ -1923,8 +1672,6 @@
           <t>与儿子一同经营</t>
         </is>
       </c>
-      <c r="J39" t="inlineStr"/>
-      <c r="K39" t="inlineStr"/>
       <c r="L39" t="inlineStr">
         <is>
           <t>跟马津深拿料，塘向麻秋勇租。与儿子一同经营，新开四口新塘、基地在建，计划对接拉料。</t>
@@ -1950,11 +1697,9 @@
           <t>三、潜力培育中</t>
         </is>
       </c>
-      <c r="D40" t="inlineStr"/>
       <c r="E40" t="n">
         <v>5</v>
       </c>
-      <c r="F40" t="inlineStr"/>
       <c r="G40" t="inlineStr">
         <is>
           <t>翔泰、通威</t>
@@ -1965,9 +1710,6 @@
           <t>马津深</t>
         </is>
       </c>
-      <c r="I40" t="inlineStr"/>
-      <c r="J40" t="inlineStr"/>
-      <c r="K40" t="inlineStr"/>
       <c r="L40" t="inlineStr">
         <is>
           <t>5口在养鱼塘多处亚盐偏高；基本全程用翔泰、拉过一车通威；反映翔泰长得不行，后两月冲重量想拉通威，但经销商马津深（同音，马金生即马津深、已并）不给拉；准备拿苗原13号推迟至16号；其弟丁开福苗塘已放60万苗（约4800尾/斤），趁早刺激快速转料，便于后续用通威小料'开口乐'开口。10.10客情走访。</t>
@@ -1998,21 +1740,16 @@
           <t>景山场地</t>
         </is>
       </c>
-      <c r="E41" t="inlineStr"/>
-      <c r="F41" t="inlineStr"/>
       <c r="G41" t="inlineStr">
         <is>
           <t>祥泰、添祥</t>
         </is>
       </c>
-      <c r="H41" t="inlineStr"/>
       <c r="I41" t="inlineStr">
         <is>
           <t>其儿子</t>
         </is>
       </c>
-      <c r="J41" t="inlineStr"/>
-      <c r="K41" t="inlineStr"/>
       <c r="L41" t="inlineStr">
         <is>
           <t>用过粤海、鸿业一号，现用添祥。景山场地由儿子负责养殖及用料，反映祥泰料包重偏轻。</t>
@@ -2038,18 +1775,11 @@
           <t>三、潜力培育中</t>
         </is>
       </c>
-      <c r="D42" t="inlineStr"/>
-      <c r="E42" t="inlineStr"/>
-      <c r="F42" t="inlineStr"/>
       <c r="G42" t="inlineStr">
         <is>
           <t>百洋</t>
         </is>
       </c>
-      <c r="H42" t="inlineStr"/>
-      <c r="I42" t="inlineStr"/>
-      <c r="J42" t="inlineStr"/>
-      <c r="K42" t="inlineStr"/>
       <c r="L42" t="inlineStr">
         <is>
           <t>原用通威9911，后被百洋切走，现用百洋，存鱼五两左右。【养殖关键节点】放苗：9月16日新抓60万尾苗放入，平均4800尾/斤（约125斤）。</t>
@@ -2075,8 +1805,6 @@
           <t>三、潜力培育中</t>
         </is>
       </c>
-      <c r="D43" t="inlineStr"/>
-      <c r="E43" t="inlineStr"/>
       <c r="F43" t="inlineStr">
         <is>
           <t>80</t>
@@ -2092,9 +1820,6 @@
           <t>成江乾</t>
         </is>
       </c>
-      <c r="I43" t="inlineStr"/>
-      <c r="J43" t="inlineStr"/>
-      <c r="K43" t="inlineStr"/>
       <c r="L43" t="inlineStr">
         <is>
           <t>80亩，祥泰，跟成江乾拿料，已出鱼。</t>
@@ -2120,8 +1845,6 @@
           <t>三、潜力培育中</t>
         </is>
       </c>
-      <c r="D44" t="inlineStr"/>
-      <c r="E44" t="inlineStr"/>
       <c r="F44" t="inlineStr">
         <is>
           <t>60</t>
@@ -2137,9 +1860,6 @@
           <t>周公保</t>
         </is>
       </c>
-      <c r="I44" t="inlineStr"/>
-      <c r="J44" t="inlineStr"/>
-      <c r="K44" t="inlineStr"/>
       <c r="L44" t="inlineStr">
         <is>
           <t>60亩，歌颂，跟周公保拿料，资金不足。</t>
@@ -2165,18 +1885,11 @@
           <t>三、潜力培育中</t>
         </is>
       </c>
-      <c r="D45" t="inlineStr"/>
-      <c r="E45" t="inlineStr"/>
-      <c r="F45" t="inlineStr"/>
       <c r="G45" t="inlineStr">
         <is>
           <t>祥泰</t>
         </is>
       </c>
-      <c r="H45" t="inlineStr"/>
-      <c r="I45" t="inlineStr"/>
-      <c r="J45" t="inlineStr"/>
-      <c r="K45" t="inlineStr"/>
       <c r="L45" t="inlineStr">
         <is>
           <t>祥泰，存塘二两小鱼，有欠款。</t>
@@ -2202,9 +1915,6 @@
           <t>三、潜力培育中</t>
         </is>
       </c>
-      <c r="D46" t="inlineStr"/>
-      <c r="E46" t="inlineStr"/>
-      <c r="F46" t="inlineStr"/>
       <c r="G46" t="inlineStr">
         <is>
           <t>祥泰</t>
@@ -2215,9 +1925,6 @@
           <t>朱康永</t>
         </is>
       </c>
-      <c r="I46" t="inlineStr"/>
-      <c r="J46" t="inlineStr"/>
-      <c r="K46" t="inlineStr"/>
       <c r="L46" t="inlineStr">
         <is>
           <t>跟朱康永拿料，祥泰，资金周转困难。</t>
@@ -2243,11 +1950,9 @@
           <t>三、潜力培育中</t>
         </is>
       </c>
-      <c r="D47" t="inlineStr"/>
       <c r="E47" t="n">
         <v>3</v>
       </c>
-      <c r="F47" t="inlineStr"/>
       <c r="G47" t="inlineStr">
         <is>
           <t>祥泰</t>
@@ -2258,8 +1963,6 @@
           <t>符策锋</t>
         </is>
       </c>
-      <c r="I47" t="inlineStr"/>
-      <c r="J47" t="inlineStr"/>
       <c r="K47" t="inlineStr">
         <is>
           <t>40</t>
@@ -2290,14 +1993,6 @@
           <t>三、潜力培育中</t>
         </is>
       </c>
-      <c r="D48" t="inlineStr"/>
-      <c r="E48" t="inlineStr"/>
-      <c r="F48" t="inlineStr"/>
-      <c r="G48" t="inlineStr"/>
-      <c r="H48" t="inlineStr"/>
-      <c r="I48" t="inlineStr"/>
-      <c r="J48" t="inlineStr"/>
-      <c r="K48" t="inlineStr"/>
       <c r="L48" t="inlineStr">
         <is>
           <t>经销商，转用通威需折扣支持。</t>
@@ -2323,18 +2018,11 @@
           <t>三、潜力培育中</t>
         </is>
       </c>
-      <c r="D49" t="inlineStr"/>
-      <c r="E49" t="inlineStr"/>
-      <c r="F49" t="inlineStr"/>
       <c r="G49" t="inlineStr">
         <is>
           <t>粤海</t>
         </is>
       </c>
-      <c r="H49" t="inlineStr"/>
-      <c r="I49" t="inlineStr"/>
-      <c r="J49" t="inlineStr"/>
-      <c r="K49" t="inlineStr"/>
       <c r="L49" t="inlineStr">
         <is>
           <t>之前做料商，自存一批粤海料。</t>
@@ -2360,18 +2048,11 @@
           <t>三、潜力培育中</t>
         </is>
       </c>
-      <c r="D50" t="inlineStr"/>
-      <c r="E50" t="inlineStr"/>
-      <c r="F50" t="inlineStr"/>
-      <c r="G50" t="inlineStr"/>
       <c r="H50" t="inlineStr">
         <is>
           <t>郑标远</t>
         </is>
       </c>
-      <c r="I50" t="inlineStr"/>
-      <c r="J50" t="inlineStr"/>
-      <c r="K50" t="inlineStr"/>
       <c r="L50" t="inlineStr">
         <is>
           <t>跟郑标远拿料，未用通威。</t>
@@ -2397,9 +2078,6 @@
           <t>三、潜力培育中</t>
         </is>
       </c>
-      <c r="D51" t="inlineStr"/>
-      <c r="E51" t="inlineStr"/>
-      <c r="F51" t="inlineStr"/>
       <c r="G51" t="inlineStr">
         <is>
           <t>海大</t>
@@ -2410,9 +2088,6 @@
           <t>王焕忠</t>
         </is>
       </c>
-      <c r="I51" t="inlineStr"/>
-      <c r="J51" t="inlineStr"/>
-      <c r="K51" t="inlineStr"/>
       <c r="L51" t="inlineStr">
         <is>
           <t>跟王焕忠拿料，海大老用户，换料意愿低。</t>
@@ -2438,18 +2113,11 @@
           <t>三、潜力培育中</t>
         </is>
       </c>
-      <c r="D52" t="inlineStr"/>
-      <c r="E52" t="inlineStr"/>
-      <c r="F52" t="inlineStr"/>
       <c r="G52" t="inlineStr">
         <is>
           <t>新希望</t>
         </is>
       </c>
-      <c r="H52" t="inlineStr"/>
-      <c r="I52" t="inlineStr"/>
-      <c r="J52" t="inlineStr"/>
-      <c r="K52" t="inlineStr"/>
       <c r="L52" t="inlineStr">
         <is>
           <t>新希望老用户。</t>
@@ -2475,18 +2143,11 @@
           <t>三、潜力培育中</t>
         </is>
       </c>
-      <c r="D53" t="inlineStr"/>
-      <c r="E53" t="inlineStr"/>
-      <c r="F53" t="inlineStr"/>
-      <c r="G53" t="inlineStr"/>
       <c r="H53" t="inlineStr">
         <is>
           <t>符侧锋暂不拿货</t>
         </is>
       </c>
-      <c r="I53" t="inlineStr"/>
-      <c r="J53" t="inlineStr"/>
-      <c r="K53" t="inlineStr"/>
       <c r="L53" t="inlineStr">
         <is>
           <t>现经销商符侧锋暂不拿货，引导更换经销商中。</t>
@@ -2512,14 +2173,6 @@
           <t>三、潜力培育中</t>
         </is>
       </c>
-      <c r="D54" t="inlineStr"/>
-      <c r="E54" t="inlineStr"/>
-      <c r="F54" t="inlineStr"/>
-      <c r="G54" t="inlineStr"/>
-      <c r="H54" t="inlineStr"/>
-      <c r="I54" t="inlineStr"/>
-      <c r="J54" t="inlineStr"/>
-      <c r="K54" t="inlineStr"/>
       <c r="L54" t="inlineStr">
         <is>
           <t>走访时用户不在家。</t>
@@ -2545,14 +2198,6 @@
           <t>三、潜力培育中</t>
         </is>
       </c>
-      <c r="D55" t="inlineStr"/>
-      <c r="E55" t="inlineStr"/>
-      <c r="F55" t="inlineStr"/>
-      <c r="G55" t="inlineStr"/>
-      <c r="H55" t="inlineStr"/>
-      <c r="I55" t="inlineStr"/>
-      <c r="J55" t="inlineStr"/>
-      <c r="K55" t="inlineStr"/>
       <c r="L55" t="inlineStr">
         <is>
           <t>当地声望高，片区影响力大。</t>
@@ -2578,14 +2223,6 @@
           <t>三、潜力培育中</t>
         </is>
       </c>
-      <c r="D56" t="inlineStr"/>
-      <c r="E56" t="inlineStr"/>
-      <c r="F56" t="inlineStr"/>
-      <c r="G56" t="inlineStr"/>
-      <c r="H56" t="inlineStr"/>
-      <c r="I56" t="inlineStr"/>
-      <c r="J56" t="inlineStr"/>
-      <c r="K56" t="inlineStr"/>
       <c r="L56" t="inlineStr">
         <is>
           <t>协助运送动保。</t>
@@ -2611,18 +2248,11 @@
           <t>三、潜力培育中</t>
         </is>
       </c>
-      <c r="D57" t="inlineStr"/>
-      <c r="E57" t="inlineStr"/>
-      <c r="F57" t="inlineStr"/>
       <c r="G57" t="inlineStr">
         <is>
           <t>海大</t>
         </is>
       </c>
-      <c r="H57" t="inlineStr"/>
-      <c r="I57" t="inlineStr"/>
-      <c r="J57" t="inlineStr"/>
-      <c r="K57" t="inlineStr"/>
       <c r="L57" t="inlineStr">
         <is>
           <t>对接海大动保业务人员。</t>
@@ -2648,14 +2278,6 @@
           <t>三、潜力培育中</t>
         </is>
       </c>
-      <c r="D58" t="inlineStr"/>
-      <c r="E58" t="inlineStr"/>
-      <c r="F58" t="inlineStr"/>
-      <c r="G58" t="inlineStr"/>
-      <c r="H58" t="inlineStr"/>
-      <c r="I58" t="inlineStr"/>
-      <c r="J58" t="inlineStr"/>
-      <c r="K58" t="inlineStr"/>
       <c r="L58" t="inlineStr">
         <is>
           <t>换料意愿不强。</t>
@@ -2681,14 +2303,6 @@
           <t>三、潜力培育中</t>
         </is>
       </c>
-      <c r="D59" t="inlineStr"/>
-      <c r="E59" t="inlineStr"/>
-      <c r="F59" t="inlineStr"/>
-      <c r="G59" t="inlineStr"/>
-      <c r="H59" t="inlineStr"/>
-      <c r="I59" t="inlineStr"/>
-      <c r="J59" t="inlineStr"/>
-      <c r="K59" t="inlineStr"/>
       <c r="L59" t="inlineStr">
         <is>
           <t>测水跟进养殖情况。</t>
@@ -2714,18 +2328,11 @@
           <t>三、潜力培育中</t>
         </is>
       </c>
-      <c r="D60" t="inlineStr"/>
-      <c r="E60" t="inlineStr"/>
-      <c r="F60" t="inlineStr"/>
       <c r="G60" t="inlineStr">
         <is>
           <t>粤农</t>
         </is>
       </c>
-      <c r="H60" t="inlineStr"/>
-      <c r="I60" t="inlineStr"/>
-      <c r="J60" t="inlineStr"/>
-      <c r="K60" t="inlineStr"/>
       <c r="L60" t="inlineStr">
         <is>
           <t>用粤农鸭料。</t>
@@ -2751,18 +2358,11 @@
           <t>三、潜力培育中</t>
         </is>
       </c>
-      <c r="D61" t="inlineStr"/>
-      <c r="E61" t="inlineStr"/>
-      <c r="F61" t="inlineStr"/>
       <c r="G61" t="inlineStr">
         <is>
           <t>蜀海</t>
         </is>
       </c>
-      <c r="H61" t="inlineStr"/>
-      <c r="I61" t="inlineStr"/>
-      <c r="J61" t="inlineStr"/>
-      <c r="K61" t="inlineStr"/>
       <c r="L61" t="inlineStr">
         <is>
           <t>多基地混养草鱼、鲢鳙，蜀海料加发酵料加鸭料，看重性价比。</t>
@@ -2788,20 +2388,14 @@
           <t>三、潜力培育中</t>
         </is>
       </c>
-      <c r="D62" t="inlineStr"/>
       <c r="E62" t="n">
         <v>6</v>
       </c>
-      <c r="F62" t="inlineStr"/>
       <c r="G62" t="inlineStr">
         <is>
           <t>金长城</t>
         </is>
       </c>
-      <c r="H62" t="inlineStr"/>
-      <c r="I62" t="inlineStr"/>
-      <c r="J62" t="inlineStr"/>
-      <c r="K62" t="inlineStr"/>
       <c r="L62" t="inlineStr">
         <is>
           <t>六口虾塘，金长城虾料。</t>
@@ -2827,14 +2421,6 @@
           <t>三、潜力培育中</t>
         </is>
       </c>
-      <c r="D63" t="inlineStr"/>
-      <c r="E63" t="inlineStr"/>
-      <c r="F63" t="inlineStr"/>
-      <c r="G63" t="inlineStr"/>
-      <c r="H63" t="inlineStr"/>
-      <c r="I63" t="inlineStr"/>
-      <c r="J63" t="inlineStr"/>
-      <c r="K63" t="inlineStr"/>
       <c r="L63" t="inlineStr">
         <is>
           <t>塘口租期临近，暂不考虑装料塔，经营药店。</t>
@@ -2860,18 +2446,11 @@
           <t>三、潜力培育中</t>
         </is>
       </c>
-      <c r="D64" t="inlineStr"/>
-      <c r="E64" t="inlineStr"/>
-      <c r="F64" t="inlineStr"/>
       <c r="G64" t="inlineStr">
         <is>
           <t>祥泰</t>
         </is>
       </c>
-      <c r="H64" t="inlineStr"/>
-      <c r="I64" t="inlineStr"/>
-      <c r="J64" t="inlineStr"/>
-      <c r="K64" t="inlineStr"/>
       <c r="L64" t="inlineStr">
         <is>
           <t>仓库存放祥泰饲料。</t>
@@ -2897,14 +2476,6 @@
           <t>三、潜力培育中</t>
         </is>
       </c>
-      <c r="D65" t="inlineStr"/>
-      <c r="E65" t="inlineStr"/>
-      <c r="F65" t="inlineStr"/>
-      <c r="G65" t="inlineStr"/>
-      <c r="H65" t="inlineStr"/>
-      <c r="I65" t="inlineStr"/>
-      <c r="J65" t="inlineStr"/>
-      <c r="K65" t="inlineStr"/>
       <c r="L65" t="inlineStr">
         <is>
           <t>鱼价低迷，暂时停养。</t>
@@ -2930,14 +2501,6 @@
           <t>三、潜力培育中</t>
         </is>
       </c>
-      <c r="D66" t="inlineStr"/>
-      <c r="E66" t="inlineStr"/>
-      <c r="F66" t="inlineStr"/>
-      <c r="G66" t="inlineStr"/>
-      <c r="H66" t="inlineStr"/>
-      <c r="I66" t="inlineStr"/>
-      <c r="J66" t="inlineStr"/>
-      <c r="K66" t="inlineStr"/>
       <c r="L66" t="inlineStr">
         <is>
           <t>已退出，之前养石斑鱼，现转养罗非。</t>
@@ -2963,14 +2526,6 @@
           <t>三、潜力培育中</t>
         </is>
       </c>
-      <c r="D67" t="inlineStr"/>
-      <c r="E67" t="inlineStr"/>
-      <c r="F67" t="inlineStr"/>
-      <c r="G67" t="inlineStr"/>
-      <c r="H67" t="inlineStr"/>
-      <c r="I67" t="inlineStr"/>
-      <c r="J67" t="inlineStr"/>
-      <c r="K67" t="inlineStr"/>
       <c r="L67" t="inlineStr">
         <is>
           <t>塘口已更换老板。</t>
@@ -2996,7 +2551,6 @@
           <t>三、潜力培育中</t>
         </is>
       </c>
-      <c r="D68" t="inlineStr"/>
       <c r="E68" t="n">
         <v>2</v>
       </c>
@@ -3005,15 +2559,11 @@
           <t>50</t>
         </is>
       </c>
-      <c r="G68" t="inlineStr"/>
       <c r="H68" t="inlineStr">
         <is>
           <t>黄友孝</t>
         </is>
       </c>
-      <c r="I68" t="inlineStr"/>
-      <c r="J68" t="inlineStr"/>
-      <c r="K68" t="inlineStr"/>
       <c r="L68" t="inlineStr">
         <is>
           <t>转做畜禽养殖，两口塘约50亩，跟黄友孝拿料。</t>
@@ -3039,9 +2589,6 @@
           <t>三、潜力培育中</t>
         </is>
       </c>
-      <c r="D69" t="inlineStr"/>
-      <c r="E69" t="inlineStr"/>
-      <c r="F69" t="inlineStr"/>
       <c r="G69" t="inlineStr">
         <is>
           <t>唐人神（小料）、天翔819（大料）</t>
@@ -3052,9 +2599,6 @@
           <t>原添祥、郑海杰，现待问清</t>
         </is>
       </c>
-      <c r="I69" t="inlineStr"/>
-      <c r="J69" t="inlineStr"/>
-      <c r="K69" t="inlineStr"/>
       <c r="L69" t="inlineStr">
         <is>
           <t>10.09走访：用料已更换，现小料唐人神、大料天翔819（挂账价114，属低档料，判断难养出效果）；现跟谁拿料待问清。鱼苗和大头混养，宝路苗，鱼现八两左右，预计11月初出鱼。【名字确认：名单原“施军华”“司君华”均为同一人施君华；10.05客情维护走访】</t>
@@ -3080,14 +2624,6 @@
           <t>三、潜力培育中</t>
         </is>
       </c>
-      <c r="D70" t="inlineStr"/>
-      <c r="E70" t="inlineStr"/>
-      <c r="F70" t="inlineStr"/>
-      <c r="G70" t="inlineStr"/>
-      <c r="H70" t="inlineStr"/>
-      <c r="I70" t="inlineStr"/>
-      <c r="J70" t="inlineStr"/>
-      <c r="K70" t="inlineStr"/>
       <c r="L70" t="inlineStr">
         <is>
           <t>老客户维护。</t>
@@ -3113,14 +2649,6 @@
           <t>三、潜力培育中</t>
         </is>
       </c>
-      <c r="D71" t="inlineStr"/>
-      <c r="E71" t="inlineStr"/>
-      <c r="F71" t="inlineStr"/>
-      <c r="G71" t="inlineStr"/>
-      <c r="H71" t="inlineStr"/>
-      <c r="I71" t="inlineStr"/>
-      <c r="J71" t="inlineStr"/>
-      <c r="K71" t="inlineStr"/>
       <c r="L71" t="inlineStr">
         <is>
           <t>老客户维护。</t>
@@ -3146,10 +2674,6 @@
           <t>三、潜力培育中</t>
         </is>
       </c>
-      <c r="D72" t="inlineStr"/>
-      <c r="E72" t="inlineStr"/>
-      <c r="F72" t="inlineStr"/>
-      <c r="G72" t="inlineStr"/>
       <c r="H72" t="inlineStr">
         <is>
           <t>马津深</t>
@@ -3160,8 +2684,6 @@
           <t>父母及工人</t>
         </is>
       </c>
-      <c r="J72" t="inlineStr"/>
-      <c r="K72" t="inlineStr"/>
       <c r="L72" t="inlineStr">
         <is>
           <t>跟马津深拿料，本人已回浙江，塘口由父母及工人负责。</t>
@@ -3187,18 +2709,11 @@
           <t>三、潜力培育中</t>
         </is>
       </c>
-      <c r="D73" t="inlineStr"/>
-      <c r="E73" t="inlineStr"/>
-      <c r="F73" t="inlineStr"/>
       <c r="G73" t="inlineStr">
         <is>
           <t>祥泰</t>
         </is>
       </c>
-      <c r="H73" t="inlineStr"/>
-      <c r="I73" t="inlineStr"/>
-      <c r="J73" t="inlineStr"/>
-      <c r="K73" t="inlineStr"/>
       <c r="L73" t="inlineStr">
         <is>
           <t>祥泰料，老板不在。</t>
@@ -3224,18 +2739,11 @@
           <t>三、潜力培育中</t>
         </is>
       </c>
-      <c r="D74" t="inlineStr"/>
-      <c r="E74" t="inlineStr"/>
-      <c r="F74" t="inlineStr"/>
       <c r="G74" t="inlineStr">
         <is>
           <t>百洋</t>
         </is>
       </c>
-      <c r="H74" t="inlineStr"/>
-      <c r="I74" t="inlineStr"/>
-      <c r="J74" t="inlineStr"/>
-      <c r="K74" t="inlineStr"/>
       <c r="L74" t="inlineStr">
         <is>
           <t>用过通威、嫌贵，现用百洋。</t>
@@ -3261,14 +2769,6 @@
           <t>三、潜力培育中</t>
         </is>
       </c>
-      <c r="D75" t="inlineStr"/>
-      <c r="E75" t="inlineStr"/>
-      <c r="F75" t="inlineStr"/>
-      <c r="G75" t="inlineStr"/>
-      <c r="H75" t="inlineStr"/>
-      <c r="I75" t="inlineStr"/>
-      <c r="J75" t="inlineStr"/>
-      <c r="K75" t="inlineStr"/>
       <c r="L75" t="inlineStr">
         <is>
           <t>外出不在。</t>
@@ -3294,18 +2794,11 @@
           <t>三、潜力培育中</t>
         </is>
       </c>
-      <c r="D76" t="inlineStr"/>
-      <c r="E76" t="inlineStr"/>
-      <c r="F76" t="inlineStr"/>
       <c r="G76" t="inlineStr">
         <is>
           <t>通力</t>
         </is>
       </c>
-      <c r="H76" t="inlineStr"/>
-      <c r="I76" t="inlineStr"/>
-      <c r="J76" t="inlineStr"/>
-      <c r="K76" t="inlineStr"/>
       <c r="L76" t="inlineStr">
         <is>
           <t>畜禽养殖，通力413。</t>
@@ -3331,18 +2824,11 @@
           <t>三、潜力培育中</t>
         </is>
       </c>
-      <c r="D77" t="inlineStr"/>
-      <c r="E77" t="inlineStr"/>
-      <c r="F77" t="inlineStr"/>
       <c r="G77" t="inlineStr">
         <is>
           <t>鸿业</t>
         </is>
       </c>
-      <c r="H77" t="inlineStr"/>
-      <c r="I77" t="inlineStr"/>
-      <c r="J77" t="inlineStr"/>
-      <c r="K77" t="inlineStr"/>
       <c r="L77" t="inlineStr">
         <is>
           <t>做种苗，海南一号种苗，鸿业粉料。</t>
@@ -3368,22 +2854,16 @@
           <t>三、潜力培育中</t>
         </is>
       </c>
-      <c r="D78" t="inlineStr"/>
-      <c r="E78" t="inlineStr"/>
       <c r="F78" t="inlineStr">
         <is>
           <t>40</t>
         </is>
       </c>
-      <c r="G78" t="inlineStr"/>
       <c r="H78" t="inlineStr">
         <is>
           <t>周公保</t>
         </is>
       </c>
-      <c r="I78" t="inlineStr"/>
-      <c r="J78" t="inlineStr"/>
-      <c r="K78" t="inlineStr"/>
       <c r="L78" t="inlineStr">
         <is>
           <t>40亩左右，跟周公保拿料。</t>
@@ -3409,18 +2889,11 @@
           <t>三、潜力培育中</t>
         </is>
       </c>
-      <c r="D79" t="inlineStr"/>
-      <c r="E79" t="inlineStr"/>
-      <c r="F79" t="inlineStr"/>
       <c r="G79" t="inlineStr">
         <is>
           <t>百洋5602</t>
         </is>
       </c>
-      <c r="H79" t="inlineStr"/>
-      <c r="I79" t="inlineStr"/>
-      <c r="J79" t="inlineStr"/>
-      <c r="K79" t="inlineStr"/>
       <c r="L79" t="inlineStr">
         <is>
           <t>百洋5602，二两鱼。 【10.07补充：冯学新兼做歌颂料渠道，吴杨松跟其拿现金料105元/包；其本人仍用百洋5602】</t>
@@ -3446,18 +2919,11 @@
           <t>三、潜力培育中</t>
         </is>
       </c>
-      <c r="D80" t="inlineStr"/>
-      <c r="E80" t="inlineStr"/>
-      <c r="F80" t="inlineStr"/>
       <c r="G80" t="inlineStr">
         <is>
           <t>百洋</t>
         </is>
       </c>
-      <c r="H80" t="inlineStr"/>
-      <c r="I80" t="inlineStr"/>
-      <c r="J80" t="inlineStr"/>
-      <c r="K80" t="inlineStr"/>
       <c r="L80" t="inlineStr">
         <is>
           <t>百洋，二两鱼。</t>
@@ -3483,18 +2949,11 @@
           <t>三、潜力培育中</t>
         </is>
       </c>
-      <c r="D81" t="inlineStr"/>
-      <c r="E81" t="inlineStr"/>
-      <c r="F81" t="inlineStr"/>
       <c r="G81" t="inlineStr">
         <is>
           <t>百洋5602</t>
         </is>
       </c>
-      <c r="H81" t="inlineStr"/>
-      <c r="I81" t="inlineStr"/>
-      <c r="J81" t="inlineStr"/>
-      <c r="K81" t="inlineStr"/>
       <c r="L81" t="inlineStr">
         <is>
           <t>百洋5602和百洋小料。</t>
@@ -3520,20 +2979,14 @@
           <t>三、潜力培育中</t>
         </is>
       </c>
-      <c r="D82" t="inlineStr"/>
       <c r="E82" t="n">
         <v>5</v>
       </c>
-      <c r="F82" t="inlineStr"/>
       <c r="G82" t="inlineStr">
         <is>
           <t>百洋5602</t>
         </is>
       </c>
-      <c r="H82" t="inlineStr"/>
-      <c r="I82" t="inlineStr"/>
-      <c r="J82" t="inlineStr"/>
-      <c r="K82" t="inlineStr"/>
       <c r="L82" t="inlineStr">
         <is>
           <t>百洋5602，5口塘加1口苗塘，鱼1.2斤，宝路苗。</t>
@@ -3559,9 +3012,6 @@
           <t>三、潜力培育中</t>
         </is>
       </c>
-      <c r="D83" t="inlineStr"/>
-      <c r="E83" t="inlineStr"/>
-      <c r="F83" t="inlineStr"/>
       <c r="G83" t="inlineStr">
         <is>
           <t>粤海2号</t>
@@ -3572,9 +3022,6 @@
           <t>符策锋</t>
         </is>
       </c>
-      <c r="I83" t="inlineStr"/>
-      <c r="J83" t="inlineStr"/>
-      <c r="K83" t="inlineStr"/>
       <c r="L83" t="inlineStr">
         <is>
           <t>跟符策锋拿料，粤海2号料，之前在锦山养亏较多。</t>
@@ -3600,19 +3047,14 @@
           <t>三、潜力培育中</t>
         </is>
       </c>
-      <c r="D84" t="inlineStr"/>
       <c r="E84" t="n">
         <v>2</v>
       </c>
-      <c r="F84" t="inlineStr"/>
       <c r="G84" t="inlineStr">
         <is>
           <t>粤海</t>
         </is>
       </c>
-      <c r="H84" t="inlineStr"/>
-      <c r="I84" t="inlineStr"/>
-      <c r="J84" t="inlineStr"/>
       <c r="K84" t="inlineStr">
         <is>
           <t>41</t>
@@ -3643,18 +3085,11 @@
           <t>三、潜力培育中</t>
         </is>
       </c>
-      <c r="D85" t="inlineStr"/>
-      <c r="E85" t="inlineStr"/>
-      <c r="F85" t="inlineStr"/>
       <c r="G85" t="inlineStr">
         <is>
           <t>海大2552</t>
         </is>
       </c>
-      <c r="H85" t="inlineStr"/>
-      <c r="I85" t="inlineStr"/>
-      <c r="J85" t="inlineStr"/>
-      <c r="K85" t="inlineStr"/>
       <c r="L85" t="inlineStr">
         <is>
           <t>海大2552，八两鱼。</t>
@@ -3680,19 +3115,14 @@
           <t>三、潜力培育中</t>
         </is>
       </c>
-      <c r="D86" t="inlineStr"/>
       <c r="E86" t="n">
         <v>6</v>
       </c>
-      <c r="F86" t="inlineStr"/>
       <c r="G86" t="inlineStr">
         <is>
           <t>粤海</t>
         </is>
       </c>
-      <c r="H86" t="inlineStr"/>
-      <c r="I86" t="inlineStr"/>
-      <c r="J86" t="inlineStr"/>
       <c r="K86" t="inlineStr">
         <is>
           <t>40</t>
@@ -3728,7 +3158,6 @@
           <t>抱罗基地</t>
         </is>
       </c>
-      <c r="E87" t="inlineStr"/>
       <c r="F87" t="inlineStr">
         <is>
           <t>100多</t>
@@ -3739,10 +3168,6 @@
           <t>海一</t>
         </is>
       </c>
-      <c r="H87" t="inlineStr"/>
-      <c r="I87" t="inlineStr"/>
-      <c r="J87" t="inlineStr"/>
-      <c r="K87" t="inlineStr"/>
       <c r="L87" t="inlineStr">
         <is>
           <t>100多亩，抱罗基地已换海一料。</t>
@@ -3768,18 +3193,11 @@
           <t>三、潜力培育中</t>
         </is>
       </c>
-      <c r="D88" t="inlineStr"/>
-      <c r="E88" t="inlineStr"/>
       <c r="F88" t="inlineStr">
         <is>
           <t>25</t>
         </is>
       </c>
-      <c r="G88" t="inlineStr"/>
-      <c r="H88" t="inlineStr"/>
-      <c r="I88" t="inlineStr"/>
-      <c r="J88" t="inlineStr"/>
-      <c r="K88" t="inlineStr"/>
       <c r="L88" t="inlineStr">
         <is>
           <t>罗非母鱼塘25亩，用料少。</t>
@@ -3805,7 +3223,6 @@
           <t>三、潜力培育中</t>
         </is>
       </c>
-      <c r="D89" t="inlineStr"/>
       <c r="E89" t="n">
         <v>1</v>
       </c>
@@ -3814,11 +3231,6 @@
           <t>45</t>
         </is>
       </c>
-      <c r="G89" t="inlineStr"/>
-      <c r="H89" t="inlineStr"/>
-      <c r="I89" t="inlineStr"/>
-      <c r="J89" t="inlineStr"/>
-      <c r="K89" t="inlineStr"/>
       <c r="L89" t="inlineStr">
         <is>
           <t>45亩一口塘，老板指定拿料。</t>
@@ -3844,18 +3256,11 @@
           <t>三、潜力培育中</t>
         </is>
       </c>
-      <c r="D90" t="inlineStr"/>
-      <c r="E90" t="inlineStr"/>
-      <c r="F90" t="inlineStr"/>
       <c r="G90" t="inlineStr">
         <is>
           <t>祥泰</t>
         </is>
       </c>
-      <c r="H90" t="inlineStr"/>
-      <c r="I90" t="inlineStr"/>
-      <c r="J90" t="inlineStr"/>
-      <c r="K90" t="inlineStr"/>
       <c r="L90" t="inlineStr">
         <is>
           <t>经销商，主营叉尾，祥泰料，上一造效果不理想。</t>
@@ -3889,16 +3294,11 @@
       <c r="E91" t="n">
         <v>1</v>
       </c>
-      <c r="F91" t="inlineStr"/>
       <c r="G91" t="inlineStr">
         <is>
           <t>百洋</t>
         </is>
       </c>
-      <c r="H91" t="inlineStr"/>
-      <c r="I91" t="inlineStr"/>
-      <c r="J91" t="inlineStr"/>
-      <c r="K91" t="inlineStr"/>
       <c r="L91" t="inlineStr">
         <is>
           <t>百洋用户，另有一口塘在凤尾在建。</t>
@@ -3929,17 +3329,11 @@
           <t>海大基地</t>
         </is>
       </c>
-      <c r="E92" t="inlineStr"/>
-      <c r="F92" t="inlineStr"/>
       <c r="G92" t="inlineStr">
         <is>
           <t>海大</t>
         </is>
       </c>
-      <c r="H92" t="inlineStr"/>
-      <c r="I92" t="inlineStr"/>
-      <c r="J92" t="inlineStr"/>
-      <c r="K92" t="inlineStr"/>
       <c r="L92" t="inlineStr">
         <is>
           <t>海大基地，虾塘改造为罗非鱼苗塘。</t>
@@ -3965,18 +3359,11 @@
           <t>三、潜力培育中</t>
         </is>
       </c>
-      <c r="D93" t="inlineStr"/>
-      <c r="E93" t="inlineStr"/>
-      <c r="F93" t="inlineStr"/>
       <c r="G93" t="inlineStr">
         <is>
           <t>疑似海大动保</t>
         </is>
       </c>
-      <c r="H93" t="inlineStr"/>
-      <c r="I93" t="inlineStr"/>
-      <c r="J93" t="inlineStr"/>
-      <c r="K93" t="inlineStr"/>
       <c r="L93" t="inlineStr">
         <is>
           <t>【10.07走访，用户不在场，见塘口有无人机作业；塘口约三口，规模偏小，推断无人机非自购，疑为海大动保飞防服务（海大动保有无人机直服）；用料情况待核实】 【名字确认：张秋海】</t>
@@ -4007,8 +3394,6 @@
           <t>锦山</t>
         </is>
       </c>
-      <c r="E94" t="inlineStr"/>
-      <c r="F94" t="inlineStr"/>
       <c r="G94" t="inlineStr">
         <is>
           <t>歌颂</t>
@@ -4019,9 +3404,6 @@
           <t>冯学新</t>
         </is>
       </c>
-      <c r="I94" t="inlineStr"/>
-      <c r="J94" t="inlineStr"/>
-      <c r="K94" t="inlineStr"/>
       <c r="L94" t="inlineStr">
         <is>
           <t>【10.07走访：现用歌颂饲料，跟冯学新拿现金料，105元/包（正常价121元）；很早之前用过通威沉水颗粒料，后用过百洋（反馈一般），现转歌颂；自"建一"出来（口述，具体所指待确认）后一直跟冯学新拿料】</t>
@@ -4047,9 +3429,6 @@
           <t>三、潜力培育中</t>
         </is>
       </c>
-      <c r="D95" t="inlineStr"/>
-      <c r="E95" t="inlineStr"/>
-      <c r="F95" t="inlineStr"/>
       <c r="G95" t="inlineStr">
         <is>
           <t>祥泰</t>
@@ -4060,8 +3439,6 @@
           <t>田永均</t>
         </is>
       </c>
-      <c r="I95" t="inlineStr"/>
-      <c r="J95" t="inlineStr"/>
       <c r="K95" t="inlineStr">
         <is>
           <t>43-44</t>
@@ -4072,7 +3449,6 @@
           <t>【10.07走访，老板不在，向工人了解情况：一直在用祥泰，跟田永均（店面在抱罗）拿料，半现金结算；存塘鱼五两左右，预计元旦前出鱼，工人反馈包产43-44；老板在等价格】（10.07走访未写入当日日志，留待下次汇报）</t>
         </is>
       </c>
-      <c r="M95" t="inlineStr"/>
     </row>
     <row r="96">
       <c r="A96" t="n">
@@ -4088,9 +3464,6 @@
           <t>三、潜力培育中</t>
         </is>
       </c>
-      <c r="D96" t="inlineStr"/>
-      <c r="E96" t="inlineStr"/>
-      <c r="F96" t="inlineStr"/>
       <c r="G96" t="inlineStr">
         <is>
           <t>金长城、百洋、海大</t>
@@ -4101,15 +3474,11 @@
           <t>昌盛</t>
         </is>
       </c>
-      <c r="I96" t="inlineStr"/>
-      <c r="J96" t="inlineStr"/>
-      <c r="K96" t="inlineStr"/>
       <c r="L96" t="inlineStr">
         <is>
           <t>【10.07走访：跟昌盛（其同学）拿料，现混用金长城+百洋+海大；塘口在修投料机，此前停养一段时间，现打算恢复养殖】</t>
         </is>
       </c>
-      <c r="M96" t="inlineStr"/>
     </row>
     <row r="97">
       <c r="A97" t="n">
@@ -4130,19 +3499,11 @@
           <t>海口市美兰区三江镇212省道</t>
         </is>
       </c>
-      <c r="E97" t="inlineStr"/>
-      <c r="F97" t="inlineStr"/>
-      <c r="G97" t="inlineStr"/>
-      <c r="H97" t="inlineStr"/>
-      <c r="I97" t="inlineStr"/>
-      <c r="J97" t="inlineStr"/>
-      <c r="K97" t="inlineStr"/>
       <c r="L97" t="inlineStr">
         <is>
           <t>【10.08走访基地测水（10:47）：基地剩一口大鱼塘，预计下周出鱼，其余为苗塘；测水数据待补录。注：马津深同时为经销商渠道，章建龙、应富伟跟其拿料】</t>
         </is>
       </c>
-      <c r="M97" t="inlineStr"/>
     </row>
     <row r="98">
       <c r="A98" t="n">
@@ -4158,24 +3519,16 @@
           <t>三、潜力培育中</t>
         </is>
       </c>
-      <c r="D98" t="inlineStr"/>
-      <c r="E98" t="inlineStr"/>
-      <c r="F98" t="inlineStr"/>
       <c r="G98" t="inlineStr">
         <is>
           <t>海大2552</t>
         </is>
       </c>
-      <c r="H98" t="inlineStr"/>
-      <c r="I98" t="inlineStr"/>
-      <c r="J98" t="inlineStr"/>
-      <c r="K98" t="inlineStr"/>
       <c r="L98" t="inlineStr">
         <is>
           <t>【10.08走访：用户不在鱼塘，仓库内见海大2552料，择日再访】</t>
         </is>
       </c>
-      <c r="M98" t="inlineStr"/>
     </row>
     <row r="99">
       <c r="A99" t="n">
@@ -4191,9 +3544,6 @@
           <t>三、潜力培育中</t>
         </is>
       </c>
-      <c r="D99" t="inlineStr"/>
-      <c r="E99" t="inlineStr"/>
-      <c r="F99" t="inlineStr"/>
       <c r="G99" t="inlineStr">
         <is>
           <t>歌颂、璃元</t>
@@ -4204,8 +3554,6 @@
           <t>陈儒、三弟</t>
         </is>
       </c>
-      <c r="I99" t="inlineStr"/>
-      <c r="J99" t="inlineStr"/>
       <c r="K99" t="inlineStr">
         <is>
           <t>43左右</t>
@@ -4216,7 +3564,6 @@
           <t>【10.08走访，交谈养殖情况：现金料用户，现用歌颂和璃元（本地料），包产43左右，跟陈儒和三弟拿料；对通威印象最近变差，认为价格偏高】</t>
         </is>
       </c>
-      <c r="M99" t="inlineStr"/>
     </row>
     <row r="100">
       <c r="A100" t="n">
@@ -4232,14 +3579,6 @@
           <t>三、潜力培育中</t>
         </is>
       </c>
-      <c r="D100" t="inlineStr"/>
-      <c r="E100" t="inlineStr"/>
-      <c r="F100" t="inlineStr"/>
-      <c r="G100" t="inlineStr"/>
-      <c r="H100" t="inlineStr"/>
-      <c r="I100" t="inlineStr"/>
-      <c r="J100" t="inlineStr"/>
-      <c r="K100" t="inlineStr"/>
       <c r="L100" t="inlineStr">
         <is>
           <t>10.09走访不在家，未交谈。</t>
@@ -4265,14 +3604,6 @@
           <t>三、潜力培育中</t>
         </is>
       </c>
-      <c r="D101" t="inlineStr"/>
-      <c r="E101" t="inlineStr"/>
-      <c r="F101" t="inlineStr"/>
-      <c r="G101" t="inlineStr"/>
-      <c r="H101" t="inlineStr"/>
-      <c r="I101" t="inlineStr"/>
-      <c r="J101" t="inlineStr"/>
-      <c r="K101" t="inlineStr"/>
       <c r="L101" t="inlineStr">
         <is>
           <t>10.09走访不在家，未交谈。</t>
@@ -4298,14 +3629,6 @@
           <t>三、潜力培育中</t>
         </is>
       </c>
-      <c r="D102" t="inlineStr"/>
-      <c r="E102" t="inlineStr"/>
-      <c r="F102" t="inlineStr"/>
-      <c r="G102" t="inlineStr"/>
-      <c r="H102" t="inlineStr"/>
-      <c r="I102" t="inlineStr"/>
-      <c r="J102" t="inlineStr"/>
-      <c r="K102" t="inlineStr"/>
       <c r="L102" t="inlineStr">
         <is>
           <t>10.09走访不在家，未交谈。</t>
@@ -4331,9 +3654,6 @@
           <t>三、潜力培育中</t>
         </is>
       </c>
-      <c r="D103" t="inlineStr"/>
-      <c r="E103" t="inlineStr"/>
-      <c r="F103" t="inlineStr"/>
       <c r="G103" t="inlineStr">
         <is>
           <t>祥泰</t>
@@ -4344,9 +3664,6 @@
           <t>田永均</t>
         </is>
       </c>
-      <c r="I103" t="inlineStr"/>
-      <c r="J103" t="inlineStr"/>
-      <c r="K103" t="inlineStr"/>
       <c r="L103" t="inlineStr">
         <is>
           <t>10.09拜访：跟田永均拿料，田永均不拉通威、用户也没法拉；本人之前用过通威但用得少；聊天意愿低。</t>
@@ -4372,18 +3689,11 @@
           <t>三、潜力培育中</t>
         </is>
       </c>
-      <c r="D104" t="inlineStr"/>
-      <c r="E104" t="inlineStr"/>
-      <c r="F104" t="inlineStr"/>
-      <c r="G104" t="inlineStr"/>
       <c r="H104" t="inlineStr">
         <is>
           <t>田永均</t>
         </is>
       </c>
-      <c r="I104" t="inlineStr"/>
-      <c r="J104" t="inlineStr"/>
-      <c r="K104" t="inlineStr"/>
       <c r="L104" t="inlineStr">
         <is>
           <t>10.09拜访：用户不愿意交谈。</t>
@@ -4409,11 +3719,9 @@
           <t>一、通威现有用户</t>
         </is>
       </c>
-      <c r="D105" t="inlineStr"/>
       <c r="E105" t="n">
         <v>2</v>
       </c>
-      <c r="F105" t="inlineStr"/>
       <c r="G105" t="inlineStr">
         <is>
           <t>通威（本兆前段用一点翔泰、后转通威）</t>
@@ -4424,9 +3732,6 @@
           <t>—（公司饲料活动拿料）</t>
         </is>
       </c>
-      <c r="I105" t="inlineStr"/>
-      <c r="J105" t="inlineStr"/>
-      <c r="K105" t="inlineStr"/>
       <c r="L105" t="inlineStr">
         <is>
           <t>8月即作为通威用户参加公司饲料活动拿料；本兆前面用过一点翔泰、后面才转用通威；上次活动拉了一点通威用到现在，下一兆提了一嘴要用全程通威。测水：14:20塘亚盐0.15、14:23塘亚盐0.10，pH均7.4。塘口位置待确认。10.10新增用户走访。</t>
@@ -4452,9 +3757,6 @@
           <t>三、潜力培育中</t>
         </is>
       </c>
-      <c r="D106" t="inlineStr"/>
-      <c r="E106" t="inlineStr"/>
-      <c r="F106" t="inlineStr"/>
       <c r="G106" t="inlineStr">
         <is>
           <t>百洋（最低端）</t>
@@ -4465,9 +3767,6 @@
           <t>—（百洋直供，不经经销商）</t>
         </is>
       </c>
-      <c r="I106" t="inlineStr"/>
-      <c r="J106" t="inlineStr"/>
-      <c r="K106" t="inlineStr"/>
       <c r="L106" t="inlineStr">
         <is>
           <t>百洋直供用户，直接从厂里拿料，不经经销商；用百洋最低端料，包产不高；因直供价低转料意愿不强。其租的塘明年5月到期，届时需另找养户租塘续养、不找经销商（找经销商租塘就被绑定按经销商意思拿料、比百洋直供贵、不划算）。10.10客情走访。</t>
@@ -4493,14 +3792,6 @@
           <t>三、潜力培育中</t>
         </is>
       </c>
-      <c r="D107" t="inlineStr"/>
-      <c r="E107" t="inlineStr"/>
-      <c r="F107" t="inlineStr"/>
-      <c r="G107" t="inlineStr"/>
-      <c r="H107" t="inlineStr"/>
-      <c r="I107" t="inlineStr"/>
-      <c r="J107" t="inlineStr"/>
-      <c r="K107" t="inlineStr"/>
       <c r="L107" t="inlineStr">
         <is>
           <t>【养殖关键节点】出鱼/抓鱼：2026-10-10（出鱼期，抓鱼中）；放苗时间：待出鱼后回访补全。
@@ -4527,17 +3818,11 @@
           <t>三、潜力培育中</t>
         </is>
       </c>
-      <c r="D108" t="inlineStr"/>
-      <c r="E108" t="inlineStr"/>
-      <c r="F108" t="inlineStr"/>
       <c r="G108" t="inlineStr">
         <is>
           <t>翔泰</t>
         </is>
       </c>
-      <c r="H108" t="inlineStr"/>
-      <c r="I108" t="inlineStr"/>
-      <c r="J108" t="inlineStr"/>
       <c r="K108" t="inlineStr">
         <is>
           <t>稳定且较高（陈南高亲述）</t>
@@ -4573,16 +3858,19 @@
           <t>锦山镇039乡道（陈尧光对面）</t>
         </is>
       </c>
-      <c r="E109" t="inlineStr"/>
-      <c r="F109" t="inlineStr"/>
-      <c r="G109" t="inlineStr"/>
-      <c r="H109" t="inlineStr"/>
-      <c r="I109" t="inlineStr"/>
-      <c r="J109" t="inlineStr"/>
-      <c r="K109" t="inlineStr"/>
+      <c r="G109" t="inlineStr">
+        <is>
+          <t>海大+祥泰</t>
+        </is>
+      </c>
+      <c r="H109" t="inlineStr">
+        <is>
+          <t>何经理（即何老板，同人异称）</t>
+        </is>
+      </c>
       <c r="L109" t="inlineStr">
         <is>
-          <t>新养殖户，爱通威地图未标；塘位于陈尧光对面（锦山镇039乡道）。2026-10-12 测水：pH 7.0、氨氮 0.20、亚盐 0.10，三项正常。目前仅测水服务，尚未走访了解养殖规模与用料。</t>
+          <t>新养殖户，爱通威地图未标；塘位于陈尧光对面（锦山镇039乡道）。2026-10-12 测水：pH 7.0、氨氮 0.20、亚盐 0.10，三项正常。目前仅测水服务，尚未走访了解养殖规模与用料。；与陈伟均跟何经理拿料（海大+祥泰），疑似一家人（用户标注？待核实，不擅自定性）。</t>
         </is>
       </c>
       <c r="M109" t="inlineStr">
@@ -4610,21 +3898,114 @@
           <t>锦山镇039乡道（陈姐塘位于其对面）</t>
         </is>
       </c>
-      <c r="E110" t="inlineStr"/>
-      <c r="F110" t="inlineStr"/>
-      <c r="G110" t="inlineStr"/>
-      <c r="H110" t="inlineStr"/>
-      <c r="I110" t="inlineStr"/>
-      <c r="J110" t="inlineStr"/>
-      <c r="K110" t="inlineStr"/>
+      <c r="G110" t="inlineStr">
+        <is>
+          <t>百洋5601+鸿业</t>
+        </is>
+      </c>
+      <c r="H110" t="inlineStr">
+        <is>
+          <t>陈江乾</t>
+        </is>
+      </c>
       <c r="L110" t="inlineStr">
         <is>
-          <t>位置参照点：陈姐塘位于其对面（锦山镇039乡道）；尚未走访了解养殖情况。</t>
+          <t>10.12客情走访：现用百洋5601+鸿业、跟陈江乾拿料；料塔计重损坏、维修要求将料全部排出，协助搬运/排出数袋料做客情维护。位置：陈姐塘对面（锦山镇039乡道）。</t>
         </is>
       </c>
       <c r="M110" t="inlineStr">
         <is>
-          <t>待走访了解养殖规模与用料，确认是否目标客户。</t>
+          <t>趁料塔维修排料期加深客情，推通威转料窗口。</t>
+        </is>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" t="n">
+        <v>110</v>
+      </c>
+      <c r="B111" t="inlineStr">
+        <is>
+          <t>叶志强</t>
+        </is>
+      </c>
+      <c r="C111" t="inlineStr">
+        <is>
+          <t>三、潜力培育中</t>
+        </is>
+      </c>
+      <c r="G111" t="inlineStr">
+        <is>
+          <t>长荣海一（推测，袋皮见，待本人确认）</t>
+        </is>
+      </c>
+      <c r="L111" t="inlineStr">
+        <is>
+          <t>10.12客情走访扑空、未交谈；见其此前抓鱼（出鱼期信号，具体日期待核实，出鱼期静默待出完再访）；投料机旁见长荣海一（海一，竞品）塑料袋，推测现用该料、待本人确认。新增未入册。</t>
+        </is>
+      </c>
+      <c r="M111" t="inlineStr">
+        <is>
+          <t>出鱼期静默，出完再访补全信息（养殖规模/现用料/拿料对象/地址）。</t>
+        </is>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" t="n">
+        <v>111</v>
+      </c>
+      <c r="B112" t="inlineStr">
+        <is>
+          <t>陈伟</t>
+        </is>
+      </c>
+      <c r="C112" t="inlineStr">
+        <is>
+          <t>三、潜力培育中</t>
+        </is>
+      </c>
+      <c r="G112" t="inlineStr">
+        <is>
+          <t>海大+祥泰</t>
+        </is>
+      </c>
+      <c r="H112" t="inlineStr">
+        <is>
+          <t>何经理（何老板）</t>
+        </is>
+      </c>
+      <c r="M112" t="inlineStr">
+        <is>
+          <t>何经理用户，何经理主打海大和祥泰，从拉苗到动保到抓鱼一条龙服务，绑定关系很强（与档案#65对齐补建）。与陈姐疑似一家人（用户标注？待核实，不擅自定性）。</t>
+        </is>
+      </c>
+      <c r="N112" t="inlineStr">
+        <is>
+          <t>竞品深度绑定（D级），维持正常客勤，不单列高价值跟进。</t>
+        </is>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" t="n">
+        <v>112</v>
+      </c>
+      <c r="B113" t="inlineStr">
+        <is>
+          <t>潘如府</t>
+        </is>
+      </c>
+      <c r="C113" t="inlineStr">
+        <is>
+          <t>三、潜力培育中</t>
+        </is>
+      </c>
+      <c r="M113" t="inlineStr">
+        <is>
+          <t>10.12客情走访：沟通后续用料问题（与潘如军为不同人，用户17:14明确区分）。新增未入册。</t>
+        </is>
+      </c>
+      <c r="N113" t="inlineStr">
+        <is>
+          <t>趁后续用料沟通窗口推通威转料。</t>
         </is>
       </c>
     </row>

--- a/数据/用户摸牌表.xlsx
+++ b/数据/用户摸牌表.xlsx
@@ -1068,7 +1068,7 @@
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>电话联系测水打样，鱼七两左右、肥满度好。</t>
+          <t>电话联系测水打样，鱼七两左右、肥满度好。10.13打样：鱼一斤三左右，长势好（较9月28日七两）。</t>
         </is>
       </c>
       <c r="M19" t="inlineStr">

--- a/数据/用户摸牌表.xlsx
+++ b/数据/用户摸牌表.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N113"/>
+  <dimension ref="A1:N115"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1083,7 +1083,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>丁立强</t>
+          <t>丁力强</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -1091,9 +1091,19 @@
           <t>三、潜力培育中</t>
         </is>
       </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>锦山镇西坡村/信坡村/南排坡（多村基地）</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>≥10（在测10口，余待补）</t>
+        </is>
+      </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>有建设光合菌扩培系统的需求。使用我司动保产品后持续跟踪效果，打样鱼五两左右。</t>
+          <t>有建设光合菌扩培系统的需求。使用我司动保产品后持续跟踪效果，打样鱼五两左右。10.13基地客勤+测水10口塘：西坡村3/5/4/2/1号塘、信坡村6/10号塘、南排坡7/8/9号塘，三项均正常（1号塘pH8.6经人眼复核确认）；其余塘口待补测。</t>
         </is>
       </c>
       <c r="M20" t="inlineStr">
@@ -1229,14 +1239,29 @@
           <t>三、潜力培育中</t>
         </is>
       </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>罗豆农场猪场</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>约8（4口已出鱼）</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>海一</t>
+        </is>
+      </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>对光合菌培养感兴趣，已交流培养经验。</t>
+          <t>对光合菌培养感兴趣，已交流培养经验。10.13客勤+测水1/2/4/3号塘（罗豆农场猪场），三项均正常；对光合菌培养感兴趣（9月已交流）；另有4口塘已出完鱼，在产4口，合计约8口；与丁茂溪同用海一。</t>
         </is>
       </c>
       <c r="M25" t="inlineStr">
         <is>
-          <t>持续服务培育，寻找切入时机</t>
+          <t>持续客勤+测水服务培育，待新造投料窗口推通威转化</t>
         </is>
       </c>
     </row>
@@ -4006,6 +4031,66 @@
       <c r="N113" t="inlineStr">
         <is>
           <t>趁后续用料沟通窗口推通威转料。</t>
+        </is>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" t="n">
+        <v>113</v>
+      </c>
+      <c r="B114" t="inlineStr">
+        <is>
+          <t>丁茂溪</t>
+        </is>
+      </c>
+      <c r="C114" t="inlineStr">
+        <is>
+          <t>三、潜力培育中</t>
+        </is>
+      </c>
+      <c r="G114" t="inlineStr">
+        <is>
+          <t>海一</t>
+        </is>
+      </c>
+      <c r="L114" t="inlineStr">
+        <is>
+          <t>10.13客勤服务时确认：与丁伟峰同用海一料（同用海一线索客户，经丁伟峰客勤时提及）；规模/地址/拿料对象待补档。</t>
+        </is>
+      </c>
+      <c r="M114" t="inlineStr">
+        <is>
+          <t>补全养殖规模/地址/拿料对象，同线经营推通威转化</t>
+        </is>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" t="n">
+        <v>114</v>
+      </c>
+      <c r="B115" t="inlineStr">
+        <is>
+          <t>梁修成</t>
+        </is>
+      </c>
+      <c r="C115" t="inlineStr">
+        <is>
+          <t>三、潜力培育中</t>
+        </is>
+      </c>
+      <c r="G115" t="inlineStr">
+        <is>
+          <t>海大2552</t>
+        </is>
+      </c>
+      <c r="L115" t="inlineStr">
+        <is>
+          <t>10.13走访（新名建档，三表此前查无）：现用海大2552，仓库仍囤较多该料、判断为刚到一批，近期料足、无换料刚需；已约10.14早为其测水。</t>
+        </is>
+      </c>
+      <c r="M115" t="inlineStr">
+        <is>
+          <t>先做客情维护+履约测水，待库存消化后再谈通威转化</t>
         </is>
       </c>
     </row>
@@ -4062,7 +4147,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>93</v>
+        <v>98</v>
       </c>
     </row>
     <row r="5">
@@ -4072,7 +4157,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>107</v>
+        <v>114</v>
       </c>
     </row>
   </sheetData>

--- a/数据/用户摸牌表.xlsx
+++ b/数据/用户摸牌表.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N115"/>
+  <dimension ref="A1:N121"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1103,7 +1103,7 @@
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>有建设光合菌扩培系统的需求。使用我司动保产品后持续跟踪效果，打样鱼五两左右。10.13基地客勤+测水10口塘：西坡村3/5/4/2/1号塘、信坡村6/10号塘、南排坡7/8/9号塘，三项均正常（1号塘pH8.6经人眼复核确认）；其余塘口待补测。</t>
+          <t>有建设光合菌扩培系统的需求。使用我司动保产品后持续跟踪效果，打样鱼五两左右。10.13基地客勤+测水10口塘：西坡村3/5/4/2/1号塘、信坡村6/10号塘、南排坡7/8/9号塘，三项均正常（1号塘pH8.6经人眼复核确认）；其余塘口待补测。 10.14协助马总放石斑进塘。</t>
         </is>
       </c>
       <c r="M20" t="inlineStr">
@@ -2921,7 +2921,7 @@
       </c>
       <c r="L79" t="inlineStr">
         <is>
-          <t>百洋5602，二两鱼。 【10.07补充：冯学新兼做歌颂料渠道，吴杨松跟其拿现金料105元/包；其本人仍用百洋5602】</t>
+          <t>百洋5602，二两鱼。 【10.07补充：冯学新兼做歌颂料渠道，吴杨松跟其拿现金料105元/包；其本人仍用百洋5602】 【10.15补充：基地与云维军基地合并（用户口述「冯学兴」，同音变体，权威名冯学新）。】</t>
         </is>
       </c>
       <c r="M79" t="inlineStr">
@@ -4023,6 +4023,11 @@
           <t>三、潜力培育中</t>
         </is>
       </c>
+      <c r="L113" t="inlineStr">
+        <is>
+          <t>10.14回访：反映黑黄料问题，料塔迟迟未动工；黑黄料涉及饲料品牌与批次待取样核实，料塔未动工原因与预计工期待跟进。</t>
+        </is>
+      </c>
       <c r="M113" t="inlineStr">
         <is>
           <t>10.12客情走访：沟通后续用料问题（与潘如军为不同人，用户17:14明确区分）。新增未入册。</t>
@@ -4085,12 +4090,162 @@
       </c>
       <c r="L115" t="inlineStr">
         <is>
-          <t>10.13走访（新名建档，三表此前查无）：现用海大2552，仓库仍囤较多该料、判断为刚到一批，近期料足、无换料刚需；已约10.14早为其测水。</t>
+          <t>10.13走访（新名建档，三表此前查无）：现用海大2552，仓库仍囤较多该料、判断为刚到一批，近期料足、无换料刚需；已约10.14早为其测水。 10.14拜访：用料情况同樊法云，用到一半打样效果不好即停。 10.15走访中获悉：存塘罗非50万苗。</t>
         </is>
       </c>
       <c r="M115" t="inlineStr">
         <is>
           <t>先做客情维护+履约测水，待库存消化后再谈通威转化</t>
+        </is>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" t="n">
+        <v>115</v>
+      </c>
+      <c r="B116" t="inlineStr">
+        <is>
+          <t>吴焕亮</t>
+        </is>
+      </c>
+      <c r="C116" t="inlineStr">
+        <is>
+          <t>三、潜力培育中</t>
+        </is>
+      </c>
+      <c r="L116" t="inlineStr">
+        <is>
+          <t>10.15客情走访（新名建档，三表此前查无）。</t>
+        </is>
+      </c>
+      <c r="M116" t="inlineStr">
+        <is>
+          <t>持续服务培育，寻找切入时机</t>
+        </is>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" t="n">
+        <v>116</v>
+      </c>
+      <c r="B117" t="inlineStr">
+        <is>
+          <t>云维军</t>
+        </is>
+      </c>
+      <c r="C117" t="inlineStr">
+        <is>
+          <t>三、潜力培育中</t>
+        </is>
+      </c>
+      <c r="L117" t="inlineStr">
+        <is>
+          <t>10.15客情走访（新名建档）：基地与冯学新基地合并（用户口述「冯学兴」，同音变体）。</t>
+        </is>
+      </c>
+      <c r="M117" t="inlineStr">
+        <is>
+          <t>持续服务培育，寻找切入时机</t>
+        </is>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" t="n">
+        <v>117</v>
+      </c>
+      <c r="B118" t="inlineStr">
+        <is>
+          <t>郑国庆</t>
+        </is>
+      </c>
+      <c r="C118" t="inlineStr">
+        <is>
+          <t>三、潜力培育中</t>
+        </is>
+      </c>
+      <c r="L118" t="inlineStr">
+        <is>
+          <t>10.15客情走访（新名建档，三表此前查无）。</t>
+        </is>
+      </c>
+      <c r="M118" t="inlineStr">
+        <is>
+          <t>持续服务培育，寻找切入时机</t>
+        </is>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" t="n">
+        <v>118</v>
+      </c>
+      <c r="B119" t="inlineStr">
+        <is>
+          <t>丁旭华</t>
+        </is>
+      </c>
+      <c r="C119" t="inlineStr">
+        <is>
+          <t>三、潜力培育中</t>
+        </is>
+      </c>
+      <c r="L119" t="inlineStr">
+        <is>
+          <t>10.15客情走访（新名建档）：存塘约20万苗，计划2027年4月抓鱼；这一造鱼大的7两左右、小的6两左右。下一造拿料节点约在2027年4月出鱼后。</t>
+        </is>
+      </c>
+      <c r="M119" t="inlineStr">
+        <is>
+          <t>持续客情维护，盯2027年4月出鱼后的转料窗口</t>
+        </is>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" t="n">
+        <v>119</v>
+      </c>
+      <c r="B120" t="inlineStr">
+        <is>
+          <t>樊法云</t>
+        </is>
+      </c>
+      <c r="C120" t="inlineStr">
+        <is>
+          <t>三、潜力培育中</t>
+        </is>
+      </c>
+      <c r="L120" t="inlineStr">
+        <is>
+          <t>10.15走访中获悉：存塘罗非30万苗。用户本次记作「樊法元」，同音变体。10.14曾拜访交谈用料：现用海一、海大，之前拉过通威、打样效果不好也没全程用，换料接受度低。</t>
+        </is>
+      </c>
+      <c r="M120" t="inlineStr">
+        <is>
+          <t>待其下一批拿料节点再探通威转化窗口</t>
+        </is>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" t="n">
+        <v>120</v>
+      </c>
+      <c r="B121" t="inlineStr">
+        <is>
+          <t>王焕忠</t>
+        </is>
+      </c>
+      <c r="C121" t="inlineStr">
+        <is>
+          <t>三、潜力培育中</t>
+        </is>
+      </c>
+      <c r="L121" t="inlineStr">
+        <is>
+          <t>10.14走访（新名建档，三表此前查无）：用料情况同樊法云，用到一半打样效果不好即停；混料差异难看出谁家饲料更好或者更次，打样不彻底则对比无据。</t>
+        </is>
+      </c>
+      <c r="M121" t="inlineStr">
+        <is>
+          <t>持续服务培育，寻找切入时机</t>
         </is>
       </c>
     </row>
@@ -4147,7 +4302,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>98</v>
+        <v>104</v>
       </c>
     </row>
     <row r="5">
@@ -4157,7 +4312,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>114</v>
+        <v>120</v>
       </c>
     </row>
   </sheetData>

--- a/数据/用户摸牌表.xlsx
+++ b/数据/用户摸牌表.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N121"/>
+  <dimension ref="A1:N122"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -595,7 +595,7 @@
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>已转用通威。有效塘口1、2、3、6、7号已完成两轮打样：9月7/8日至9月29日，1号塘0.50增至0.72、2号塘0.31增至0.50、3号塘0.25增至0.54、6号塘0.55增至0.72、7号塘0.45增至0.66，总增重1.08，平均增重约0.22。期间曾出现死鱼、亚硝酸盐严重超标，协助处理后当日见效，次日回访恢复正常。目前养殖情况稳定，持续跟进中。 【10.05走访秋溪尾基地、10.07走访大致坡基地，均测水做服务；两处均反馈喂料后水面有大片油膜，用户为1053专用料户；】 【10.07大致坡基地测水7口塘：2号、3号塘亚盐0.8超量程⚠️（鱼易浮头，重点处理）；1号、7号塘氨氮0.90偏高；4号、5号塘正常；6号塘氨氮0.50、亚盐0.20；油膜问题待核实塘口还是饲料原因】</t>
+          <t>已转用通威。有效塘口1、2、3、6、7号已完成两轮打样：9月7/8日至9月29日，1号塘0.50增至0.72、2号塘0.31增至0.50、3号塘0.25增至0.54、6号塘0.55增至0.72、7号塘0.45增至0.66，总增重1.08，平均增重约0.22。期间曾出现死鱼、亚硝酸盐严重超标，协助处理后当日见效，次日回访恢复正常。目前养殖情况稳定，持续跟进中。 【10.05走访秋溪尾基地、10.07走访大致坡基地，均测水做服务；两处均反馈喂料后水面有大片油膜，用户为1053专用料户；】 【10.07大致坡基地测水7口塘：2号、3号塘亚盐0.8超量程⚠️（鱼易浮头，重点处理）；1号、7号塘氨氮0.90偏高；4号、5号塘正常；6号塘氨氮0.50、亚盐0.20；油膜问题待核实塘口还是饲料原因】；10月16日大致坡基地第三轮打样：1号1.02、2号0.81、3号0.77、4号0.53、5号0.54、6号0.99、7号0.83斤/条，较9月29日涨0.17-0.31，1号过斤；交谈后续用料计划；查阅8-10月投料台账，用量持续攀升，10月日均约76包</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
@@ -1068,7 +1068,7 @@
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>电话联系测水打样，鱼七两左右、肥满度好。10.13打样：鱼一斤三左右，长势好（较9月28日七两）。</t>
+          <t>电话联系测水打样，鱼七两左右、肥满度好。10.13打样：鱼一斤三左右，长势好（较9月28日七两）。；10.16走访：今日未打样，约定10月23日打样测水（底下那口塘）</t>
         </is>
       </c>
       <c r="M19" t="inlineStr">
@@ -3721,7 +3721,7 @@
       </c>
       <c r="L104" t="inlineStr">
         <is>
-          <t>10.09拜访：用户不愿意交谈。</t>
+          <t>10.09拜访：用户不愿意交谈。；10.16走访：人不在鱼塘，去接小孩，未见到本人</t>
         </is>
       </c>
       <c r="M104" t="inlineStr">
@@ -4246,6 +4246,31 @@
       <c r="M121" t="inlineStr">
         <is>
           <t>持续服务培育，寻找切入时机</t>
+        </is>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" t="n">
+        <v>121</v>
+      </c>
+      <c r="B122" t="inlineStr">
+        <is>
+          <t>榆林舰</t>
+        </is>
+      </c>
+      <c r="C122" t="inlineStr">
+        <is>
+          <t>三、潜力培育中</t>
+        </is>
+      </c>
+      <c r="L122" t="inlineStr">
+        <is>
+          <t>10.16走访（新接触），详情待补</t>
+        </is>
+      </c>
+      <c r="M122" t="inlineStr">
+        <is>
+          <t>补充基本情况后定跟进策略</t>
         </is>
       </c>
     </row>
@@ -4302,7 +4327,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>104</v>
+        <v>105</v>
       </c>
     </row>
     <row r="5">
@@ -4312,7 +4337,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>120</v>
+        <v>121</v>
       </c>
     </row>
   </sheetData>

--- a/数据/用户摸牌表.xlsx
+++ b/数据/用户摸牌表.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N122"/>
+  <dimension ref="A1:N125"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -595,7 +595,7 @@
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>已转用通威。有效塘口1、2、3、6、7号已完成两轮打样：9月7/8日至9月29日，1号塘0.50增至0.72、2号塘0.31增至0.50、3号塘0.25增至0.54、6号塘0.55增至0.72、7号塘0.45增至0.66，总增重1.08，平均增重约0.22。期间曾出现死鱼、亚硝酸盐严重超标，协助处理后当日见效，次日回访恢复正常。目前养殖情况稳定，持续跟进中。 【10.05走访秋溪尾基地、10.07走访大致坡基地，均测水做服务；两处均反馈喂料后水面有大片油膜，用户为1053专用料户；】 【10.07大致坡基地测水7口塘：2号、3号塘亚盐0.8超量程⚠️（鱼易浮头，重点处理）；1号、7号塘氨氮0.90偏高；4号、5号塘正常；6号塘氨氮0.50、亚盐0.20；油膜问题待核实塘口还是饲料原因】；10月16日大致坡基地第三轮打样：1号1.02、2号0.81、3号0.77、4号0.53、5号0.54、6号0.99、7号0.83斤/条，较9月29日涨0.17-0.31，1号过斤；交谈后续用料计划；查阅8-10月投料台账，用量持续攀升，10月日均约76包</t>
+          <t>已转用通威。有效塘口1、2、3、6、7号已完成两轮打样：9月7/8日至9月29日，1号塘0.50增至0.72、2号塘0.31增至0.50、3号塘0.25增至0.54、6号塘0.55增至0.72、7号塘0.45增至0.66，总增重1.08，平均增重约0.22。期间曾出现死鱼、亚硝酸盐严重超标，协助处理后当日见效，次日回访恢复正常。目前养殖情况稳定，持续跟进中。 【10.05走访秋溪尾基地、10.07走访大致坡基地，均测水做服务；两处均反馈喂料后水面有大片油膜，用户为1053专用料户；】 【10.07大致坡基地测水7口塘：2号、3号塘亚盐0.8超量程⚠️（鱼易浮头，重点处理）；1号、7号塘氨氮0.90偏高；4号、5号塘正常；6号塘氨氮0.50、亚盐0.20；油膜问题待核实塘口还是饲料原因】；10月16日大致坡基地第三轮打样：1号1.02、2号0.81、3号0.77、4号0.53、5号0.54、6号0.99、7号0.83斤/条，较9月29日涨0.17-0.31，1号过斤；交谈后续用料计划；查阅8-10月投料台账，用量持续攀升，10月日均约76包；10月19日大致坡基地打样，解答该基地鱼长势偏慢的疑问；4号塘计划本月底出鱼，后续跟进出鱼安排与用料情况</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
@@ -1068,7 +1068,7 @@
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>电话联系测水打样，鱼七两左右、肥满度好。10.13打样：鱼一斤三左右，长势好（较9月28日七两）。；10.16走访：今日未打样，约定10月23日打样测水（底下那口塘）</t>
+          <t>电话联系测水打样，鱼七两左右、肥满度好。10.13打样：鱼一斤三左右，长势好（较9月28日七两）。；10.16走访：今日未打样，约定10月23日打样测水（底下那口塘）；10.23打样测水，塘号结构1号苗塘、2号中间那口、3号路边塘：1号塘10月21日放苗14万尾、亚盐偏高0.3左右踩报警线；2号塘条均八两、存塘鱼7万尾；3号塘条均预计1.4斤以上（10月13日1.35斤）、存塘未知；2号3号水质正常</t>
         </is>
       </c>
       <c r="M19" t="inlineStr">
@@ -1103,7 +1103,7 @@
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>有建设光合菌扩培系统的需求。使用我司动保产品后持续跟踪效果，打样鱼五两左右。10.13基地客勤+测水10口塘：西坡村3/5/4/2/1号塘、信坡村6/10号塘、南排坡7/8/9号塘，三项均正常（1号塘pH8.6经人眼复核确认）；其余塘口待补测。 10.14协助马总放石斑进塘。</t>
+          <t>有建设光合菌扩培系统的需求。使用我司动保产品后持续跟踪效果，打样鱼五两左右。10.13基地客勤+测水10口塘：西坡村3/5/4/2/1号塘、信坡村6/10号塘、南排坡7/8/9号塘，三项均正常（1号塘pH8.6经人眼复核确认）；其余塘口待补测。 10.14协助马总放石斑进塘。；10.23积炭素累计用到100包，今天拉了33包</t>
         </is>
       </c>
       <c r="M20" t="inlineStr">
@@ -2626,7 +2626,7 @@
       </c>
       <c r="L69" t="inlineStr">
         <is>
-          <t>10.09走访：用料已更换，现小料唐人神、大料天翔819（挂账价114，属低档料，判断难养出效果）；现跟谁拿料待问清。鱼苗和大头混养，宝路苗，鱼现八两左右，预计11月初出鱼。【名字确认：名单原“施军华”“司君华”均为同一人施君华；10.05客情维护走访】</t>
+          <t>10.09走访：用料已更换，现小料唐人神、大料天翔819（挂账价114，属低档料，判断难养出效果）；现跟谁拿料待问清。鱼苗和大头混养，宝路苗，鱼现八两左右，预计11月初出鱼。【名字确认：名单原“施军华”“司君华”均为同一人施君华；10.05客情维护走访】；10.17沟通转料：用户口述现用天祥料价格113（同音变体：天翔819），与我司产品价格层级不符，转料非常困难，后续继续跟进</t>
         </is>
       </c>
       <c r="M69" t="inlineStr">
@@ -4240,7 +4240,7 @@
       </c>
       <c r="L121" t="inlineStr">
         <is>
-          <t>10.14走访（新名建档，三表此前查无）：用料情况同樊法云，用到一半打样效果不好即停；混料差异难看出谁家饲料更好或者更次，打样不彻底则对比无据。</t>
+          <t>10.14走访（新名建档，三表此前查无）：用料情况同樊法云，用到一半打样效果不好即停；混料差异难看出谁家饲料更好或者更次，打样不彻底则对比无据。；10.23渠道线索：给王卫明供海大2552料，角色从养殖户延伸至经手供料</t>
         </is>
       </c>
       <c r="M121" t="inlineStr">
@@ -4273,6 +4273,116 @@
           <t>补充基本情况后定跟进策略</t>
         </is>
       </c>
+    </row>
+    <row r="123">
+      <c r="A123" t="n">
+        <v>122</v>
+      </c>
+      <c r="B123" t="inlineStr">
+        <is>
+          <t>陈老板</t>
+        </is>
+      </c>
+      <c r="C123" t="inlineStr">
+        <is>
+          <t>三、潜力培育中</t>
+        </is>
+      </c>
+      <c r="D123" t="inlineStr"/>
+      <c r="E123" t="inlineStr"/>
+      <c r="F123" t="inlineStr"/>
+      <c r="G123" t="inlineStr"/>
+      <c r="H123" t="inlineStr"/>
+      <c r="I123" t="inlineStr"/>
+      <c r="J123" t="inlineStr"/>
+      <c r="K123" t="inlineStr"/>
+      <c r="L123" t="inlineStr">
+        <is>
+          <t>10.19走访（新接触）：养殖叉尾，维护客情，基本情况待跟进；与塔楼区域叉尾养户是否同批待核实</t>
+        </is>
+      </c>
+      <c r="M123" t="inlineStr">
+        <is>
+          <t>持续客情维护，摸清养殖规模与用料情况</t>
+        </is>
+      </c>
+      <c r="N123" t="inlineStr"/>
+    </row>
+    <row r="124">
+      <c r="A124" t="n">
+        <v>123</v>
+      </c>
+      <c r="B124" t="inlineStr">
+        <is>
+          <t>王卫明</t>
+        </is>
+      </c>
+      <c r="C124" t="inlineStr">
+        <is>
+          <t>三、潜力培育中</t>
+        </is>
+      </c>
+      <c r="D124" t="inlineStr"/>
+      <c r="E124" t="inlineStr"/>
+      <c r="F124" t="inlineStr"/>
+      <c r="G124" t="inlineStr">
+        <is>
+          <t>海大2552</t>
+        </is>
+      </c>
+      <c r="H124" t="inlineStr">
+        <is>
+          <t>王焕忠</t>
+        </is>
+      </c>
+      <c r="I124" t="inlineStr"/>
+      <c r="J124" t="inlineStr"/>
+      <c r="K124" t="inlineStr"/>
+      <c r="L124" t="inlineStr">
+        <is>
+          <t>10.22拜访（新接触）：存塘鱼八两左右，之前用百洋料，这一造全程用海大，说明年用料再考虑通威</t>
+        </is>
+      </c>
+      <c r="M124" t="inlineStr">
+        <is>
+          <t>持续客情维护，盯明年出鱼后的转料窗口</t>
+        </is>
+      </c>
+      <c r="N124" t="inlineStr"/>
+    </row>
+    <row r="125">
+      <c r="A125" t="n">
+        <v>124</v>
+      </c>
+      <c r="B125" t="inlineStr">
+        <is>
+          <t>徐在苏</t>
+        </is>
+      </c>
+      <c r="C125" t="inlineStr">
+        <is>
+          <t>三、潜力培育中</t>
+        </is>
+      </c>
+      <c r="D125" t="inlineStr"/>
+      <c r="E125" t="inlineStr"/>
+      <c r="F125" t="inlineStr"/>
+      <c r="G125" t="inlineStr"/>
+      <c r="H125" t="inlineStr"/>
+      <c r="I125" t="inlineStr"/>
+      <c r="J125" t="inlineStr"/>
+      <c r="K125" t="inlineStr"/>
+      <c r="L125" t="inlineStr">
+        <is>
+          <t>10.22走访：老板休息，约次日看抓鱼；10.23抓鱼回访：一号塘包产35（死鱼严重）、二号塘包产38、三号塘未抓完；老徐自述包产不过40系鱼苗问题</t>
+        </is>
+      </c>
+      <c r="M125" t="inlineStr">
+        <is>
+          <t>摸清用料品牌与一号塘死鱼原因，下一造找转化切口</t>
+        </is>
+      </c>
+      <c r="N125" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -4327,7 +4437,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>105</v>
+        <v>108</v>
       </c>
     </row>
     <row r="5">
@@ -4337,7 +4447,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>121</v>
+        <v>124</v>
       </c>
     </row>
   </sheetData>

--- a/数据/用户摸牌表.xlsx
+++ b/数据/用户摸牌表.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N125"/>
+  <dimension ref="A1:N126"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1103,7 +1103,7 @@
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>有建设光合菌扩培系统的需求。使用我司动保产品后持续跟踪效果，打样鱼五两左右。10.13基地客勤+测水10口塘：西坡村3/5/4/2/1号塘、信坡村6/10号塘、南排坡7/8/9号塘，三项均正常（1号塘pH8.6经人眼复核确认）；其余塘口待补测。 10.14协助马总放石斑进塘。；10.23积炭素累计用到100包，今天拉了33包</t>
+          <t>有建设光合菌扩培系统的需求。使用我司动保产品后持续跟踪效果，打样鱼五两左右。10.13基地客勤+测水10口塘：西坡村3/5/4/2/1号塘、信坡村6/10号塘、南排坡7/8/9号塘，三项均正常（1号塘pH8.6经人眼复核确认）；其余塘口待补测。 10.14协助马总放石斑进塘。；10.23积炭素累计用到100包，今天拉了33包；10.25送冻宝和药物，客情维护。</t>
         </is>
       </c>
       <c r="M20" t="inlineStr">
@@ -1742,7 +1742,7 @@
       </c>
       <c r="M40" t="inlineStr">
         <is>
-          <t>盯紧拿苗节点（16号），拿苗后趁冲重量需求推通威；借丁开福放苗刺激快速转料、推开口乐；渠道被马津深卡不给拉，需先打通通路。</t>
+          <t>盯紧拿苗节点（16号），拿苗后趁冲重量需求推通威；借丁开福放苗刺激快速转料、推开口乐；渠道被马津深卡不给拉，需先打通通路。；10.24新增：6号塘氨氮亚盐双高⚠️，2天内复测取具体数值并给调水建议；3号塘为鱼苗塘已拿苗50万尾，拿苗后盯转料窗口；10.10的1号塘是否存栏待核实；塘号按10.24口定基准（3号塘=鱼苗塘、6号塘=双高塘，新增顺延补号）。</t>
         </is>
       </c>
     </row>
@@ -4138,9 +4138,14 @@
           <t>三、潜力培育中</t>
         </is>
       </c>
+      <c r="H117" t="inlineStr">
+        <is>
+          <t>冯学新</t>
+        </is>
+      </c>
       <c r="L117" t="inlineStr">
         <is>
-          <t>10.15客情走访（新名建档）：基地与冯学新基地合并（用户口述「冯学兴」，同音变体）。</t>
+          <t>10.15客情走访（新名建档）：基地与冯学新基地合并（用户口述「冯学兴」，同音变体）。10.25：拿料受限于冯学新。</t>
         </is>
       </c>
       <c r="M117" t="inlineStr">
@@ -4190,7 +4195,7 @@
       </c>
       <c r="L119" t="inlineStr">
         <is>
-          <t>10.15客情走访（新名建档）：存塘约20万苗，计划2027年4月抓鱼；这一造鱼大的7两左右、小的6两左右。下一造拿料节点约在2027年4月出鱼后。</t>
+          <t>10.15客情走访（新名建档）：存塘约20万苗，计划2027年4月抓鱼；这一造鱼大的7两左右、小的6两左右。下一造拿料节点约在2027年4月出鱼后。10.24用户要求打样，查看酵益宝养殖情况；10.25对接打样，案例佐证酵益宝效果。</t>
         </is>
       </c>
       <c r="M119" t="inlineStr">
@@ -4288,14 +4293,6 @@
           <t>三、潜力培育中</t>
         </is>
       </c>
-      <c r="D123" t="inlineStr"/>
-      <c r="E123" t="inlineStr"/>
-      <c r="F123" t="inlineStr"/>
-      <c r="G123" t="inlineStr"/>
-      <c r="H123" t="inlineStr"/>
-      <c r="I123" t="inlineStr"/>
-      <c r="J123" t="inlineStr"/>
-      <c r="K123" t="inlineStr"/>
       <c r="L123" t="inlineStr">
         <is>
           <t>10.19走访（新接触）：养殖叉尾，维护客情，基本情况待跟进；与塔楼区域叉尾养户是否同批待核实</t>
@@ -4306,7 +4303,6 @@
           <t>持续客情维护，摸清养殖规模与用料情况</t>
         </is>
       </c>
-      <c r="N123" t="inlineStr"/>
     </row>
     <row r="124">
       <c r="A124" t="n">
@@ -4322,9 +4318,6 @@
           <t>三、潜力培育中</t>
         </is>
       </c>
-      <c r="D124" t="inlineStr"/>
-      <c r="E124" t="inlineStr"/>
-      <c r="F124" t="inlineStr"/>
       <c r="G124" t="inlineStr">
         <is>
           <t>海大2552</t>
@@ -4335,9 +4328,6 @@
           <t>王焕忠</t>
         </is>
       </c>
-      <c r="I124" t="inlineStr"/>
-      <c r="J124" t="inlineStr"/>
-      <c r="K124" t="inlineStr"/>
       <c r="L124" t="inlineStr">
         <is>
           <t>10.22拜访（新接触）：存塘鱼八两左右，之前用百洋料，这一造全程用海大，说明年用料再考虑通威</t>
@@ -4348,7 +4338,6 @@
           <t>持续客情维护，盯明年出鱼后的转料窗口</t>
         </is>
       </c>
-      <c r="N124" t="inlineStr"/>
     </row>
     <row r="125">
       <c r="A125" t="n">
@@ -4364,14 +4353,6 @@
           <t>三、潜力培育中</t>
         </is>
       </c>
-      <c r="D125" t="inlineStr"/>
-      <c r="E125" t="inlineStr"/>
-      <c r="F125" t="inlineStr"/>
-      <c r="G125" t="inlineStr"/>
-      <c r="H125" t="inlineStr"/>
-      <c r="I125" t="inlineStr"/>
-      <c r="J125" t="inlineStr"/>
-      <c r="K125" t="inlineStr"/>
       <c r="L125" t="inlineStr">
         <is>
           <t>10.22走访：老板休息，约次日看抓鱼；10.23抓鱼回访：一号塘包产35（死鱼严重）、二号塘包产38、三号塘未抓完；老徐自述包产不过40系鱼苗问题</t>
@@ -4382,7 +4363,31 @@
           <t>摸清用料品牌与一号塘死鱼原因，下一造找转化切口</t>
         </is>
       </c>
-      <c r="N125" t="inlineStr"/>
+    </row>
+    <row r="126">
+      <c r="A126" t="n">
+        <v>125</v>
+      </c>
+      <c r="B126" t="inlineStr">
+        <is>
+          <t>施锦云</t>
+        </is>
+      </c>
+      <c r="C126" t="inlineStr">
+        <is>
+          <t>三、潜力培育中</t>
+        </is>
+      </c>
+      <c r="L126" t="inlineStr">
+        <is>
+          <t>10月25日首次拜访，用户不在，基本情况待了解。</t>
+        </is>
+      </c>
+      <c r="M126" t="inlineStr">
+        <is>
+          <t>择日再访，摸清养殖规模、现用品牌与拿料对象。</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -4437,7 +4442,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>108</v>
+        <v>109</v>
       </c>
     </row>
     <row r="5">
@@ -4447,7 +4452,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>124</v>
+        <v>125</v>
       </c>
     </row>
   </sheetData>

--- a/数据/用户摸牌表.xlsx
+++ b/数据/用户摸牌表.xlsx
@@ -4370,7 +4370,7 @@
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>施锦云</t>
+          <t>施景云</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">

--- a/数据/用户摸牌表.xlsx
+++ b/数据/用户摸牌表.xlsx
@@ -1103,7 +1103,7 @@
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>有建设光合菌扩培系统的需求。使用我司动保产品后持续跟踪效果，打样鱼五两左右。10.13基地客勤+测水10口塘：西坡村3/5/4/2/1号塘、信坡村6/10号塘、南排坡7/8/9号塘，三项均正常（1号塘pH8.6经人眼复核确认）；其余塘口待补测。 10.14协助马总放石斑进塘。；10.23积炭素累计用到100包，今天拉了33包；10.25送冻宝和药物，客情维护。</t>
+          <t>有建设光合菌扩培系统的需求。使用我司动保产品后持续跟踪效果，打样鱼五两左右。10.13基地客勤+测水10口塘：西坡村3/5/4/2/1号塘、信坡村6/10号塘、南排坡7/8/9号塘，三项均正常（1号塘pH8.6经人眼复核确认）；其余塘口待补测。 10.14协助马总放石斑进塘。；10.23积炭素累计用到100包，今天拉了33包；10.25送动保和药物，客情维护。</t>
         </is>
       </c>
       <c r="M20" t="inlineStr">

--- a/数据/用户摸牌表.xlsx
+++ b/数据/用户摸牌表.xlsx
@@ -1068,12 +1068,12 @@
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>电话联系测水打样，鱼七两左右、肥满度好。10.13打样：鱼一斤三左右，长势好（较9月28日七两）。；10.16走访：今日未打样，约定10月23日打样测水（底下那口塘）；10.23打样测水，塘号结构1号苗塘、2号中间那口、3号路边塘：1号塘10月21日放苗14万尾、亚盐偏高0.3左右踩报警线；2号塘条均八两、存塘鱼7万尾；3号塘条均预计1.4斤以上（10月13日1.35斤）、存塘未知；2号3号水质正常</t>
+          <t>电话联系测水打样，鱼七两左右、肥满度好。10.13打样：鱼一斤三左右，长势好（较9月28日七两）。；10.16走访：今日未打样，约定10月23日打样测水（底下那口塘）；10.23打样测水，塘号结构1号苗塘、2号中间那口、3号路边塘：1号塘10月21日放苗14万尾、亚盐偏高0.3左右踩报警线；2号塘条均八两、存塘鱼7万尾；3号塘条均预计1.4斤以上（10月13日1.35斤）、存塘未知；2号3号水质正常；10.27测水：1号苗塘经硝硝乐（同音变体：消消乐）处理，原亚盐0.3+踩报警线已降至正常；2号塘亚盐0.25临界接近0.3警戒线、预计约20天出鱼；用户想培育光合菌</t>
         </is>
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>持续服务培育，寻找切入时机</t>
+          <t>持续服务培育，2号塘亚盐临界(0.25)临近出鱼期重点盯复测；借用户培育光合菌需求深化技术服务、寻找切料时机</t>
         </is>
       </c>
     </row>
@@ -4355,7 +4355,7 @@
       </c>
       <c r="L125" t="inlineStr">
         <is>
-          <t>10.22走访：老板休息，约次日看抓鱼；10.23抓鱼回访：一号塘包产35（死鱼严重）、二号塘包产38、三号塘未抓完；老徐自述包产不过40系鱼苗问题</t>
+          <t>10.22走访：老板休息，约次日看抓鱼；10.23抓鱼回访：一号塘包产35（死鱼严重）、二号塘包产38、三号塘未抓完；老徐自述包产不过40系鱼苗问题；10.27出鱼回访：最后一口塘未干塘、已抓8万多、包产约39；用户反馈鱼苗质量太低（与包产不过40系鱼苗问题印证）</t>
         </is>
       </c>
       <c r="M125" t="inlineStr">

--- a/数据/用户摸牌表.xlsx
+++ b/数据/用户摸牌表.xlsx
@@ -1103,7 +1103,7 @@
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>有建设光合菌扩培系统的需求。使用我司动保产品后持续跟踪效果，打样鱼五两左右。10.13基地客勤+测水10口塘：西坡村3/5/4/2/1号塘、信坡村6/10号塘、南排坡7/8/9号塘，三项均正常（1号塘pH8.6经人眼复核确认）；其余塘口待补测。 10.14协助马总放石斑进塘。；10.23积炭素累计用到100包，今天拉了33包；10.25送动保和药物，客情维护。</t>
+          <t>有建设光合菌扩培系统的需求。使用我司动保产品后持续跟踪效果，打样鱼五两左右。10.13基地客勤+测水10口塘：西坡村3/5/4/2/1号塘、信坡村6/10号塘、南排坡7/8/9号塘，三项均正常（1号塘pH8.6经人眼复核确认）；其余塘口待补测。 10.14协助马总放石斑进塘。；10.23积炭素累计用到100包，今天拉了33包；10.25送动保和药物，客情维护。；10.27测水：西坡村1/2/3/4/5号塘，pH、氨氮、亚盐均正常，无异常。</t>
         </is>
       </c>
       <c r="M20" t="inlineStr">

--- a/数据/用户摸牌表.xlsx
+++ b/数据/用户摸牌表.xlsx
@@ -1066,6 +1066,11 @@
           <t>三、潜力培育中</t>
         </is>
       </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>9912（我司；非全程用）</t>
+        </is>
+      </c>
       <c r="L19" t="inlineStr">
         <is>
           <t>电话联系测水打样，鱼七两左右、肥满度好。10.13打样：鱼一斤三左右，长势好（较9月28日七两）。；10.16走访：今日未打样，约定10月23日打样测水（底下那口塘）；10.23打样测水，塘号结构1号苗塘、2号中间那口、3号路边塘：1号塘10月21日放苗14万尾、亚盐偏高0.3左右踩报警线；2号塘条均八两、存塘鱼7万尾；3号塘条均预计1.4斤以上（10月13日1.35斤）、存塘未知；2号3号水质正常；10.27测水：1号苗塘经硝硝乐（同音变体：消消乐）处理，原亚盐0.3+踩报警线已降至正常；2号塘亚盐0.25临界接近0.3警戒线、预计约20天出鱼；用户想培育光合菌</t>
@@ -1099,6 +1104,11 @@
       <c r="E20" t="inlineStr">
         <is>
           <t>≥10（在测10口，余待补）</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>1053（非全程用）</t>
         </is>
       </c>
       <c r="L20" t="inlineStr">

--- a/数据/用户摸牌表.xlsx
+++ b/数据/用户摸牌表.xlsx
@@ -1073,12 +1073,12 @@
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>电话联系测水打样，鱼七两左右、肥满度好。10.13打样：鱼一斤三左右，长势好（较9月28日七两）。；10.16走访：今日未打样，约定10月23日打样测水（底下那口塘）；10.23打样测水，塘号结构1号苗塘、2号中间那口、3号路边塘：1号塘10月21日放苗14万尾、亚盐偏高0.3左右踩报警线；2号塘条均八两、存塘鱼7万尾；3号塘条均预计1.4斤以上（10月13日1.35斤）、存塘未知；2号3号水质正常；10.27测水：1号苗塘经硝硝乐（同音变体：消消乐）处理，原亚盐0.3+踩报警线已降至正常；2号塘亚盐0.25临界接近0.3警戒线、预计约20天出鱼；用户想培育光合菌</t>
+          <t>电话联系测水打样，鱼七两左右、肥满度好。10.13打样：鱼一斤三左右，长势好（较9月28日七两）。；10.16走访：今日未打样，约定10月23日打样测水（底下那口塘）；10.23打样测水，塘号结构1号苗塘、2号中间那口、3号路边塘：1号塘10月21日放苗14万尾、亚盐偏高0.3左右踩报警线；2号塘条均八两、存塘鱼7万尾；3号塘条均预计1.4斤以上（10月13日1.35斤）、存塘未知；2号3号水质正常10月27日测水（比色卡目视实测，铺前镇华兰村）：1号苗塘pH7.1/氨氮0.20/亚盐0.15（硝硝乐处理后正常）、2号塘pH6.9/氨氮0/亚盐0.20（临界临近0.3警戒线，预计约20天出鱼）、3号塘pH7.2/氨氮0/亚盐0.05（原未测补测）；用户想培育光合菌。</t>
         </is>
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>持续服务培育，2号塘亚盐临界(0.25)临近出鱼期重点盯复测；借用户培育光合菌需求深化技术服务、寻找切料时机</t>
+          <t>持续服务培育，2号塘亚盐0.20（实测，临界临近0.3警戒线）临近出鱼期重点盯复测；借用户培育光合菌需求深化技术服务、寻找切料时机</t>
         </is>
       </c>
     </row>
@@ -1113,7 +1113,7 @@
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>有建设光合菌扩培系统的需求。使用我司动保产品后持续跟踪效果，打样鱼五两左右。10.13基地客勤+测水10口塘：西坡村3/5/4/2/1号塘、信坡村6/10号塘、南排坡7/8/9号塘，三项均正常（1号塘pH8.6经人眼复核确认）；其余塘口待补测。 10.14协助马总放石斑进塘。；10.23积炭素累计用到100包，今天拉了33包；10.25送动保和药物，客情维护。；10.27测水：西坡村1/2/3/4/5号塘，pH、氨氮、亚盐均正常，无异常。</t>
+          <t>有建设光合菌扩培系统的需求。使用我司动保产品后持续跟踪效果，打样鱼五两左右。10.13基地客勤+测水10口塘：西坡村3/5/4/2/1号塘、信坡村6/10号塘、南排坡7/8/9号塘，三项均正常（1号塘pH8.6经人眼复核确认）；其余塘口待补测。 10.14协助马总放石斑进塘。；10.23积炭素累计用到100包，今天拉了33包；10.25送动保和药物，客情维护。10月27日测水（比色卡目视实测）：1号塘(罗豆农场猪场)pH7.2/氨氮0.20/亚盐0、2号塘(西坡村)pH7.4/氨氮0.60/亚盐0.10(五口最高，回访重点)、3号塘pH7.2/氨氮0.60/亚盐0.005、4号塘pH7.0/氨氮0.20/亚盐0、5号塘pH7.2/氨氮0.20/亚盐0.01；全部在安全线内。</t>
         </is>
       </c>
       <c r="M20" t="inlineStr">
